--- a/myCBD/myInfo/gbd.ICD.Map.xlsx
+++ b/myCBD/myInfo/gbd.ICD.Map.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0.CBD\myCBD\myInfo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="10935"/>
   </bookViews>
@@ -36,7 +31,7 @@
     <author>Dauphine, David (CDPH-CHSI)</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="1" shapeId="0">
+    <comment ref="C57" authorId="1">
       <text>
         <r>
           <rPr>
@@ -84,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P126" authorId="2" shapeId="0">
+    <comment ref="P126" authorId="2">
       <text>
         <r>
           <rPr>
@@ -4476,7 +4471,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.;###0."/>
   </numFmts>
@@ -5136,7 +5131,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5171,7 +5166,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/myCBD/myInfo/gbd.ICD.Map.xlsx
+++ b/myCBD/myInfo/gbd.ICD.Map.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0.CBD\myCBD\myInfo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="10935"/>
   </bookViews>
@@ -12,7 +17,7 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$X$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$X$225</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +36,7 @@
     <author>Dauphine, David (CDPH-CHSI)</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="1">
+    <comment ref="C57" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P126" authorId="2">
+    <comment ref="P126" authorId="2" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="1403">
   <si>
     <t>I. Communicable, maternal, perinatal and nutritional conditions</t>
   </si>
@@ -3940,9 +3945,6 @@
     <t>S|W39|W44|W5[3-9]|W6[0-4]|W7[7-9]|W[8-9]|X[2,5]|X3[0-2,9]|Y[4-7]|Y8[0-6,8]|Y89[2-9]</t>
   </si>
   <si>
-    <t xml:space="preserve">Added S per Dave (see notes, consider renaming category). Moved Y890 to homicide per CDPH and Y891 to collective violence per IHME. Also per IHME, moved V050-V98 to road injuries and added X30-32 and X39 from natural disasters.  </t>
-  </si>
-  <si>
     <t>Think I was able to map all Michael emailed me about except 000 and 0000</t>
   </si>
   <si>
@@ -4116,23 +4118,6 @@
     <t>Move G721 to alcohol, G45-46 to stroke - some of G45 and all of G46 still here?
 REVIEW WITH DAVE
 Michael added back G4[7-9]</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">035-035.9, 036.41-036.43, 036.6, 070.22-070.23, 070.32-070.33, 070.44, 070.54, 074.2, 074.21-074.23, 102-103.9, 133-133.6, 135-135.9, 136.6, 140-148.9, 150-158.9, 160-164.9, 170-175.9, 180-183.8, 184.0-184.4, 184.8, 185-186.9, 187.1-187.8, 188-188.9, 189.0-189.8, 190-194.8, 200-208.92, 209.0-209.17, 209.21-209.27, 209.31-209.57, 209.61, 209.63-209.67, 210.0-210.9, 211.0-211.8, 212.0-212.8, 213-213.9, 217-220.9, 221.0-221.8, 222.0-222.8, 223.0-223.89, 224-228.9, 229.0, 229.8, 230.1-230.8, 231.0-231.2, 232-232.9, 233.0-233.2, 233.31-233.32, 233.4-233.5, 233.7, 234.0-234.8, 235.0, 235.4, 235.6-235.8, 236.0-236.2, 236.4-236.5, 236.7, 236.91-237.3, 237.5-237.9,
-238.0-238.5, 239.2-239.4, 239.6, 240-243.9, 244.0-244.1, 244.3-244.8, 245-
-246.9, 250-259.9, 270-273.9, 275-276, 277-277.2, 277.4-277.9, 278.0-278.8, 282-284.9, 286-286.5, 286.7-289.7, 290-292.9, 294.1-295.95, 303-303.93, 304.0-304.83, 305-305.93, 307.1, 307.51, 307.54, 327.2-327.8, 330-331.2, 331.5-337.9, 340-341.9, 345-345.91, 349-349.8, 353.6-353.9, 356-356.9, 357.0-357.7, 358-359.9, 376.0-376.1, 391-391.9, 392.0, 393-398.99, 402-404.93, 410-414.9, 416.1, 417-417.9, 420-423, 423.1-425.9, 427-427.32, 427.6-427.89, 429.0-429.1, 430-435.9, 437.0-437.2, 437.4-437.8, 441-443.9, 446-457.9, 459, 459.1-459.39, 470, 470.9-474.9, 476-476.1, 477-479, 490-504.9, 506-506.9, 508-509, 515, 516-517.8, 518.6-518.7, 518.9, 519.0-519.4, 530-536.1, 536.4-536.49, 537-537.6, 537.8-537.84, 538-543.9, 550-553.6, 555-558.9, 560-560.39, 560.8-560.9, 562-562.13, 564-564.7, 565-566.9, 569.0-569.44, 569.5-569.71, 569.84-569.85, 571-571.9, 572.3-572.9, 573.0-573.4, 573.8-577.9, 579-583.9, 585-585.9, 588-590.9, 592-593.89, 594-599.69, 599.8-599.89, 601-602.9, 604-604.99, 608.2-608.24, 610-610.9, 617-618.9, 620-620.9, 621.4-621.9, 622.3-622.7, 629-629.81, 680-689, 694-695.59, 707-707.9, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>710-711.99, 714-714.33, 714.8-714.9, 728.86, 728.88, 730.1-730.19, 732-732.9, 733.0-733.19, 740-749.04, 749.2-758.9, 759.0-759.89, 760.7-760.79, 775.0-775.3, 779.4-779.5, 780.57, 780.59, 780.62-780.63, 786.03, 787.1, 788.0, 790.2-790.22, 790.3, 798-798.0, E850-E850.29, E850.9-E854.39, E860-E860.19</t>
-    </r>
   </si>
   <si>
     <r>
@@ -4147,31 +4132,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>c</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>E800-E800.3, E801-E801.3, E802-E802.3, E803-E803.3, E804-E804.3, E805-E805.3, E806-E806.3, E807-E807.3, E810.0-E810.7, E811.0-E811.7, E812.0-E812.7, E813.0-E813.7, E814.0-E814.7, E815.0-E815.7, E816.0-E816.7, E817.0-E817.7, E818.0-E818.7, E819.0-E819.7, E820.0-E820.7, E821.0-E821.7,
-E822.0-E822.7, E823.0-E823.7, E824.0-E824.7, E825.0-E825.7, E826.0-E826.4, E827.0-E827.4, E828.0-E828.4, E829.0-E829.4, E830-E838.9, E840-E849.9, E850.3-E850.89, E854.8, E856-E857.09, E860.2-E869.99,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> E870-E876.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, E878-E879.9, E880-E886.99, E888-E928.89, E929.1-E929.5, E930-E979.9, E990-E999.1</t>
     </r>
   </si>
   <si>
@@ -4376,106 +4336,150 @@
     <t>Y355,  Y36, Y891, Y38, y899</t>
   </si>
   <si>
-    <t xml:space="preserve">Added Y891 (sequelae of war operations) per IHME, move Y890 (officer-involved killings) to homicides rather than here per CDPH
+    <t>Y355|Y36|Y37|Y891|Y38</t>
+  </si>
+  <si>
+    <t>U01[0-9]|U02|X8[5-9]|X9|Y0|Y871</t>
+  </si>
+  <si>
+    <t>Y35[0-4]|Y35[6-9]|Y890</t>
+  </si>
+  <si>
+    <t>Execution, War, Terroism</t>
+  </si>
+  <si>
+    <t>W32-W34.9</t>
+  </si>
+  <si>
+    <t>W3[2-4]</t>
+  </si>
+  <si>
+    <t>Accidental Firearm</t>
+  </si>
+  <si>
+    <t>Moved W3[2-4] here from line above.</t>
+  </si>
+  <si>
+    <t>W20-W38, W40-W43, W45, W46, W49-W52, W75, W76
+not W3[2-4]</t>
+  </si>
+  <si>
+    <t>6. Accidental Firearm</t>
+  </si>
+  <si>
+    <t>W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[5-6]</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>Substance Use - associated poisonings</t>
+  </si>
+  <si>
+    <t>2. Non-SA Poisonings</t>
+  </si>
+  <si>
+    <t>X42|X44</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> X42, X44</t>
+  </si>
+  <si>
+    <t>DELETED X42 and X44 per CDPH review (1/9/2019) - to Substance Use - associated poisonings;</t>
+  </si>
+  <si>
+    <t>F13, F16, F18, F19, P044</t>
+  </si>
+  <si>
+    <t>F1[3,6,8,9]|P044</t>
+  </si>
+  <si>
+    <t>X4[0,1,3,6-9]</t>
+  </si>
+  <si>
+    <t>X40, X41, X43, X46-X49</t>
+  </si>
+  <si>
+    <t>E.2. Substance use disorders</t>
+  </si>
+  <si>
+    <t>Substance use disorders</t>
+  </si>
+  <si>
+    <t>Substance use-associated poisonings</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">035-035.9, 036.41-036.43, 036.6, 070.22-070.23, 070.32-070.33, 070.44, 070.54, 074.2, 074.21-074.23, 102-103.9, 133-133.6, 135-135.9, 136.6, 140-148.9, 150-158.9, 160-164.9, 170-175.9, 180-183.8, 184.0-184.4, 184.8, 185-186.9, 187.1-187.8, 188-188.9, 189.0-189.8, 190-194.8, 200-208.92, 209.0-209.17, 209.21-209.27, 209.31-209.57, 209.61, 209.63-209.67, 210.0-210.9, 211.0-211.8, 212.0-212.8, 213-213.9, 217-220.9, 221.0-221.8, 222.0-222.8, 223.0-223.89, 224-228.9, 229.0, 229.8, 230.1-230.8, 231.0-231.2, 232-232.9, 233.0-233.2, 233.31-233.32, 233.4-233.5, 233.7, 234.0-234.8, 235.0, 235.4, 235.6-235.8, 236.0-236.2, 236.4-236.5, 236.7, 236.91-237.3, 237.5-237.9,
+238.0-238.5, 239.2-239.4, 239.6, 240-243.9, 244.0-244.1, 244.3-244.8, 245-
+246.9, 250-259.9, 270-273.9, 275-276, 277-277.2, 277.4-277.9, 278.0-278.8, 282-284.9, 286-286.5, 286.7-289.7, 290-292.9, 294.1-295.95, 303-303.93, 304.0-304.83, 305-305.93, 307.1, 307.51, 307.54, 327.2-327.8, 330-331.2, 331.5-337.9, 340-341.9, 345-345.91, 349-349.8, 353.6-353.9, 356-356.9, 357.0-357.7, 358-359.9, 376.0-376.1, 391-391.9, 392.0, 393-398.99, 402-404.93, 410-414.9, 416.1, 417-417.9, 420-423, 423.1-425.9, 427-427.32, 427.6-427.89, 429.0-429.1, 430-435.9, 437.0-437.2, 437.4-437.8, 441-443.9, 446-457.9, 459, 459.1-459.39, 470, 470.9-474.9, 476-476.1, 477-479, 490-504.9, 506-506.9, 508-509, 515, 516-517.8, 518.6-518.7, 518.9, 519.0-519.4, 530-536.1, 536.4-536.49, 537-537.6, 537.8-537.84, 538-543.9, 550-553.6, 555-558.9, 560-560.39, 560.8-560.9, 562-562.13, 564-564.7, 565-566.9, 569.0-569.44, 569.5-569.71, 569.84-569.85, 571-571.9, 572.3-572.9, 573.0-573.4, 573.8-577.9, 579-583.9, 585-585.9, 588-590.9, 592-593.89, 594-599.69, 599.8-599.89, 601-602.9, 604-604.99, 608.2-608.24, 610-610.9, 617-618.9, 620-620.9, 621.4-621.9, 622.3-622.7, 629-629.81, 680-689, 694-695.59, 707-707.9, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>710-711.99, 714-714.33, 714.8-714.9, 728.86, 728.88, 730.1-730.19, 732-732.9, 733.0-733.19, 740-749.04, 749.2-758.9, 759.0-759.89, 760.7-760.79, 775.0-775.3, 779.4-779.5, 780.57, 780.59, 780.62-780.63, 786.03, 787.1, 788.0, 790.2-790.22, 790.3, 798-798.0, E850-E850.29, E850.9-E854.39, E860-E860.19</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>E800-E800.3, E801-E801.3, E802-E802.3, E803-E803.3, E804-E804.3, E805-E805.3, E806-E806.3, E807-E807.3, E810.0-E810.7, E811.0-E811.7, E812.0-E812.7, E813.0-E813.7, E814.0-E814.7, E815.0-E815.7, E816.0-E816.7, E817.0-E817.7, E818.0-E818.7, E819.0-E819.7, E820.0-E820.7, E821.0-E821.7,
+E822.0-E822.7, E823.0-E823.7, E824.0-E824.7, E825.0-E825.7, E826.0-E826.4, E827.0-E827.4, E828.0-E828.4, E829.0-E829.4, E830-E838.9, E840-E849.9, E850.3-E850.89, E854.8, E856-E857.09, E860.2-E869.99,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> E870-E876.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, E878-E879.9, E880-E886.99, E888-E928.89, E929.1-E929.5, E930-E979.9, E990-E999.1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Added and U010-U019, U02 (terrorism) </t>
+  </si>
+  <si>
+    <t>Y350-4, 356-7, 890 (officer-involved shootings etc. from war/legal interventions to homicides);   See 4oct2018 email regarding recommendation to add Y358-9 (other and unspecified officer-involved deaths)</t>
+  </si>
+  <si>
+    <t>Added Y891 (sequelae of war operations) per IHME, move Y890 (officer-involved killings) to homicides rather than here per CDPH
 Y35.5 - execution
 Y36, Y37, Y89.1 - war/military
-Y38 - terrorism
-</t>
-  </si>
-  <si>
-    <t>Y355|Y36|Y37|Y891|Y38</t>
-  </si>
-  <si>
-    <t>U01[0-9]|U02|X8[5-9]|X9|Y0|Y871</t>
-  </si>
-  <si>
-    <t>Y35[0-4]|Y35[6-9]|Y890</t>
-  </si>
-  <si>
-    <t>Execution, War, Terroism</t>
-  </si>
-  <si>
-    <t>Added Y350-4, 356-7, 890 (officer-involved shootings etc. from war/legal interventions to homicides) and U010-U019, U02 (terrorism) per CDPH. See 4oct2018 email regarding recommendation to Added Y358-9 (other and unspecified officer-involved deaths) to be consistent with CDPH-recommended for legal interventions. 
-exploring seperating "legal intervention" from other homicide
-removed "cE03" code from G
-for "210" row 223, TEMP change of E from 99 to 03, and make F c</t>
-  </si>
-  <si>
-    <t>W32-W34.9</t>
-  </si>
-  <si>
-    <t>W3[2-4]</t>
-  </si>
-  <si>
-    <t>Accidental Firearm</t>
-  </si>
-  <si>
-    <t>Moved W3[2-4] here from line above.</t>
-  </si>
-  <si>
-    <t>W20-W38, W40-W43, W45, W46, W49-W52, W75, W76
-not W3[2-4]</t>
-  </si>
-  <si>
-    <t>6. Accidental Firearm</t>
-  </si>
-  <si>
-    <t>W2|W3[0-1,5-8]|W4[0-3,5-6,9]|W5[0-2]|W7[5-6]</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>Substance Use - associated poisonings</t>
-  </si>
-  <si>
-    <t>2. Non-SA Poisonings</t>
-  </si>
-  <si>
-    <t>X42|X44</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> X42, X44</t>
-  </si>
-  <si>
-    <t>DELETED X42 and X44 per CDPH review (1/9/2019) - to Substance Use - associated poisonings;</t>
-  </si>
-  <si>
-    <t>Added P044  ; as above moved X41 to 2. Non-SA Poisonings</t>
-  </si>
-  <si>
-    <t>F13, F16, F18, F19, P044</t>
-  </si>
-  <si>
-    <t>F1[3,6,8,9]|P044</t>
-  </si>
-  <si>
-    <t>X4[0,1,3,6-9]</t>
-  </si>
-  <si>
-    <t>X40, X41, X43, X46-X49</t>
-  </si>
-  <si>
-    <t>E.2. Substance use disorders</t>
-  </si>
-  <si>
-    <t>Substance use disorders</t>
-  </si>
-  <si>
-    <t>Substance use-associated poisonings</t>
-  </si>
-  <si>
-    <t>Other poisonings</t>
+Y38 - terrorism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added S per Dave (see notes, consider renaming category).  Also per IHME,  added X30-32 and X39 from natural disasters.  </t>
+  </si>
+  <si>
+    <t>Added P044  ; as above moved X41 to Poisonings (non-substance)</t>
+  </si>
+  <si>
+    <t>Poisonings (non-substance use)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.;###0."/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4633,6 +4637,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="3"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -4787,7 +4804,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4962,20 +4979,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5003,9 +5008,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5041,6 +5043,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5131,7 +5151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5166,7 +5186,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5375,28 +5395,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X233"/>
+  <dimension ref="A1:X232"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57" style="44" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="46" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" style="44" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="46" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="44" customWidth="1"/>
     <col min="4" max="4" width="4.42578125" style="56" customWidth="1"/>
     <col min="5" max="5" width="3.7109375" style="55" customWidth="1"/>
     <col min="6" max="6" width="5.85546875" style="56" customWidth="1"/>
     <col min="7" max="7" width="8.28515625" style="56" customWidth="1"/>
     <col min="8" max="8" width="8" style="56" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="62.85546875" style="16" customWidth="1"/>
     <col min="10" max="10" width="10" style="48" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" style="16" customWidth="1"/>
-    <col min="12" max="12" width="33.42578125" style="16" customWidth="1"/>
+    <col min="11" max="11" width="37.28515625" style="16" customWidth="1"/>
+    <col min="12" max="12" width="38.140625" style="16" customWidth="1"/>
     <col min="13" max="13" width="27.5703125" style="16" customWidth="1"/>
     <col min="14" max="14" width="71.28515625" style="16" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" style="72" customWidth="1"/>
-    <col min="16" max="16" width="35.140625" style="72" customWidth="1"/>
-    <col min="17" max="17" width="38.42578125" style="73" customWidth="1"/>
-    <col min="18" max="18" width="62.140625" style="74" customWidth="1"/>
-    <col min="19" max="19" width="40.7109375" style="74" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="68" customWidth="1"/>
+    <col min="16" max="16" width="35.140625" style="68" customWidth="1"/>
+    <col min="17" max="17" width="38.42578125" style="69" customWidth="1"/>
+    <col min="18" max="18" width="62.140625" style="87" customWidth="1"/>
+    <col min="19" max="19" width="40.7109375" style="87" customWidth="1"/>
     <col min="20" max="20" width="50.85546875" style="48" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="50.85546875" style="48" customWidth="1"/>
     <col min="22" max="22" width="50.85546875" style="46" bestFit="1" customWidth="1"/>
@@ -5431,10 +5451,10 @@
         <v>1124</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>384</v>
@@ -5443,10 +5463,10 @@
         <v>759</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="O1" s="59" t="s">
         <v>1161</v>
@@ -5457,10 +5477,10 @@
       <c r="Q1" s="59" t="s">
         <v>1136</v>
       </c>
-      <c r="R1" s="61" t="s">
+      <c r="R1" s="82" t="s">
         <v>509</v>
       </c>
-      <c r="S1" s="61" t="s">
+      <c r="S1" s="82" t="s">
         <v>760</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -5479,7 +5499,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="str">
         <f>CONCATENATE(".",V2)</f>
         <v>.All CAUSES</v>
@@ -5509,8 +5529,8 @@
       <c r="O2" s="59"/>
       <c r="P2" s="59"/>
       <c r="Q2" s="59"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
       <c r="T2" s="1" t="s">
         <v>951</v>
       </c>
@@ -5525,7 +5545,7 @@
       </c>
       <c r="X2" s="6"/>
     </row>
-    <row r="3" spans="1:24" ht="153" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="41.25" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="str">
         <f>IF(H3&lt;&gt;"",IF(F3&lt;&gt;"",CONCATENATE("....",D3,".",E3,".",F3,". - ",T3),IF(E3&lt;&gt;"",CONCATENATE("...",D3,".",E3,". - ",T3),CONCATENATE("..",D3,". - ",T3))),"")</f>
         <v>..A. - Communicable, maternal, perinatal and nutritional conditions</v>
@@ -5559,10 +5579,10 @@
         <v>947</v>
       </c>
       <c r="Q3" s="59"/>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="83" t="s">
         <v>510</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="83" t="s">
         <v>670</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -5609,8 +5629,8 @@
       <c r="O4" s="59"/>
       <c r="P4" s="59"/>
       <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
       <c r="T4" s="20" t="s">
         <v>1129</v>
       </c>
@@ -5621,7 +5641,7 @@
       <c r="W4" s="45"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="1:24" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -5652,10 +5672,10 @@
         <v>320</v>
       </c>
       <c r="Q5" s="59"/>
-      <c r="R5" s="59" t="s">
+      <c r="R5" s="83" t="s">
         <v>671</v>
       </c>
-      <c r="S5" s="62" t="s">
+      <c r="S5" s="84" t="s">
         <v>672</v>
       </c>
       <c r="T5" s="2" t="s">
@@ -5709,14 +5729,14 @@
       <c r="O6" s="59" t="s">
         <v>387</v>
       </c>
-      <c r="P6" s="63" t="s">
+      <c r="P6" s="60" t="s">
         <v>321</v>
       </c>
-      <c r="Q6" s="63"/>
-      <c r="R6" s="59" t="s">
+      <c r="Q6" s="60"/>
+      <c r="R6" s="83" t="s">
         <v>511</v>
       </c>
-      <c r="S6" s="59" t="s">
+      <c r="S6" s="83" t="s">
         <v>1111</v>
       </c>
       <c r="T6" s="5" t="s">
@@ -5763,8 +5783,8 @@
       <c r="O7" s="59"/>
       <c r="P7" s="59"/>
       <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
       <c r="T7" s="2" t="s">
         <v>1155</v>
       </c>
@@ -5819,10 +5839,10 @@
         <v>322</v>
       </c>
       <c r="Q8" s="59"/>
-      <c r="R8" s="59" t="s">
+      <c r="R8" s="83" t="s">
         <v>512</v>
       </c>
-      <c r="S8" s="59" t="s">
+      <c r="S8" s="83" t="s">
         <v>1048</v>
       </c>
       <c r="T8" s="2" t="s">
@@ -5875,14 +5895,14 @@
       <c r="O9" s="59" t="s">
         <v>389</v>
       </c>
-      <c r="P9" s="63" t="s">
+      <c r="P9" s="60" t="s">
         <v>323</v>
       </c>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="59" t="s">
+      <c r="Q9" s="60"/>
+      <c r="R9" s="83" t="s">
         <v>513</v>
       </c>
-      <c r="S9" s="59" t="s">
+      <c r="S9" s="83" t="s">
         <v>1049</v>
       </c>
       <c r="T9" s="5" t="s">
@@ -5935,14 +5955,14 @@
       <c r="O10" s="59" t="s">
         <v>390</v>
       </c>
-      <c r="P10" s="63" t="s">
+      <c r="P10" s="60" t="s">
         <v>324</v>
       </c>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="59" t="s">
+      <c r="Q10" s="60"/>
+      <c r="R10" s="83" t="s">
         <v>514</v>
       </c>
-      <c r="S10" s="62" t="s">
+      <c r="S10" s="84" t="s">
         <v>1058</v>
       </c>
       <c r="T10" s="5" t="s">
@@ -5995,14 +6015,14 @@
       <c r="O11" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="P11" s="63" t="s">
+      <c r="P11" s="60" t="s">
         <v>325</v>
       </c>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="59" t="s">
+      <c r="Q11" s="60"/>
+      <c r="R11" s="83" t="s">
         <v>515</v>
       </c>
-      <c r="S11" s="59" t="s">
+      <c r="S11" s="83" t="s">
         <v>1047</v>
       </c>
       <c r="T11" s="5" t="s">
@@ -6055,12 +6075,12 @@
       <c r="O12" s="59" t="s">
         <v>326</v>
       </c>
-      <c r="P12" s="63" t="s">
+      <c r="P12" s="60" t="s">
         <v>326</v>
       </c>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="59"/>
-      <c r="S12" s="59"/>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="83"/>
+      <c r="S12" s="83"/>
       <c r="T12" s="5" t="s">
         <v>150</v>
       </c>
@@ -6077,7 +6097,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6113,14 +6133,14 @@
       <c r="O13" s="59" t="s">
         <v>391</v>
       </c>
-      <c r="P13" s="63" t="s">
+      <c r="P13" s="60" t="s">
         <v>327</v>
       </c>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="59" t="s">
+      <c r="Q13" s="60"/>
+      <c r="R13" s="83" t="s">
         <v>517</v>
       </c>
-      <c r="S13" s="59" t="s">
+      <c r="S13" s="83" t="s">
         <v>1046</v>
       </c>
       <c r="T13" s="5" t="s">
@@ -6175,14 +6195,14 @@
       <c r="O14" s="59" t="s">
         <v>392</v>
       </c>
-      <c r="P14" s="63" t="s">
+      <c r="P14" s="60" t="s">
         <v>328</v>
       </c>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="59" t="s">
+      <c r="Q14" s="60"/>
+      <c r="R14" s="83" t="s">
         <v>518</v>
       </c>
-      <c r="S14" s="59" t="s">
+      <c r="S14" s="83" t="s">
         <v>1013</v>
       </c>
       <c r="T14" s="5" t="s">
@@ -6235,12 +6255,12 @@
       <c r="O15" s="59" t="s">
         <v>393</v>
       </c>
-      <c r="P15" s="63" t="s">
+      <c r="P15" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="Q15" s="63"/>
-      <c r="R15" s="59"/>
-      <c r="S15" s="59"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="83"/>
       <c r="T15" s="5" t="s">
         <v>153</v>
       </c>
@@ -6291,14 +6311,14 @@
       <c r="O16" s="59" t="s">
         <v>960</v>
       </c>
-      <c r="P16" s="63" t="s">
+      <c r="P16" s="60" t="s">
         <v>330</v>
       </c>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="59" t="s">
+      <c r="Q16" s="60"/>
+      <c r="R16" s="83" t="s">
         <v>519</v>
       </c>
-      <c r="S16" s="59" t="s">
+      <c r="S16" s="83" t="s">
         <v>1013</v>
       </c>
       <c r="T16" s="5" t="s">
@@ -6349,14 +6369,14 @@
       <c r="O17" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="P17" s="63" t="s">
+      <c r="P17" s="60" t="s">
         <v>331</v>
       </c>
-      <c r="Q17" s="63"/>
-      <c r="R17" s="59" t="s">
+      <c r="Q17" s="60"/>
+      <c r="R17" s="83" t="s">
         <v>520</v>
       </c>
-      <c r="S17" s="59" t="s">
+      <c r="S17" s="83" t="s">
         <v>1059</v>
       </c>
       <c r="T17" s="5" t="s">
@@ -6410,8 +6430,8 @@
         <v>332</v>
       </c>
       <c r="Q18" s="59"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
+      <c r="R18" s="83"/>
+      <c r="S18" s="83"/>
       <c r="T18" s="2" t="s">
         <v>156</v>
       </c>
@@ -6459,14 +6479,14 @@
       <c r="O19" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="P19" s="63" t="s">
+      <c r="P19" s="60" t="s">
         <v>333</v>
       </c>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="59" t="s">
+      <c r="Q19" s="60"/>
+      <c r="R19" s="83" t="s">
         <v>521</v>
       </c>
-      <c r="S19" s="59" t="s">
+      <c r="S19" s="83" t="s">
         <v>1060</v>
       </c>
       <c r="T19" s="5" t="s">
@@ -6517,14 +6537,14 @@
       <c r="O20" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="P20" s="63" t="s">
+      <c r="P20" s="60" t="s">
         <v>334</v>
       </c>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="59" t="s">
+      <c r="Q20" s="60"/>
+      <c r="R20" s="83" t="s">
         <v>522</v>
       </c>
-      <c r="S20" s="59" t="s">
+      <c r="S20" s="83" t="s">
         <v>1044</v>
       </c>
       <c r="T20" s="5" t="s">
@@ -6575,14 +6595,14 @@
       <c r="O21" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="P21" s="63" t="s">
+      <c r="P21" s="60" t="s">
         <v>335</v>
       </c>
-      <c r="Q21" s="63"/>
-      <c r="R21" s="59" t="s">
+      <c r="Q21" s="60"/>
+      <c r="R21" s="83" t="s">
         <v>523</v>
       </c>
-      <c r="S21" s="59" t="s">
+      <c r="S21" s="83" t="s">
         <v>1045</v>
       </c>
       <c r="T21" s="5" t="s">
@@ -6633,14 +6653,14 @@
       <c r="O22" s="59" t="s">
         <v>396</v>
       </c>
-      <c r="P22" s="63" t="s">
+      <c r="P22" s="60" t="s">
         <v>336</v>
       </c>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="59" t="s">
+      <c r="Q22" s="60"/>
+      <c r="R22" s="83" t="s">
         <v>524</v>
       </c>
-      <c r="S22" s="59" t="s">
+      <c r="S22" s="83" t="s">
         <v>1043</v>
       </c>
       <c r="T22" s="5" t="s">
@@ -6694,14 +6714,14 @@
       <c r="O23" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="P23" s="63" t="s">
+      <c r="P23" s="60" t="s">
         <v>337</v>
       </c>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="59" t="s">
+      <c r="Q23" s="60"/>
+      <c r="R23" s="83" t="s">
         <v>525</v>
       </c>
-      <c r="S23" s="59" t="s">
+      <c r="S23" s="83" t="s">
         <v>1112</v>
       </c>
       <c r="T23" s="5" t="s">
@@ -6755,14 +6775,14 @@
       <c r="O24" s="59" t="s">
         <v>398</v>
       </c>
-      <c r="P24" s="63" t="s">
+      <c r="P24" s="60" t="s">
         <v>338</v>
       </c>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="59" t="s">
+      <c r="Q24" s="60"/>
+      <c r="R24" s="83" t="s">
         <v>526</v>
       </c>
-      <c r="S24" s="59" t="s">
+      <c r="S24" s="83" t="s">
         <v>1061</v>
       </c>
       <c r="T24" s="5" t="s">
@@ -6813,12 +6833,12 @@
       <c r="O25" s="59" t="s">
         <v>961</v>
       </c>
-      <c r="P25" s="63" t="s">
+      <c r="P25" s="60" t="s">
         <v>339</v>
       </c>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="59"/>
-      <c r="S25" s="59"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="83"/>
       <c r="T25" s="5" t="s">
         <v>163</v>
       </c>
@@ -6867,12 +6887,12 @@
       <c r="O26" s="59" t="s">
         <v>340</v>
       </c>
-      <c r="P26" s="63" t="s">
+      <c r="P26" s="60" t="s">
         <v>340</v>
       </c>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="59"/>
-      <c r="S26" s="59"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="83"/>
+      <c r="S26" s="83"/>
       <c r="T26" s="5" t="s">
         <v>164</v>
       </c>
@@ -6887,7 +6907,7 @@
       </c>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.06.a. - Acute hepatitis B</v>
@@ -6926,12 +6946,12 @@
       <c r="O27" s="59" t="s">
         <v>962</v>
       </c>
-      <c r="P27" s="63" t="s">
+      <c r="P27" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="Q27" s="63"/>
-      <c r="R27" s="59"/>
-      <c r="S27" s="59"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="83"/>
+      <c r="S27" s="83"/>
       <c r="T27" s="5" t="s">
         <v>165</v>
       </c>
@@ -6964,10 +6984,10 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="O28" s="59"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
       <c r="T28" s="5"/>
       <c r="U28" s="20"/>
       <c r="V28" s="5"/>
@@ -7013,12 +7033,12 @@
       <c r="O29" s="59" t="s">
         <v>963</v>
       </c>
-      <c r="P29" s="63" t="s">
+      <c r="P29" s="60" t="s">
         <v>342</v>
       </c>
-      <c r="Q29" s="63"/>
-      <c r="R29" s="59"/>
-      <c r="S29" s="59"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="83"/>
+      <c r="S29" s="83"/>
       <c r="T29" s="5" t="s">
         <v>166</v>
       </c>
@@ -7067,12 +7087,12 @@
       <c r="O30" s="59" t="s">
         <v>964</v>
       </c>
-      <c r="P30" s="63" t="s">
+      <c r="P30" s="60" t="s">
         <v>343</v>
       </c>
-      <c r="Q30" s="63"/>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="83"/>
+      <c r="S30" s="83"/>
       <c r="T30" s="5" t="s">
         <v>167</v>
       </c>
@@ -7122,8 +7142,8 @@
         <v>344</v>
       </c>
       <c r="Q31" s="59"/>
-      <c r="R31" s="59"/>
-      <c r="S31" s="59"/>
+      <c r="R31" s="83"/>
+      <c r="S31" s="83"/>
       <c r="T31" s="2" t="s">
         <v>168</v>
       </c>
@@ -7172,14 +7192,14 @@
       <c r="O32" s="59" t="s">
         <v>400</v>
       </c>
-      <c r="P32" s="63" t="s">
+      <c r="P32" s="60" t="s">
         <v>345</v>
       </c>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="59" t="s">
+      <c r="Q32" s="60"/>
+      <c r="R32" s="83" t="s">
         <v>527</v>
       </c>
-      <c r="S32" s="59" t="s">
+      <c r="S32" s="83" t="s">
         <v>1042</v>
       </c>
       <c r="T32" s="5" t="s">
@@ -7230,14 +7250,14 @@
       <c r="O33" s="59" t="s">
         <v>346</v>
       </c>
-      <c r="P33" s="63" t="s">
+      <c r="P33" s="60" t="s">
         <v>346</v>
       </c>
-      <c r="Q33" s="63"/>
-      <c r="R33" s="59" t="s">
+      <c r="Q33" s="60"/>
+      <c r="R33" s="83" t="s">
         <v>528</v>
       </c>
-      <c r="S33" s="59" t="s">
+      <c r="S33" s="83" t="s">
         <v>1041</v>
       </c>
       <c r="T33" s="5" t="s">
@@ -7288,14 +7308,14 @@
       <c r="O34" s="59" t="s">
         <v>347</v>
       </c>
-      <c r="P34" s="63" t="s">
+      <c r="P34" s="60" t="s">
         <v>347</v>
       </c>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="59" t="s">
+      <c r="Q34" s="60"/>
+      <c r="R34" s="83" t="s">
         <v>529</v>
       </c>
-      <c r="S34" s="59" t="s">
+      <c r="S34" s="83" t="s">
         <v>1040</v>
       </c>
       <c r="T34" s="5" t="s">
@@ -7346,14 +7366,14 @@
       <c r="O35" s="59" t="s">
         <v>348</v>
       </c>
-      <c r="P35" s="63" t="s">
+      <c r="P35" s="60" t="s">
         <v>348</v>
       </c>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="59" t="s">
+      <c r="Q35" s="60"/>
+      <c r="R35" s="83" t="s">
         <v>530</v>
       </c>
-      <c r="S35" s="59" t="s">
+      <c r="S35" s="83" t="s">
         <v>1050</v>
       </c>
       <c r="T35" s="5" t="s">
@@ -7404,14 +7424,14 @@
       <c r="O36" s="59" t="s">
         <v>349</v>
       </c>
-      <c r="P36" s="63" t="s">
+      <c r="P36" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="64" t="s">
+      <c r="Q36" s="60"/>
+      <c r="R36" s="85" t="s">
         <v>1039</v>
       </c>
-      <c r="S36" s="64" t="s">
+      <c r="S36" s="85" t="s">
         <v>1039</v>
       </c>
       <c r="T36" s="5" t="s">
@@ -7462,12 +7482,12 @@
       <c r="O37" s="59" t="s">
         <v>401</v>
       </c>
-      <c r="P37" s="63" t="s">
+      <c r="P37" s="60" t="s">
         <v>350</v>
       </c>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="83"/>
+      <c r="S37" s="83"/>
       <c r="T37" s="5" t="s">
         <v>174</v>
       </c>
@@ -7516,12 +7536,12 @@
       <c r="O38" s="59" t="s">
         <v>351</v>
       </c>
-      <c r="P38" s="63" t="s">
+      <c r="P38" s="60" t="s">
         <v>351</v>
       </c>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="59"/>
-      <c r="S38" s="59"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="83"/>
+      <c r="S38" s="83"/>
       <c r="T38" s="5" t="s">
         <v>175</v>
       </c>
@@ -7570,14 +7590,14 @@
       <c r="O39" s="59" t="s">
         <v>352</v>
       </c>
-      <c r="P39" s="63" t="s">
+      <c r="P39" s="60" t="s">
         <v>352</v>
       </c>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="64">
+      <c r="Q39" s="60"/>
+      <c r="R39" s="85">
         <v>123.1</v>
       </c>
-      <c r="S39" s="64">
+      <c r="S39" s="85">
         <v>1231</v>
       </c>
       <c r="T39" s="5" t="s">
@@ -7628,14 +7648,14 @@
       <c r="O40" s="59" t="s">
         <v>353</v>
       </c>
-      <c r="P40" s="63" t="s">
+      <c r="P40" s="60" t="s">
         <v>353</v>
       </c>
-      <c r="Q40" s="63"/>
-      <c r="R40" s="59" t="s">
+      <c r="Q40" s="60"/>
+      <c r="R40" s="83" t="s">
         <v>531</v>
       </c>
-      <c r="S40" s="59" t="s">
+      <c r="S40" s="83" t="s">
         <v>1035</v>
       </c>
       <c r="T40" s="5" t="s">
@@ -7686,12 +7706,12 @@
       <c r="O41" s="59" t="s">
         <v>757</v>
       </c>
-      <c r="P41" s="63" t="s">
+      <c r="P41" s="60" t="s">
         <v>757</v>
       </c>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="59"/>
-      <c r="S41" s="59"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="83"/>
+      <c r="S41" s="83"/>
       <c r="T41" s="5" t="s">
         <v>758</v>
       </c>
@@ -7740,14 +7760,14 @@
       <c r="O42" s="59" t="s">
         <v>402</v>
       </c>
-      <c r="P42" s="63" t="s">
+      <c r="P42" s="60" t="s">
         <v>354</v>
       </c>
-      <c r="Q42" s="63"/>
-      <c r="R42" s="59" t="s">
+      <c r="Q42" s="60"/>
+      <c r="R42" s="83" t="s">
         <v>532</v>
       </c>
-      <c r="S42" s="59" t="s">
+      <c r="S42" s="83" t="s">
         <v>1038</v>
       </c>
       <c r="T42" s="5" t="s">
@@ -7798,12 +7818,12 @@
       <c r="O43" s="59" t="s">
         <v>355</v>
       </c>
-      <c r="P43" s="63" t="s">
+      <c r="P43" s="60" t="s">
         <v>355</v>
       </c>
-      <c r="Q43" s="63"/>
-      <c r="R43" s="59"/>
-      <c r="S43" s="59"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="83"/>
+      <c r="S43" s="83"/>
       <c r="T43" s="5" t="s">
         <v>179</v>
       </c>
@@ -7852,14 +7872,14 @@
       <c r="O44" s="59" t="s">
         <v>356</v>
       </c>
-      <c r="P44" s="63" t="s">
+      <c r="P44" s="60" t="s">
         <v>356</v>
       </c>
-      <c r="Q44" s="63"/>
-      <c r="R44" s="59" t="s">
+      <c r="Q44" s="60"/>
+      <c r="R44" s="83" t="s">
         <v>533</v>
       </c>
-      <c r="S44" s="59" t="s">
+      <c r="S44" s="83" t="s">
         <v>1037</v>
       </c>
       <c r="T44" s="5" t="s">
@@ -7910,14 +7930,14 @@
       <c r="O45" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="P45" s="63" t="s">
+      <c r="P45" s="60" t="s">
         <v>357</v>
       </c>
-      <c r="Q45" s="63"/>
-      <c r="R45" s="59" t="s">
+      <c r="Q45" s="60"/>
+      <c r="R45" s="83" t="s">
         <v>534</v>
       </c>
-      <c r="S45" s="59" t="s">
+      <c r="S45" s="83" t="s">
         <v>1036</v>
       </c>
       <c r="T45" s="5" t="s">
@@ -7969,10 +7989,10 @@
         <v>1120</v>
       </c>
       <c r="Q46" s="59"/>
-      <c r="R46" s="64">
+      <c r="R46" s="85">
         <v>127</v>
       </c>
-      <c r="S46" s="64">
+      <c r="S46" s="85">
         <v>127</v>
       </c>
       <c r="T46" s="2" t="s">
@@ -8023,14 +8043,14 @@
       <c r="O47" s="59" t="s">
         <v>358</v>
       </c>
-      <c r="P47" s="63" t="s">
+      <c r="P47" s="60" t="s">
         <v>358</v>
       </c>
-      <c r="Q47" s="63"/>
-      <c r="R47" s="64">
+      <c r="Q47" s="60"/>
+      <c r="R47" s="85">
         <v>127</v>
       </c>
-      <c r="S47" s="64">
+      <c r="S47" s="85">
         <v>127</v>
       </c>
       <c r="T47" s="5" t="s">
@@ -8081,12 +8101,12 @@
       <c r="O48" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="P48" s="63" t="s">
+      <c r="P48" s="60" t="s">
         <v>359</v>
       </c>
-      <c r="Q48" s="63"/>
-      <c r="R48" s="59"/>
-      <c r="S48" s="59"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="83"/>
+      <c r="S48" s="83"/>
       <c r="T48" s="5" t="s">
         <v>184</v>
       </c>
@@ -8135,12 +8155,12 @@
       <c r="O49" s="59" t="s">
         <v>360</v>
       </c>
-      <c r="P49" s="63" t="s">
+      <c r="P49" s="60" t="s">
         <v>360</v>
       </c>
-      <c r="Q49" s="63"/>
-      <c r="R49" s="59"/>
-      <c r="S49" s="59"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="83"/>
+      <c r="S49" s="83"/>
       <c r="T49" s="5" t="s">
         <v>185</v>
       </c>
@@ -8189,12 +8209,12 @@
       <c r="O50" s="59" t="s">
         <v>949</v>
       </c>
-      <c r="P50" s="63" t="s">
+      <c r="P50" s="60" t="s">
         <v>361</v>
       </c>
-      <c r="Q50" s="63"/>
-      <c r="R50" s="59"/>
-      <c r="S50" s="59"/>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="83"/>
+      <c r="S50" s="83"/>
       <c r="T50" s="5" t="s">
         <v>186</v>
       </c>
@@ -8209,7 +8229,7 @@
       </c>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8233,7 +8253,7 @@
       </c>
       <c r="H51" s="40"/>
       <c r="I51" s="5" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>1232</v>
@@ -8249,14 +8269,14 @@
       <c r="O51" s="59" t="s">
         <v>965</v>
       </c>
-      <c r="P51" s="63" t="s">
+      <c r="P51" s="60" t="s">
         <v>362</v>
       </c>
-      <c r="Q51" s="63"/>
-      <c r="R51" s="59" t="s">
+      <c r="Q51" s="60"/>
+      <c r="R51" s="83" t="s">
         <v>535</v>
       </c>
-      <c r="S51" s="59" t="s">
+      <c r="S51" s="83" t="s">
         <v>1110</v>
       </c>
       <c r="T51" s="5" t="s">
@@ -8272,10 +8292,10 @@
         <v>880</v>
       </c>
       <c r="X51" s="5" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.07. - Respiratory infections</v>
@@ -8315,10 +8335,10 @@
         <v>363</v>
       </c>
       <c r="Q52" s="59"/>
-      <c r="R52" s="59" t="s">
+      <c r="R52" s="83" t="s">
         <v>536</v>
       </c>
-      <c r="S52" s="62" t="s">
+      <c r="S52" s="84" t="s">
         <v>673</v>
       </c>
       <c r="T52" s="2" t="s">
@@ -8368,26 +8388,26 @@
       <c r="K53" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="L53" s="80" t="s">
-        <v>1331</v>
-      </c>
-      <c r="M53" s="80" t="s">
-        <v>1357</v>
-      </c>
-      <c r="N53" s="80" t="s">
-        <v>1358</v>
+      <c r="L53" s="75" t="s">
+        <v>1328</v>
+      </c>
+      <c r="M53" s="75" t="s">
+        <v>1354</v>
+      </c>
+      <c r="N53" s="75" t="s">
+        <v>1355</v>
       </c>
       <c r="O53" s="59" t="s">
         <v>404</v>
       </c>
-      <c r="P53" s="63" t="s">
+      <c r="P53" s="60" t="s">
         <v>364</v>
       </c>
-      <c r="Q53" s="63"/>
-      <c r="R53" s="59" t="s">
+      <c r="Q53" s="60"/>
+      <c r="R53" s="83" t="s">
         <v>537</v>
       </c>
-      <c r="S53" s="59" t="s">
+      <c r="S53" s="83" t="s">
         <v>1109</v>
       </c>
       <c r="T53" s="5" t="s">
@@ -8449,14 +8469,14 @@
       <c r="O54" s="59" t="s">
         <v>405</v>
       </c>
-      <c r="P54" s="63" t="s">
+      <c r="P54" s="60" t="s">
         <v>365</v>
       </c>
-      <c r="Q54" s="63"/>
-      <c r="R54" s="59" t="s">
+      <c r="Q54" s="60"/>
+      <c r="R54" s="83" t="s">
         <v>538</v>
       </c>
-      <c r="S54" s="59" t="s">
+      <c r="S54" s="83" t="s">
         <v>1108</v>
       </c>
       <c r="T54" s="5" t="s">
@@ -8513,14 +8533,14 @@
       <c r="O55" s="59" t="s">
         <v>406</v>
       </c>
-      <c r="P55" s="63" t="s">
+      <c r="P55" s="60" t="s">
         <v>366</v>
       </c>
-      <c r="Q55" s="63"/>
-      <c r="R55" s="59" t="s">
+      <c r="Q55" s="60"/>
+      <c r="R55" s="83" t="s">
         <v>539</v>
       </c>
-      <c r="S55" s="59" t="s">
+      <c r="S55" s="83" t="s">
         <v>1062</v>
       </c>
       <c r="T55" s="5" t="s">
@@ -8579,10 +8599,10 @@
         <v>367</v>
       </c>
       <c r="Q56" s="59"/>
-      <c r="R56" s="59" t="s">
+      <c r="R56" s="83" t="s">
         <v>540</v>
       </c>
-      <c r="S56" s="59" t="s">
+      <c r="S56" s="83" t="s">
         <v>674</v>
       </c>
       <c r="T56" s="2" t="s">
@@ -8625,28 +8645,28 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="M57" s="16" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="N57" s="16" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="O57" s="59" t="s">
         <v>408</v>
       </c>
-      <c r="P57" s="63" t="s">
+      <c r="P57" s="60" t="s">
         <v>368</v>
       </c>
-      <c r="Q57" s="63"/>
-      <c r="R57" s="59" t="s">
+      <c r="Q57" s="60"/>
+      <c r="R57" s="83" t="s">
         <v>541</v>
       </c>
-      <c r="S57" s="59" t="s">
+      <c r="S57" s="83" t="s">
         <v>1066</v>
       </c>
       <c r="T57" s="5" t="s">
@@ -8662,7 +8682,7 @@
         <v>33</v>
       </c>
       <c r="X57" s="5" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
@@ -8705,14 +8725,14 @@
       <c r="O58" s="59" t="s">
         <v>409</v>
       </c>
-      <c r="P58" s="63" t="s">
+      <c r="P58" s="60" t="s">
         <v>369</v>
       </c>
-      <c r="Q58" s="63"/>
-      <c r="R58" s="59" t="s">
+      <c r="Q58" s="60"/>
+      <c r="R58" s="83" t="s">
         <v>542</v>
       </c>
-      <c r="S58" s="59" t="s">
+      <c r="S58" s="83" t="s">
         <v>1064</v>
       </c>
       <c r="T58" s="5" t="s">
@@ -8761,7 +8781,7 @@
         <v>370</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="N59" s="16" t="s">
         <v>370</v>
@@ -8769,14 +8789,14 @@
       <c r="O59" s="59" t="s">
         <v>410</v>
       </c>
-      <c r="P59" s="63" t="s">
+      <c r="P59" s="60" t="s">
         <v>370</v>
       </c>
-      <c r="Q59" s="63"/>
-      <c r="R59" s="59" t="s">
+      <c r="Q59" s="60"/>
+      <c r="R59" s="83" t="s">
         <v>543</v>
       </c>
-      <c r="S59" s="64">
+      <c r="S59" s="85">
         <v>642</v>
       </c>
       <c r="T59" s="5" t="s">
@@ -8792,7 +8812,7 @@
         <v>35</v>
       </c>
       <c r="X59" s="5" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
@@ -8835,14 +8855,14 @@
       <c r="O60" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="P60" s="63" t="s">
+      <c r="P60" s="60" t="s">
         <v>371</v>
       </c>
-      <c r="Q60" s="63"/>
-      <c r="R60" s="59" t="s">
+      <c r="Q60" s="60"/>
+      <c r="R60" s="83" t="s">
         <v>544</v>
       </c>
-      <c r="S60" s="59" t="s">
+      <c r="S60" s="83" t="s">
         <v>1065</v>
       </c>
       <c r="T60" s="5" t="s">
@@ -8891,22 +8911,22 @@
         <v>372</v>
       </c>
       <c r="M61" s="16" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="N61" s="16" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="O61" s="59" t="s">
         <v>412</v>
       </c>
-      <c r="P61" s="63" t="s">
+      <c r="P61" s="60" t="s">
         <v>372</v>
       </c>
-      <c r="Q61" s="63"/>
-      <c r="R61" s="59" t="s">
+      <c r="Q61" s="60"/>
+      <c r="R61" s="83" t="s">
         <v>545</v>
       </c>
-      <c r="S61" s="59" t="s">
+      <c r="S61" s="83" t="s">
         <v>1063</v>
       </c>
       <c r="T61" s="5" t="s">
@@ -8955,22 +8975,22 @@
         <v>373</v>
       </c>
       <c r="M62" s="16" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="N62" s="16" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="O62" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="P62" s="63" t="s">
+      <c r="P62" s="60" t="s">
         <v>373</v>
       </c>
-      <c r="Q62" s="63"/>
-      <c r="R62" s="59" t="s">
+      <c r="Q62" s="60"/>
+      <c r="R62" s="83" t="s">
         <v>546</v>
       </c>
-      <c r="S62" s="59" t="s">
+      <c r="S62" s="83" t="s">
         <v>1107</v>
       </c>
       <c r="T62" s="5" t="s">
@@ -8987,7 +9007,7 @@
       </c>
       <c r="X62" s="2"/>
     </row>
-    <row r="63" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.09. - Neonatal conditions</v>
@@ -9029,10 +9049,10 @@
         <v>1118</v>
       </c>
       <c r="Q63" s="59"/>
-      <c r="R63" s="59" t="s">
+      <c r="R63" s="83" t="s">
         <v>548</v>
       </c>
-      <c r="S63" s="59" t="s">
+      <c r="S63" s="83" t="s">
         <v>547</v>
       </c>
       <c r="T63" s="2" t="s">
@@ -9083,14 +9103,14 @@
       <c r="O64" s="59" t="s">
         <v>415</v>
       </c>
-      <c r="P64" s="63" t="s">
+      <c r="P64" s="60" t="s">
         <v>374</v>
       </c>
-      <c r="Q64" s="63"/>
-      <c r="R64" s="59" t="s">
+      <c r="Q64" s="60"/>
+      <c r="R64" s="83" t="s">
         <v>549</v>
       </c>
-      <c r="S64" s="59" t="s">
+      <c r="S64" s="83" t="s">
         <v>1094</v>
       </c>
       <c r="T64" s="5" t="s">
@@ -9107,7 +9127,7 @@
       </c>
       <c r="X64" s="2"/>
     </row>
-    <row r="65" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9141,14 +9161,14 @@
       <c r="O65" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="P65" s="63" t="s">
+      <c r="P65" s="60" t="s">
         <v>375</v>
       </c>
-      <c r="Q65" s="63"/>
-      <c r="R65" s="59" t="s">
+      <c r="Q65" s="60"/>
+      <c r="R65" s="83" t="s">
         <v>550</v>
       </c>
-      <c r="S65" s="59" t="s">
+      <c r="S65" s="83" t="s">
         <v>1093</v>
       </c>
       <c r="T65" s="5" t="s">
@@ -9199,14 +9219,14 @@
       <c r="O66" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="P66" s="63" t="s">
+      <c r="P66" s="60" t="s">
         <v>1119</v>
       </c>
-      <c r="Q66" s="63"/>
-      <c r="R66" s="59" t="s">
+      <c r="Q66" s="60"/>
+      <c r="R66" s="83" t="s">
         <v>551</v>
       </c>
-      <c r="S66" s="59" t="s">
+      <c r="S66" s="83" t="s">
         <v>1034</v>
       </c>
       <c r="T66" s="5" t="s">
@@ -9223,7 +9243,7 @@
       </c>
       <c r="X66" s="2"/>
     </row>
-    <row r="67" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9247,7 +9267,7 @@
       </c>
       <c r="H67" s="40"/>
       <c r="I67" s="5" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>1160</v>
@@ -9263,14 +9283,14 @@
       <c r="O67" s="59" t="s">
         <v>418</v>
       </c>
-      <c r="P67" s="63" t="s">
+      <c r="P67" s="60" t="s">
         <v>376</v>
       </c>
-      <c r="Q67" s="63"/>
-      <c r="R67" s="59" t="s">
+      <c r="Q67" s="60"/>
+      <c r="R67" s="83" t="s">
         <v>552</v>
       </c>
-      <c r="S67" s="59" t="s">
+      <c r="S67" s="83" t="s">
         <v>1092</v>
       </c>
       <c r="T67" s="5" t="s">
@@ -9322,10 +9342,10 @@
         <v>377</v>
       </c>
       <c r="Q68" s="59"/>
-      <c r="R68" s="59" t="s">
+      <c r="R68" s="83" t="s">
         <v>553</v>
       </c>
-      <c r="S68" s="59" t="s">
+      <c r="S68" s="83" t="s">
         <v>675</v>
       </c>
       <c r="T68" s="2" t="s">
@@ -9376,14 +9396,14 @@
       <c r="O69" s="59" t="s">
         <v>420</v>
       </c>
-      <c r="P69" s="65" t="s">
+      <c r="P69" s="61" t="s">
         <v>378</v>
       </c>
-      <c r="Q69" s="63"/>
-      <c r="R69" s="59" t="s">
+      <c r="Q69" s="60"/>
+      <c r="R69" s="83" t="s">
         <v>554</v>
       </c>
-      <c r="S69" s="59" t="s">
+      <c r="S69" s="83" t="s">
         <v>1067</v>
       </c>
       <c r="T69" s="5" t="s">
@@ -9434,14 +9454,14 @@
       <c r="O70" s="59" t="s">
         <v>421</v>
       </c>
-      <c r="P70" s="63" t="s">
+      <c r="P70" s="60" t="s">
         <v>379</v>
       </c>
-      <c r="Q70" s="63"/>
-      <c r="R70" s="64">
+      <c r="Q70" s="60"/>
+      <c r="R70" s="85">
         <v>244.2</v>
       </c>
-      <c r="S70" s="64">
+      <c r="S70" s="85">
         <v>2442</v>
       </c>
       <c r="T70" s="5" t="s">
@@ -9492,12 +9512,12 @@
       <c r="O71" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="P71" s="63" t="s">
+      <c r="P71" s="60" t="s">
         <v>380</v>
       </c>
-      <c r="Q71" s="63"/>
-      <c r="R71" s="59"/>
-      <c r="S71" s="59"/>
+      <c r="Q71" s="60"/>
+      <c r="R71" s="83"/>
+      <c r="S71" s="83"/>
       <c r="T71" s="5" t="s">
         <v>207</v>
       </c>
@@ -9546,14 +9566,14 @@
       <c r="O72" s="59" t="s">
         <v>422</v>
       </c>
-      <c r="P72" s="63" t="s">
+      <c r="P72" s="60" t="s">
         <v>381</v>
       </c>
-      <c r="Q72" s="63"/>
-      <c r="R72" s="59" t="s">
+      <c r="Q72" s="60"/>
+      <c r="R72" s="83" t="s">
         <v>555</v>
       </c>
-      <c r="S72" s="59" t="s">
+      <c r="S72" s="83" t="s">
         <v>1033</v>
       </c>
       <c r="T72" s="5" t="s">
@@ -9604,14 +9624,14 @@
       <c r="O73" s="59" t="s">
         <v>423</v>
       </c>
-      <c r="P73" s="63" t="s">
+      <c r="P73" s="60" t="s">
         <v>382</v>
       </c>
-      <c r="Q73" s="63"/>
-      <c r="R73" s="59" t="s">
+      <c r="Q73" s="60"/>
+      <c r="R73" s="83" t="s">
         <v>556</v>
       </c>
-      <c r="S73" s="59" t="s">
+      <c r="S73" s="83" t="s">
         <v>1068</v>
       </c>
       <c r="T73" s="5" t="s">
@@ -9628,7 +9648,7 @@
       </c>
       <c r="X73" s="2"/>
     </row>
-    <row r="74" spans="1:24" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A74" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9661,10 +9681,10 @@
         <v>383</v>
       </c>
       <c r="Q74" s="59"/>
-      <c r="R74" s="60" t="s">
-        <v>1315</v>
-      </c>
-      <c r="S74" s="59" t="s">
+      <c r="R74" s="86" t="s">
+        <v>1395</v>
+      </c>
+      <c r="S74" s="83" t="s">
         <v>557</v>
       </c>
       <c r="T74" s="2" t="s">
@@ -9707,10 +9727,10 @@
       <c r="M75" s="19"/>
       <c r="N75" s="19"/>
       <c r="O75" s="59"/>
-      <c r="P75" s="66"/>
-      <c r="Q75" s="67"/>
-      <c r="R75" s="59"/>
-      <c r="S75" s="59"/>
+      <c r="P75" s="62"/>
+      <c r="Q75" s="63"/>
+      <c r="R75" s="83"/>
+      <c r="S75" s="83"/>
       <c r="T75" s="20" t="s">
         <v>1156</v>
       </c>
@@ -9719,7 +9739,7 @@
       </c>
       <c r="X75" s="2"/>
     </row>
-    <row r="76" spans="1:24" ht="57.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="44" t="str">
         <f t="shared" si="5"/>
         <v>..B. - Cancer/Malignant neoplasms</v>
@@ -9753,18 +9773,18 @@
       <c r="O76" s="59" t="s">
         <v>424</v>
       </c>
-      <c r="P76" s="66" t="s">
+      <c r="P76" s="62" t="s">
         <v>765</v>
       </c>
-      <c r="Q76" s="67"/>
-      <c r="R76" s="59" t="s">
+      <c r="Q76" s="63"/>
+      <c r="R76" s="83" t="s">
         <v>559</v>
       </c>
-      <c r="S76" s="59" t="s">
+      <c r="S76" s="83" t="s">
         <v>558</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="U76" s="20" t="s">
         <v>51</v>
@@ -9806,22 +9826,22 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="L77" s="49" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M77" s="49"/>
       <c r="N77" s="49"/>
       <c r="O77" s="59" t="s">
         <v>425</v>
       </c>
-      <c r="P77" s="68" t="s">
+      <c r="P77" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="Q77" s="69"/>
-      <c r="R77" s="59"/>
-      <c r="S77" s="59"/>
+      <c r="Q77" s="65"/>
+      <c r="R77" s="83"/>
+      <c r="S77" s="83"/>
       <c r="T77" s="5" t="s">
         <v>212</v>
       </c>
@@ -9836,7 +9856,7 @@
       </c>
       <c r="X77" s="2"/>
     </row>
-    <row r="78" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9860,30 +9880,30 @@
       </c>
       <c r="H78" s="40"/>
       <c r="I78" s="18" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J78" s="17" t="s">
         <v>1160</v>
       </c>
       <c r="K78" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L78" s="19" t="s">
         <v>1266</v>
-      </c>
-      <c r="L78" s="19" t="s">
-        <v>1267</v>
       </c>
       <c r="M78" s="19"/>
       <c r="N78" s="19"/>
       <c r="O78" s="59" t="s">
         <v>967</v>
       </c>
-      <c r="P78" s="68" t="s">
+      <c r="P78" s="64" t="s">
         <v>767</v>
       </c>
-      <c r="Q78" s="69"/>
-      <c r="R78" s="59" t="s">
+      <c r="Q78" s="65"/>
+      <c r="R78" s="83" t="s">
         <v>560</v>
       </c>
-      <c r="S78" s="59" t="s">
+      <c r="S78" s="83" t="s">
         <v>1086</v>
       </c>
       <c r="T78" s="5" t="s">
@@ -9924,7 +9944,7 @@
       </c>
       <c r="H79" s="40"/>
       <c r="I79" s="19" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J79" s="17" t="s">
         <v>1160</v>
@@ -9940,14 +9960,14 @@
       <c r="O79" s="59" t="s">
         <v>768</v>
       </c>
-      <c r="P79" s="68" t="s">
+      <c r="P79" s="64" t="s">
         <v>768</v>
       </c>
-      <c r="Q79" s="69"/>
-      <c r="R79" s="59" t="s">
+      <c r="Q79" s="65"/>
+      <c r="R79" s="83" t="s">
         <v>561</v>
       </c>
-      <c r="S79" s="59" t="s">
+      <c r="S79" s="83" t="s">
         <v>1087</v>
       </c>
       <c r="T79" s="5" t="s">
@@ -10000,14 +10020,14 @@
       <c r="O80" s="59" t="s">
         <v>968</v>
       </c>
-      <c r="P80" s="68" t="s">
+      <c r="P80" s="64" t="s">
         <v>769</v>
       </c>
-      <c r="Q80" s="69"/>
-      <c r="R80" s="59" t="s">
+      <c r="Q80" s="65"/>
+      <c r="R80" s="83" t="s">
         <v>562</v>
       </c>
-      <c r="S80" s="59" t="s">
+      <c r="S80" s="83" t="s">
         <v>1088</v>
       </c>
       <c r="T80" s="5" t="s">
@@ -10051,7 +10071,7 @@
         <v>B02</v>
       </c>
       <c r="I81" s="18" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="J81" s="17" t="s">
         <v>1160</v>
@@ -10067,14 +10087,14 @@
       <c r="O81" s="59" t="s">
         <v>426</v>
       </c>
-      <c r="P81" s="68" t="s">
+      <c r="P81" s="64" t="s">
         <v>426</v>
       </c>
-      <c r="Q81" s="69"/>
-      <c r="R81" s="59" t="s">
+      <c r="Q81" s="65"/>
+      <c r="R81" s="83" t="s">
         <v>563</v>
       </c>
-      <c r="S81" s="59" t="s">
+      <c r="S81" s="83" t="s">
         <v>1089</v>
       </c>
       <c r="T81" s="5" t="s">
@@ -10118,7 +10138,7 @@
         <v>B03</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J82" s="17" t="s">
         <v>1160</v>
@@ -10134,14 +10154,14 @@
       <c r="O82" s="59" t="s">
         <v>427</v>
       </c>
-      <c r="P82" s="68" t="s">
+      <c r="P82" s="64" t="s">
         <v>427</v>
       </c>
-      <c r="Q82" s="69"/>
-      <c r="R82" s="59" t="s">
+      <c r="Q82" s="65"/>
+      <c r="R82" s="83" t="s">
         <v>564</v>
       </c>
-      <c r="S82" s="59" t="s">
+      <c r="S82" s="83" t="s">
         <v>1090</v>
       </c>
       <c r="T82" s="5" t="s">
@@ -10187,7 +10207,7 @@
         <v>B04</v>
       </c>
       <c r="I83" s="16" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="J83" s="17" t="s">
         <v>1160</v>
@@ -10203,14 +10223,14 @@
       <c r="O83" s="59" t="s">
         <v>428</v>
       </c>
-      <c r="P83" s="68" t="s">
+      <c r="P83" s="64" t="s">
         <v>770</v>
       </c>
-      <c r="Q83" s="69"/>
-      <c r="R83" s="59" t="s">
+      <c r="Q83" s="65"/>
+      <c r="R83" s="83" t="s">
         <v>565</v>
       </c>
-      <c r="S83" s="59" t="s">
+      <c r="S83" s="83" t="s">
         <v>1091</v>
       </c>
       <c r="T83" s="5" t="s">
@@ -10254,7 +10274,7 @@
         <v>B05</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J84" s="17" t="s">
         <v>1160</v>
@@ -10270,14 +10290,14 @@
       <c r="O84" s="59" t="s">
         <v>429</v>
       </c>
-      <c r="P84" s="68" t="s">
+      <c r="P84" s="64" t="s">
         <v>429</v>
       </c>
-      <c r="Q84" s="69"/>
-      <c r="R84" s="59" t="s">
+      <c r="Q84" s="65"/>
+      <c r="R84" s="83" t="s">
         <v>566</v>
       </c>
-      <c r="S84" s="59" t="s">
+      <c r="S84" s="83" t="s">
         <v>1082</v>
       </c>
       <c r="T84" s="5" t="s">
@@ -10321,7 +10341,7 @@
         <v>B06</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J85" s="17" t="s">
         <v>1160</v>
@@ -10337,14 +10357,14 @@
       <c r="O85" s="59" t="s">
         <v>430</v>
       </c>
-      <c r="P85" s="68" t="s">
+      <c r="P85" s="64" t="s">
         <v>430</v>
       </c>
-      <c r="Q85" s="69"/>
-      <c r="R85" s="59" t="s">
+      <c r="Q85" s="65"/>
+      <c r="R85" s="83" t="s">
         <v>567</v>
       </c>
-      <c r="S85" s="59" t="s">
+      <c r="S85" s="83" t="s">
         <v>1083</v>
       </c>
       <c r="T85" s="5" t="s">
@@ -10388,7 +10408,7 @@
         <v>B07</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="J86" s="17" t="s">
         <v>1160</v>
@@ -10404,14 +10424,14 @@
       <c r="O86" s="59" t="s">
         <v>431</v>
       </c>
-      <c r="P86" s="68" t="s">
+      <c r="P86" s="64" t="s">
         <v>771</v>
       </c>
-      <c r="Q86" s="69"/>
-      <c r="R86" s="59" t="s">
+      <c r="Q86" s="65"/>
+      <c r="R86" s="83" t="s">
         <v>568</v>
       </c>
-      <c r="S86" s="59" t="s">
+      <c r="S86" s="83" t="s">
         <v>1085</v>
       </c>
       <c r="T86" s="5" t="s">
@@ -10467,12 +10487,12 @@
       <c r="O87" s="59" t="s">
         <v>432</v>
       </c>
-      <c r="P87" s="68" t="s">
+      <c r="P87" s="64" t="s">
         <v>772</v>
       </c>
-      <c r="Q87" s="69"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
+      <c r="Q87" s="65"/>
+      <c r="R87" s="83"/>
+      <c r="S87" s="83"/>
       <c r="T87" s="5" t="s">
         <v>222</v>
       </c>
@@ -10511,7 +10531,7 @@
       </c>
       <c r="H88" s="40"/>
       <c r="I88" s="18" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="J88" s="17" t="s">
         <v>1160</v>
@@ -10527,14 +10547,14 @@
       <c r="O88" s="59" t="s">
         <v>773</v>
       </c>
-      <c r="P88" s="68" t="s">
+      <c r="P88" s="64" t="s">
         <v>773</v>
       </c>
-      <c r="Q88" s="69"/>
-      <c r="R88" s="59" t="s">
+      <c r="Q88" s="65"/>
+      <c r="R88" s="83" t="s">
         <v>569</v>
       </c>
-      <c r="S88" s="64">
+      <c r="S88" s="85">
         <v>172</v>
       </c>
       <c r="T88" s="5" t="s">
@@ -10575,7 +10595,7 @@
       </c>
       <c r="H89" s="40"/>
       <c r="I89" s="18" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="J89" s="17" t="s">
         <v>1160</v>
@@ -10591,14 +10611,14 @@
       <c r="O89" s="59" t="s">
         <v>774</v>
       </c>
-      <c r="P89" s="68" t="s">
+      <c r="P89" s="64" t="s">
         <v>774</v>
       </c>
-      <c r="Q89" s="69"/>
-      <c r="R89" s="59" t="s">
+      <c r="Q89" s="65"/>
+      <c r="R89" s="83" t="s">
         <v>570</v>
       </c>
-      <c r="S89" s="59" t="s">
+      <c r="S89" s="83" t="s">
         <v>1079</v>
       </c>
       <c r="T89" s="5" t="s">
@@ -10642,7 +10662,7 @@
         <v>B09</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="J90" s="17" t="s">
         <v>1160</v>
@@ -10658,14 +10678,14 @@
       <c r="O90" s="59" t="s">
         <v>433</v>
       </c>
-      <c r="P90" s="68" t="s">
+      <c r="P90" s="64" t="s">
         <v>433</v>
       </c>
-      <c r="Q90" s="69"/>
-      <c r="R90" s="59" t="s">
+      <c r="Q90" s="65"/>
+      <c r="R90" s="83" t="s">
         <v>571</v>
       </c>
-      <c r="S90" s="59" t="s">
+      <c r="S90" s="83" t="s">
         <v>1080</v>
       </c>
       <c r="T90" s="5" t="s">
@@ -10689,7 +10709,7 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="37" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>1138</v>
@@ -10711,16 +10731,16 @@
       <c r="M91" s="49"/>
       <c r="N91" s="49"/>
       <c r="O91" s="59"/>
-      <c r="P91" s="68"/>
-      <c r="Q91" s="69"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
+      <c r="P91" s="64"/>
+      <c r="Q91" s="65"/>
+      <c r="R91" s="83"/>
+      <c r="S91" s="83"/>
       <c r="T91" s="5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="U91" s="20"/>
       <c r="V91" s="5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="W91" s="45"/>
       <c r="X91" s="2"/>
@@ -10749,7 +10769,7 @@
       </c>
       <c r="H92" s="40"/>
       <c r="I92" s="5" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="J92" s="17" t="s">
         <v>1160</v>
@@ -10765,14 +10785,14 @@
       <c r="O92" s="59" t="s">
         <v>434</v>
       </c>
-      <c r="P92" s="68" t="s">
+      <c r="P92" s="64" t="s">
         <v>434</v>
       </c>
-      <c r="Q92" s="69"/>
-      <c r="R92" s="59" t="s">
+      <c r="Q92" s="65"/>
+      <c r="R92" s="83" t="s">
         <v>572</v>
       </c>
-      <c r="S92" s="59" t="s">
+      <c r="S92" s="83" t="s">
         <v>1074</v>
       </c>
       <c r="T92" s="5" t="s">
@@ -10789,7 +10809,7 @@
       </c>
       <c r="X92" s="2"/>
     </row>
-    <row r="93" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A93" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10813,7 +10833,7 @@
       </c>
       <c r="H93" s="40"/>
       <c r="I93" s="5" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="J93" s="17" t="s">
         <v>1160</v>
@@ -10822,21 +10842,21 @@
         <v>1247</v>
       </c>
       <c r="L93" s="49" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M93" s="49"/>
       <c r="N93" s="49"/>
       <c r="O93" s="59" t="s">
         <v>435</v>
       </c>
-      <c r="P93" s="68" t="s">
+      <c r="P93" s="64" t="s">
         <v>775</v>
       </c>
-      <c r="Q93" s="69"/>
-      <c r="R93" s="59" t="s">
+      <c r="Q93" s="65"/>
+      <c r="R93" s="83" t="s">
         <v>573</v>
       </c>
-      <c r="S93" s="59" t="s">
+      <c r="S93" s="83" t="s">
         <v>1073</v>
       </c>
       <c r="T93" s="5" t="s">
@@ -10880,7 +10900,7 @@
         <v>B11</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="J94" s="17" t="s">
         <v>1160</v>
@@ -10896,14 +10916,14 @@
       <c r="O94" s="59" t="s">
         <v>436</v>
       </c>
-      <c r="P94" s="68" t="s">
+      <c r="P94" s="64" t="s">
         <v>436</v>
       </c>
-      <c r="Q94" s="69"/>
-      <c r="R94" s="59" t="s">
+      <c r="Q94" s="65"/>
+      <c r="R94" s="83" t="s">
         <v>574</v>
       </c>
-      <c r="S94" s="59" t="s">
+      <c r="S94" s="83" t="s">
         <v>1078</v>
       </c>
       <c r="T94" s="5" t="s">
@@ -10947,7 +10967,7 @@
         <v>B12</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="J95" s="17" t="s">
         <v>1160</v>
@@ -10963,14 +10983,14 @@
       <c r="O95" s="59" t="s">
         <v>437</v>
       </c>
-      <c r="P95" s="68" t="s">
+      <c r="P95" s="64" t="s">
         <v>437</v>
       </c>
-      <c r="Q95" s="69"/>
-      <c r="R95" s="59" t="s">
+      <c r="Q95" s="65"/>
+      <c r="R95" s="83" t="s">
         <v>575</v>
       </c>
-      <c r="S95" s="59" t="s">
+      <c r="S95" s="83" t="s">
         <v>1077</v>
       </c>
       <c r="T95" s="5" t="s">
@@ -11011,7 +11031,7 @@
       </c>
       <c r="H96" s="40"/>
       <c r="I96" s="19" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="J96" s="17" t="s">
         <v>1160</v>
@@ -11027,14 +11047,14 @@
       <c r="O96" s="59" t="s">
         <v>776</v>
       </c>
-      <c r="P96" s="68" t="s">
+      <c r="P96" s="64" t="s">
         <v>776</v>
       </c>
-      <c r="Q96" s="69"/>
-      <c r="R96" s="59" t="s">
+      <c r="Q96" s="65"/>
+      <c r="R96" s="83" t="s">
         <v>576</v>
       </c>
-      <c r="S96" s="59" t="s">
+      <c r="S96" s="83" t="s">
         <v>1081</v>
       </c>
       <c r="T96" s="5" t="s">
@@ -11051,7 +11071,7 @@
       </c>
       <c r="X96" s="2"/>
     </row>
-    <row r="97" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.13. - Kidney, renal pelvis and ureter cancer</v>
@@ -11078,7 +11098,7 @@
         <v>B13</v>
       </c>
       <c r="I97" s="19" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="J97" s="17" t="s">
         <v>1160</v>
@@ -11094,14 +11114,14 @@
       <c r="O97" s="59" t="s">
         <v>969</v>
       </c>
-      <c r="P97" s="68" t="s">
+      <c r="P97" s="64" t="s">
         <v>777</v>
       </c>
-      <c r="Q97" s="69"/>
-      <c r="R97" s="59" t="s">
+      <c r="Q97" s="65"/>
+      <c r="R97" s="83" t="s">
         <v>577</v>
       </c>
-      <c r="S97" s="59" t="s">
+      <c r="S97" s="83" t="s">
         <v>1084</v>
       </c>
       <c r="T97" s="5" t="s">
@@ -11145,7 +11165,7 @@
         <v>B14</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="J98" s="17" t="s">
         <v>1160</v>
@@ -11161,14 +11181,14 @@
       <c r="O98" s="59" t="s">
         <v>438</v>
       </c>
-      <c r="P98" s="68" t="s">
+      <c r="P98" s="64" t="s">
         <v>438</v>
       </c>
-      <c r="Q98" s="69"/>
-      <c r="R98" s="59" t="s">
+      <c r="Q98" s="65"/>
+      <c r="R98" s="83" t="s">
         <v>578</v>
       </c>
-      <c r="S98" s="59" t="s">
+      <c r="S98" s="83" t="s">
         <v>1076</v>
       </c>
       <c r="T98" s="5" t="s">
@@ -11212,7 +11232,7 @@
         <v>B15</v>
       </c>
       <c r="I99" s="16" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="J99" s="17" t="s">
         <v>1160</v>
@@ -11228,14 +11248,14 @@
       <c r="O99" s="59" t="s">
         <v>970</v>
       </c>
-      <c r="P99" s="68" t="s">
+      <c r="P99" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="Q99" s="69"/>
-      <c r="R99" s="59" t="s">
+      <c r="Q99" s="65"/>
+      <c r="R99" s="83" t="s">
         <v>579</v>
       </c>
-      <c r="S99" s="59" t="s">
+      <c r="S99" s="83" t="s">
         <v>1072</v>
       </c>
       <c r="T99" s="5" t="s">
@@ -11276,7 +11296,7 @@
       </c>
       <c r="H100" s="40"/>
       <c r="I100" s="19" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="J100" s="17" t="s">
         <v>1160</v>
@@ -11292,14 +11312,14 @@
       <c r="O100" s="59" t="s">
         <v>971</v>
       </c>
-      <c r="P100" s="68" t="s">
+      <c r="P100" s="64" t="s">
         <v>779</v>
       </c>
-      <c r="Q100" s="69"/>
-      <c r="R100" s="59" t="s">
+      <c r="Q100" s="65"/>
+      <c r="R100" s="83" t="s">
         <v>580</v>
       </c>
-      <c r="S100" s="59" t="s">
+      <c r="S100" s="83" t="s">
         <v>1075</v>
       </c>
       <c r="T100" s="5" t="s">
@@ -11340,7 +11360,7 @@
       </c>
       <c r="H101" s="40"/>
       <c r="I101" s="19" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="J101" s="17" t="s">
         <v>1160</v>
@@ -11356,14 +11376,14 @@
       <c r="O101" s="59" t="s">
         <v>780</v>
       </c>
-      <c r="P101" s="68" t="s">
+      <c r="P101" s="64" t="s">
         <v>780</v>
       </c>
-      <c r="Q101" s="69"/>
-      <c r="R101" s="59" t="s">
+      <c r="Q101" s="65"/>
+      <c r="R101" s="83" t="s">
         <v>581</v>
       </c>
-      <c r="S101" s="59" t="s">
+      <c r="S101" s="83" t="s">
         <v>1071</v>
       </c>
       <c r="T101" s="5" t="s">
@@ -11404,7 +11424,7 @@
       </c>
       <c r="H102" s="40"/>
       <c r="I102" s="19" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="J102" s="17" t="s">
         <v>1160</v>
@@ -11420,14 +11440,14 @@
       <c r="O102" s="59" t="s">
         <v>781</v>
       </c>
-      <c r="P102" s="68" t="s">
+      <c r="P102" s="64" t="s">
         <v>781</v>
       </c>
-      <c r="Q102" s="69"/>
-      <c r="R102" s="59" t="s">
+      <c r="Q102" s="65"/>
+      <c r="R102" s="83" t="s">
         <v>582</v>
       </c>
-      <c r="S102" s="59" t="s">
+      <c r="S102" s="83" t="s">
         <v>1070</v>
       </c>
       <c r="T102" s="5" t="s">
@@ -11480,14 +11500,14 @@
       <c r="O103" s="59" t="s">
         <v>782</v>
       </c>
-      <c r="P103" s="68" t="s">
+      <c r="P103" s="64" t="s">
         <v>782</v>
       </c>
-      <c r="Q103" s="69"/>
-      <c r="R103" s="59" t="s">
+      <c r="Q103" s="65"/>
+      <c r="R103" s="83" t="s">
         <v>583</v>
       </c>
-      <c r="S103" s="59" t="s">
+      <c r="S103" s="83" t="s">
         <v>1069</v>
       </c>
       <c r="T103" s="5" t="s">
@@ -11540,14 +11560,14 @@
       <c r="O104" s="59" t="s">
         <v>439</v>
       </c>
-      <c r="P104" s="68" t="s">
+      <c r="P104" s="64" t="s">
         <v>783</v>
       </c>
-      <c r="Q104" s="69"/>
-      <c r="R104" s="59" t="s">
+      <c r="Q104" s="65"/>
+      <c r="R104" s="83" t="s">
         <v>584</v>
       </c>
-      <c r="S104" s="59" t="s">
+      <c r="S104" s="83" t="s">
         <v>1032</v>
       </c>
       <c r="T104" s="5" t="s">
@@ -11605,14 +11625,14 @@
       <c r="O105" s="59" t="s">
         <v>784</v>
       </c>
-      <c r="P105" s="68" t="s">
+      <c r="P105" s="64" t="s">
         <v>784</v>
       </c>
-      <c r="Q105" s="69"/>
-      <c r="R105" s="59" t="s">
+      <c r="Q105" s="65"/>
+      <c r="R105" s="83" t="s">
         <v>585</v>
       </c>
-      <c r="S105" s="64">
+      <c r="S105" s="85">
         <v>201</v>
       </c>
       <c r="T105" s="5" t="s">
@@ -11670,14 +11690,14 @@
       <c r="O106" s="59" t="s">
         <v>972</v>
       </c>
-      <c r="P106" s="68" t="s">
+      <c r="P106" s="64" t="s">
         <v>785</v>
       </c>
-      <c r="Q106" s="69"/>
-      <c r="R106" s="59" t="s">
+      <c r="Q106" s="65"/>
+      <c r="R106" s="83" t="s">
         <v>586</v>
       </c>
-      <c r="S106" s="59" t="s">
+      <c r="S106" s="83" t="s">
         <v>1031</v>
       </c>
       <c r="T106" s="5" t="s">
@@ -11735,14 +11755,14 @@
       <c r="O107" s="59" t="s">
         <v>973</v>
       </c>
-      <c r="P107" s="68" t="s">
+      <c r="P107" s="64" t="s">
         <v>786</v>
       </c>
-      <c r="Q107" s="69"/>
-      <c r="R107" s="59" t="s">
+      <c r="Q107" s="65"/>
+      <c r="R107" s="83" t="s">
         <v>587</v>
       </c>
-      <c r="S107" s="64">
+      <c r="S107" s="85">
         <v>203</v>
       </c>
       <c r="T107" s="5" t="s">
@@ -11798,14 +11818,14 @@
       <c r="O108" s="59" t="s">
         <v>440</v>
       </c>
-      <c r="P108" s="68" t="s">
+      <c r="P108" s="64" t="s">
         <v>787</v>
       </c>
-      <c r="Q108" s="69"/>
-      <c r="R108" s="59" t="s">
+      <c r="Q108" s="65"/>
+      <c r="R108" s="83" t="s">
         <v>588</v>
       </c>
-      <c r="S108" s="59" t="s">
+      <c r="S108" s="83" t="s">
         <v>1030</v>
       </c>
       <c r="T108" s="5" t="s">
@@ -11822,7 +11842,7 @@
       </c>
       <c r="X108" s="2"/>
     </row>
-    <row r="109" spans="1:24" ht="51" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.99. - Other malignant neoplasms</v>
@@ -11849,7 +11869,7 @@
         <v>B99</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>1160</v>
@@ -11865,12 +11885,12 @@
       <c r="O109" s="59" t="s">
         <v>974</v>
       </c>
-      <c r="P109" s="68" t="s">
+      <c r="P109" s="64" t="s">
         <v>788</v>
       </c>
-      <c r="Q109" s="69"/>
-      <c r="R109" s="59"/>
-      <c r="S109" s="59"/>
+      <c r="Q109" s="65"/>
+      <c r="R109" s="83"/>
+      <c r="S109" s="83"/>
       <c r="T109" s="5" t="s">
         <v>236</v>
       </c>
@@ -11885,7 +11905,7 @@
       </c>
       <c r="X109" s="2"/>
     </row>
-    <row r="110" spans="1:24" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A110" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11909,24 +11929,24 @@
       </c>
       <c r="H110" s="40"/>
       <c r="K110" s="5" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="M110" s="5"/>
       <c r="N110" s="5"/>
       <c r="O110" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="P110" s="68" t="s">
+      <c r="P110" s="64" t="s">
         <v>789</v>
       </c>
-      <c r="Q110" s="69"/>
-      <c r="R110" s="59" t="s">
+      <c r="Q110" s="65"/>
+      <c r="R110" s="83" t="s">
         <v>590</v>
       </c>
-      <c r="S110" s="60" t="s">
+      <c r="S110" s="86" t="s">
         <v>589</v>
       </c>
       <c r="T110" s="5" t="s">
@@ -11970,7 +11990,7 @@
         <v>D01</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>1160</v>
@@ -11979,25 +11999,25 @@
         <v>1250</v>
       </c>
       <c r="L111" s="49" t="s">
+        <v>1332</v>
+      </c>
+      <c r="M111" s="49" t="s">
+        <v>1337</v>
+      </c>
+      <c r="N111" s="49" t="s">
         <v>1335</v>
-      </c>
-      <c r="M111" s="49" t="s">
-        <v>1340</v>
-      </c>
-      <c r="N111" s="49" t="s">
-        <v>1338</v>
       </c>
       <c r="O111" s="59" t="s">
         <v>975</v>
       </c>
-      <c r="P111" s="68" t="s">
+      <c r="P111" s="64" t="s">
         <v>790</v>
       </c>
-      <c r="Q111" s="69"/>
-      <c r="R111" s="59" t="s">
+      <c r="Q111" s="65"/>
+      <c r="R111" s="83" t="s">
         <v>592</v>
       </c>
-      <c r="S111" s="62" t="s">
+      <c r="S111" s="84" t="s">
         <v>591</v>
       </c>
       <c r="T111" s="5" t="s">
@@ -12013,10 +12033,10 @@
         <v>66</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="112" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A112" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...D.02. - Endocrine, blood, immune disorders</v>
@@ -12044,24 +12064,24 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="L112" s="19" t="s">
         <v>1306</v>
-      </c>
-      <c r="L112" s="19" t="s">
-        <v>1307</v>
       </c>
       <c r="M112" s="19"/>
       <c r="N112" s="19"/>
       <c r="O112" s="59" t="s">
+        <v>1305</v>
+      </c>
+      <c r="P112" s="62" t="s">
         <v>1306</v>
       </c>
-      <c r="P112" s="66" t="s">
-        <v>1307</v>
-      </c>
-      <c r="Q112" s="69"/>
-      <c r="R112" s="59" t="s">
+      <c r="Q112" s="65"/>
+      <c r="R112" s="83" t="s">
         <v>684</v>
       </c>
-      <c r="S112" s="62" t="s">
+      <c r="S112" s="84" t="s">
         <v>685</v>
       </c>
       <c r="T112" s="5" t="s">
@@ -12114,14 +12134,14 @@
       <c r="O113" s="59" t="s">
         <v>791</v>
       </c>
-      <c r="P113" s="68" t="s">
+      <c r="P113" s="64" t="s">
         <v>791</v>
       </c>
-      <c r="Q113" s="69"/>
-      <c r="R113" s="59" t="s">
+      <c r="Q113" s="65"/>
+      <c r="R113" s="83" t="s">
         <v>593</v>
       </c>
-      <c r="S113" s="64">
+      <c r="S113" s="85">
         <v>2824</v>
       </c>
       <c r="T113" s="5" t="s">
@@ -12174,14 +12194,14 @@
       <c r="O114" s="59" t="s">
         <v>792</v>
       </c>
-      <c r="P114" s="68" t="s">
+      <c r="P114" s="64" t="s">
         <v>792</v>
       </c>
-      <c r="Q114" s="69"/>
-      <c r="R114" s="59" t="s">
+      <c r="Q114" s="65"/>
+      <c r="R114" s="83" t="s">
         <v>594</v>
       </c>
-      <c r="S114" s="64">
+      <c r="S114" s="85">
         <v>2826</v>
       </c>
       <c r="T114" s="5" t="s">
@@ -12234,14 +12254,14 @@
       <c r="O115" s="59" t="s">
         <v>976</v>
       </c>
-      <c r="P115" s="68" t="s">
+      <c r="P115" s="64" t="s">
         <v>793</v>
       </c>
-      <c r="Q115" s="69"/>
-      <c r="R115" s="59" t="s">
+      <c r="Q115" s="65"/>
+      <c r="R115" s="83" t="s">
         <v>595</v>
       </c>
-      <c r="S115" s="59" t="s">
+      <c r="S115" s="83" t="s">
         <v>1105</v>
       </c>
       <c r="T115" s="5" t="s">
@@ -12258,7 +12278,7 @@
       </c>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A116" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12294,14 +12314,14 @@
       <c r="O116" s="59" t="s">
         <v>977</v>
       </c>
-      <c r="P116" s="68" t="s">
+      <c r="P116" s="64" t="s">
         <v>794</v>
       </c>
-      <c r="Q116" s="69"/>
-      <c r="R116" s="59" t="s">
+      <c r="Q116" s="65"/>
+      <c r="R116" s="83" t="s">
         <v>596</v>
       </c>
-      <c r="S116" s="62" t="s">
+      <c r="S116" s="84" t="s">
         <v>1106</v>
       </c>
       <c r="T116" s="5" t="s">
@@ -12318,7 +12338,7 @@
       </c>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:24" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:24" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12353,14 +12373,14 @@
       <c r="O117" s="59" t="s">
         <v>978</v>
       </c>
-      <c r="P117" s="66" t="s">
+      <c r="P117" s="62" t="s">
         <v>795</v>
       </c>
-      <c r="Q117" s="67"/>
-      <c r="R117" s="59" t="s">
+      <c r="Q117" s="63"/>
+      <c r="R117" s="83" t="s">
         <v>598</v>
       </c>
-      <c r="S117" s="59" t="s">
+      <c r="S117" s="83" t="s">
         <v>597</v>
       </c>
       <c r="T117" s="2" t="s">
@@ -12384,7 +12404,7 @@
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="32" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>1141</v>
@@ -12407,16 +12427,16 @@
       <c r="M118" s="19"/>
       <c r="N118" s="19"/>
       <c r="O118" s="59"/>
-      <c r="P118" s="66"/>
-      <c r="Q118" s="67"/>
-      <c r="R118" s="59"/>
-      <c r="S118" s="59"/>
+      <c r="P118" s="62"/>
+      <c r="Q118" s="63"/>
+      <c r="R118" s="83"/>
+      <c r="S118" s="83"/>
       <c r="T118" s="2" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="U118" s="20"/>
       <c r="V118" s="2" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="W118" s="45"/>
       <c r="X118" s="2"/>
@@ -12428,7 +12448,7 @@
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="32" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>1141</v>
@@ -12449,12 +12469,12 @@
       <c r="M119" s="19"/>
       <c r="N119" s="19"/>
       <c r="O119" s="59"/>
-      <c r="P119" s="66"/>
-      <c r="Q119" s="67"/>
-      <c r="R119" s="59"/>
-      <c r="S119" s="59"/>
+      <c r="P119" s="62"/>
+      <c r="Q119" s="63"/>
+      <c r="R119" s="83"/>
+      <c r="S119" s="83"/>
       <c r="T119" s="2" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="U119" s="20"/>
       <c r="V119" s="2" t="s">
@@ -12484,10 +12504,10 @@
       <c r="M120" s="19"/>
       <c r="N120" s="19"/>
       <c r="O120" s="59"/>
-      <c r="P120" s="66"/>
-      <c r="Q120" s="67"/>
-      <c r="R120" s="59"/>
-      <c r="S120" s="59"/>
+      <c r="P120" s="62"/>
+      <c r="Q120" s="63"/>
+      <c r="R120" s="83"/>
+      <c r="S120" s="83"/>
       <c r="T120" s="2"/>
       <c r="U120" s="20"/>
       <c r="V120" s="2"/>
@@ -12523,12 +12543,12 @@
       <c r="O121" s="59" t="s">
         <v>979</v>
       </c>
-      <c r="P121" s="68" t="s">
+      <c r="P121" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="Q121" s="69"/>
-      <c r="R121" s="59"/>
-      <c r="S121" s="59"/>
+      <c r="Q121" s="65"/>
+      <c r="R121" s="83"/>
+      <c r="S121" s="83"/>
       <c r="T121" s="2" t="s">
         <v>244</v>
       </c>
@@ -12583,12 +12603,12 @@
       <c r="O122" s="59" t="s">
         <v>980</v>
       </c>
-      <c r="P122" s="70" t="s">
+      <c r="P122" s="66" t="s">
         <v>797</v>
       </c>
-      <c r="Q122" s="71"/>
-      <c r="R122" s="59"/>
-      <c r="S122" s="59"/>
+      <c r="Q122" s="67"/>
+      <c r="R122" s="83"/>
+      <c r="S122" s="83"/>
       <c r="T122" s="2" t="s">
         <v>245</v>
       </c>
@@ -12643,12 +12663,12 @@
       <c r="O123" s="59" t="s">
         <v>981</v>
       </c>
-      <c r="P123" s="66" t="s">
+      <c r="P123" s="62" t="s">
         <v>798</v>
       </c>
-      <c r="Q123" s="67"/>
-      <c r="R123" s="59"/>
-      <c r="S123" s="59"/>
+      <c r="Q123" s="63"/>
+      <c r="R123" s="83"/>
+      <c r="S123" s="83"/>
       <c r="T123" s="2" t="s">
         <v>246</v>
       </c>
@@ -12703,12 +12723,12 @@
       <c r="O124" s="59" t="s">
         <v>442</v>
       </c>
-      <c r="P124" s="68" t="s">
+      <c r="P124" s="64" t="s">
         <v>799</v>
       </c>
-      <c r="Q124" s="69"/>
-      <c r="R124" s="59"/>
-      <c r="S124" s="59"/>
+      <c r="Q124" s="65"/>
+      <c r="R124" s="83"/>
+      <c r="S124" s="83"/>
       <c r="T124" s="5" t="s">
         <v>908</v>
       </c>
@@ -12752,25 +12772,25 @@
         <v>443</v>
       </c>
       <c r="L125" s="49" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="M125" s="49" t="s">
         <v>443</v>
       </c>
       <c r="N125" s="49" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="O125" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="P125" s="68" t="s">
+      <c r="P125" s="64" t="s">
         <v>754</v>
       </c>
-      <c r="Q125" s="69"/>
-      <c r="R125" s="59" t="s">
+      <c r="Q125" s="65"/>
+      <c r="R125" s="83" t="s">
         <v>599</v>
       </c>
-      <c r="S125" s="64">
+      <c r="S125" s="85">
         <v>295</v>
       </c>
       <c r="T125" s="5" t="s">
@@ -12787,7 +12807,7 @@
       </c>
       <c r="X125" s="2"/>
     </row>
-    <row r="126" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A126" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.a. - Alcohol use disorders</v>
@@ -12816,7 +12836,7 @@
         <v>D04a</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>1233</v>
@@ -12825,21 +12845,21 @@
         <v>1220</v>
       </c>
       <c r="L126" s="19" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="M126" s="19"/>
       <c r="N126" s="19"/>
       <c r="O126" s="59" t="s">
-        <v>1316</v>
-      </c>
-      <c r="P126" s="66" t="s">
-        <v>1261</v>
-      </c>
-      <c r="Q126" s="69"/>
-      <c r="R126" s="59" t="s">
+        <v>1314</v>
+      </c>
+      <c r="P126" s="62" t="s">
+        <v>1260</v>
+      </c>
+      <c r="Q126" s="65"/>
+      <c r="R126" s="83" t="s">
         <v>600</v>
       </c>
-      <c r="S126" s="59" t="s">
+      <c r="S126" s="83" t="s">
         <v>1096</v>
       </c>
       <c r="T126" s="5" t="s">
@@ -12885,14 +12905,14 @@
       <c r="O127" s="59" t="s">
         <v>982</v>
       </c>
-      <c r="P127" s="68" t="s">
+      <c r="P127" s="64" t="s">
         <v>800</v>
       </c>
-      <c r="Q127" s="69"/>
-      <c r="R127" s="59" t="s">
+      <c r="Q127" s="65"/>
+      <c r="R127" s="83" t="s">
         <v>601</v>
       </c>
-      <c r="S127" s="59" t="s">
+      <c r="S127" s="83" t="s">
         <v>1104</v>
       </c>
       <c r="T127" s="5" t="s">
@@ -12909,7 +12929,7 @@
       </c>
       <c r="X127" s="2"/>
     </row>
-    <row r="128" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A128" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.b. - Opioid use disorders</v>
@@ -12937,29 +12957,29 @@
         <f>CONCATENATE(D128,E128,F128)</f>
         <v>D04b</v>
       </c>
-      <c r="I128" s="84" t="s">
-        <v>1392</v>
+      <c r="I128" s="79" t="s">
+        <v>1387</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="L128" s="49" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="M128" s="49"/>
       <c r="N128" s="49"/>
       <c r="O128" s="59" t="s">
         <v>983</v>
       </c>
-      <c r="P128" s="68" t="s">
+      <c r="P128" s="64" t="s">
         <v>801</v>
       </c>
-      <c r="Q128" s="69"/>
-      <c r="R128" s="59" t="s">
+      <c r="Q128" s="65"/>
+      <c r="R128" s="83" t="s">
         <v>602</v>
       </c>
-      <c r="S128" s="59" t="s">
+      <c r="S128" s="83" t="s">
         <v>1099</v>
       </c>
       <c r="T128" s="5" t="s">
@@ -13017,14 +13037,14 @@
       <c r="O129" s="59" t="s">
         <v>802</v>
       </c>
-      <c r="P129" s="68" t="s">
+      <c r="P129" s="64" t="s">
         <v>802</v>
       </c>
-      <c r="Q129" s="69"/>
-      <c r="R129" s="59" t="s">
+      <c r="Q129" s="65"/>
+      <c r="R129" s="83" t="s">
         <v>603</v>
       </c>
-      <c r="S129" s="59" t="s">
+      <c r="S129" s="83" t="s">
         <v>1098</v>
       </c>
       <c r="T129" s="5" t="s">
@@ -13082,14 +13102,14 @@
       <c r="O130" s="59" t="s">
         <v>803</v>
       </c>
-      <c r="P130" s="68" t="s">
+      <c r="P130" s="64" t="s">
         <v>803</v>
       </c>
-      <c r="Q130" s="69"/>
-      <c r="R130" s="59" t="s">
+      <c r="Q130" s="65"/>
+      <c r="R130" s="83" t="s">
         <v>604</v>
       </c>
-      <c r="S130" s="59" t="s">
+      <c r="S130" s="83" t="s">
         <v>1097</v>
       </c>
       <c r="T130" s="5" t="s">
@@ -13141,12 +13161,12 @@
       <c r="O131" s="59" t="s">
         <v>804</v>
       </c>
-      <c r="P131" s="68" t="s">
+      <c r="P131" s="64" t="s">
         <v>804</v>
       </c>
-      <c r="Q131" s="69"/>
-      <c r="R131" s="59"/>
-      <c r="S131" s="59"/>
+      <c r="Q131" s="65"/>
+      <c r="R131" s="83"/>
+      <c r="S131" s="83"/>
       <c r="T131" s="5" t="s">
         <v>912</v>
       </c>
@@ -13161,7 +13181,7 @@
       </c>
       <c r="X131" s="2"/>
     </row>
-    <row r="132" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="44" t="str">
         <f t="shared" ref="A132:A195" si="12">IF(H132&lt;&gt;"",IF(F132&lt;&gt;"",CONCATENATE("....",D132,".",E132,".",F132,". - ",T132),IF(E132&lt;&gt;"",CONCATENATE("...",D132,".",E132,". - ",T132),CONCATENATE("..",D132,". - ",T132))),"")</f>
         <v/>
@@ -13184,31 +13204,31 @@
         <v>cD04</v>
       </c>
       <c r="H132" s="40"/>
-      <c r="I132" s="84" t="s">
-        <v>1393</v>
+      <c r="I132" s="79" t="s">
+        <v>1401</v>
       </c>
       <c r="J132" s="5" t="s">
         <v>1160</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="L132" s="19" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="M132" s="19"/>
       <c r="N132" s="19"/>
       <c r="O132" s="59" t="s">
         <v>984</v>
       </c>
-      <c r="P132" s="68" t="s">
+      <c r="P132" s="64" t="s">
         <v>805</v>
       </c>
-      <c r="Q132" s="69"/>
-      <c r="R132" s="59" t="s">
+      <c r="Q132" s="65"/>
+      <c r="R132" s="83" t="s">
         <v>605</v>
       </c>
-      <c r="S132" s="59" t="s">
+      <c r="S132" s="83" t="s">
         <v>1100</v>
       </c>
       <c r="T132" s="5" t="s">
@@ -13263,12 +13283,12 @@
       <c r="O133" s="59" t="s">
         <v>444</v>
       </c>
-      <c r="P133" s="68" t="s">
+      <c r="P133" s="64" t="s">
         <v>806</v>
       </c>
-      <c r="Q133" s="69"/>
-      <c r="R133" s="59"/>
-      <c r="S133" s="59"/>
+      <c r="Q133" s="65"/>
+      <c r="R133" s="83"/>
+      <c r="S133" s="83"/>
       <c r="T133" s="5" t="s">
         <v>250</v>
       </c>
@@ -13319,14 +13339,14 @@
       <c r="O134" s="59" t="s">
         <v>445</v>
       </c>
-      <c r="P134" s="68" t="s">
+      <c r="P134" s="64" t="s">
         <v>445</v>
       </c>
-      <c r="Q134" s="69"/>
-      <c r="R134" s="59" t="s">
+      <c r="Q134" s="65"/>
+      <c r="R134" s="83" t="s">
         <v>606</v>
       </c>
-      <c r="S134" s="59" t="s">
+      <c r="S134" s="83" t="s">
         <v>1051</v>
       </c>
       <c r="T134" s="5" t="s">
@@ -13379,12 +13399,12 @@
       <c r="O135" s="59" t="s">
         <v>807</v>
       </c>
-      <c r="P135" s="68" t="s">
+      <c r="P135" s="64" t="s">
         <v>807</v>
       </c>
-      <c r="Q135" s="69"/>
-      <c r="R135" s="59"/>
-      <c r="S135" s="59"/>
+      <c r="Q135" s="65"/>
+      <c r="R135" s="83"/>
+      <c r="S135" s="83"/>
       <c r="T135" s="5" t="s">
         <v>914</v>
       </c>
@@ -13428,12 +13448,12 @@
       <c r="O136" s="59" t="s">
         <v>985</v>
       </c>
-      <c r="P136" s="68" t="s">
+      <c r="P136" s="64" t="s">
         <v>808</v>
       </c>
-      <c r="Q136" s="69"/>
-      <c r="R136" s="59"/>
-      <c r="S136" s="59"/>
+      <c r="Q136" s="65"/>
+      <c r="R136" s="83"/>
+      <c r="S136" s="83"/>
       <c r="T136" s="5" t="s">
         <v>915</v>
       </c>
@@ -13484,12 +13504,12 @@
       <c r="O137" s="59" t="s">
         <v>809</v>
       </c>
-      <c r="P137" s="68" t="s">
+      <c r="P137" s="64" t="s">
         <v>809</v>
       </c>
-      <c r="Q137" s="69"/>
-      <c r="R137" s="59"/>
-      <c r="S137" s="59"/>
+      <c r="Q137" s="65"/>
+      <c r="R137" s="83"/>
+      <c r="S137" s="83"/>
       <c r="T137" s="5" t="s">
         <v>916</v>
       </c>
@@ -13540,12 +13560,12 @@
       <c r="O138" s="59" t="s">
         <v>986</v>
       </c>
-      <c r="P138" s="68" t="s">
+      <c r="P138" s="64" t="s">
         <v>810</v>
       </c>
-      <c r="Q138" s="69"/>
-      <c r="R138" s="59"/>
-      <c r="S138" s="59"/>
+      <c r="Q138" s="65"/>
+      <c r="R138" s="83"/>
+      <c r="S138" s="83"/>
       <c r="T138" s="5" t="s">
         <v>917</v>
       </c>
@@ -13596,12 +13616,12 @@
       <c r="O139" s="59" t="s">
         <v>446</v>
       </c>
-      <c r="P139" s="68" t="s">
+      <c r="P139" s="64" t="s">
         <v>811</v>
       </c>
-      <c r="Q139" s="69"/>
-      <c r="R139" s="59"/>
-      <c r="S139" s="59"/>
+      <c r="Q139" s="65"/>
+      <c r="R139" s="83"/>
+      <c r="S139" s="83"/>
       <c r="T139" s="5" t="s">
         <v>252</v>
       </c>
@@ -13616,7 +13636,7 @@
       </c>
       <c r="X139" s="2"/>
     </row>
-    <row r="140" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:24" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13652,12 +13672,12 @@
       <c r="O140" s="59" t="s">
         <v>987</v>
       </c>
-      <c r="P140" s="68" t="s">
+      <c r="P140" s="64" t="s">
         <v>812</v>
       </c>
-      <c r="Q140" s="69"/>
-      <c r="R140" s="59"/>
-      <c r="S140" s="59"/>
+      <c r="Q140" s="65"/>
+      <c r="R140" s="83"/>
+      <c r="S140" s="83"/>
       <c r="T140" s="5" t="s">
         <v>253</v>
       </c>
@@ -13672,7 +13692,7 @@
       </c>
       <c r="X140" s="2"/>
     </row>
-    <row r="141" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13705,14 +13725,14 @@
       <c r="O141" s="59" t="s">
         <v>447</v>
       </c>
-      <c r="P141" s="66" t="s">
+      <c r="P141" s="62" t="s">
         <v>813</v>
       </c>
-      <c r="Q141" s="67"/>
-      <c r="R141" s="59" t="s">
+      <c r="Q141" s="63"/>
+      <c r="R141" s="83" t="s">
         <v>608</v>
       </c>
-      <c r="S141" s="59" t="s">
+      <c r="S141" s="83" t="s">
         <v>683</v>
       </c>
       <c r="T141" s="2" t="s">
@@ -13770,14 +13790,14 @@
       <c r="O142" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="P142" s="68" t="s">
+      <c r="P142" s="64" t="s">
         <v>814</v>
       </c>
-      <c r="Q142" s="69"/>
-      <c r="R142" s="59" t="s">
+      <c r="Q142" s="65"/>
+      <c r="R142" s="83" t="s">
         <v>609</v>
       </c>
-      <c r="S142" s="59" t="s">
+      <c r="S142" s="83" t="s">
         <v>1095</v>
       </c>
       <c r="T142" s="5" t="s">
@@ -13830,14 +13850,14 @@
       <c r="O143" s="59" t="s">
         <v>449</v>
       </c>
-      <c r="P143" s="68" t="s">
+      <c r="P143" s="64" t="s">
         <v>815</v>
       </c>
-      <c r="Q143" s="69"/>
-      <c r="R143" s="59" t="s">
+      <c r="Q143" s="65"/>
+      <c r="R143" s="83" t="s">
         <v>610</v>
       </c>
-      <c r="S143" s="64">
+      <c r="S143" s="85">
         <v>332</v>
       </c>
       <c r="T143" s="5" t="s">
@@ -13890,14 +13910,14 @@
       <c r="O144" s="59" t="s">
         <v>450</v>
       </c>
-      <c r="P144" s="68" t="s">
+      <c r="P144" s="64" t="s">
         <v>816</v>
       </c>
-      <c r="Q144" s="69"/>
-      <c r="R144" s="59" t="s">
+      <c r="Q144" s="65"/>
+      <c r="R144" s="83" t="s">
         <v>611</v>
       </c>
-      <c r="S144" s="64">
+      <c r="S144" s="85">
         <v>345</v>
       </c>
       <c r="T144" s="5" t="s">
@@ -13950,14 +13970,14 @@
       <c r="O145" s="59" t="s">
         <v>451</v>
       </c>
-      <c r="P145" s="68" t="s">
+      <c r="P145" s="64" t="s">
         <v>451</v>
       </c>
-      <c r="Q145" s="69"/>
-      <c r="R145" s="59" t="s">
+      <c r="Q145" s="65"/>
+      <c r="R145" s="83" t="s">
         <v>612</v>
       </c>
-      <c r="S145" s="64">
+      <c r="S145" s="85">
         <v>340</v>
       </c>
       <c r="T145" s="5" t="s">
@@ -14010,12 +14030,12 @@
       <c r="O146" s="59" t="s">
         <v>452</v>
       </c>
-      <c r="P146" s="68" t="s">
+      <c r="P146" s="64" t="s">
         <v>452</v>
       </c>
-      <c r="Q146" s="69"/>
-      <c r="R146" s="59"/>
-      <c r="S146" s="59"/>
+      <c r="Q146" s="65"/>
+      <c r="R146" s="83"/>
+      <c r="S146" s="83"/>
       <c r="T146" s="5" t="s">
         <v>259</v>
       </c>
@@ -14066,12 +14086,12 @@
       <c r="O147" s="59" t="s">
         <v>453</v>
       </c>
-      <c r="P147" s="68" t="s">
+      <c r="P147" s="64" t="s">
         <v>453</v>
       </c>
-      <c r="Q147" s="69"/>
-      <c r="R147" s="59"/>
-      <c r="S147" s="59"/>
+      <c r="Q147" s="65"/>
+      <c r="R147" s="83"/>
+      <c r="S147" s="83"/>
       <c r="T147" s="5" t="s">
         <v>260</v>
       </c>
@@ -14086,7 +14106,7 @@
       </c>
       <c r="X147" s="2"/>
     </row>
-    <row r="148" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:24" ht="51" x14ac:dyDescent="0.25">
       <c r="A148" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.06. - Other neurological conditions</v>
@@ -14113,7 +14133,7 @@
         <v>D06</v>
       </c>
       <c r="I148" s="57" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="J148" s="18" t="s">
         <v>1160</v>
@@ -14122,21 +14142,21 @@
         <v>1200</v>
       </c>
       <c r="L148" s="58" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="M148" s="58"/>
       <c r="N148" s="58"/>
       <c r="O148" s="59" t="s">
         <v>454</v>
       </c>
-      <c r="P148" s="68" t="s">
+      <c r="P148" s="64" t="s">
         <v>817</v>
       </c>
-      <c r="Q148" s="69"/>
-      <c r="R148" s="59" t="s">
+      <c r="Q148" s="65"/>
+      <c r="R148" s="83" t="s">
         <v>613</v>
       </c>
-      <c r="S148" s="59" t="s">
+      <c r="S148" s="83" t="s">
         <v>1103</v>
       </c>
       <c r="T148" s="5" t="s">
@@ -14186,12 +14206,12 @@
       <c r="O149" s="59" t="s">
         <v>455</v>
       </c>
-      <c r="P149" s="66" t="s">
+      <c r="P149" s="62" t="s">
         <v>818</v>
       </c>
-      <c r="Q149" s="67"/>
-      <c r="R149" s="59"/>
-      <c r="S149" s="62"/>
+      <c r="Q149" s="63"/>
+      <c r="R149" s="83"/>
+      <c r="S149" s="84"/>
       <c r="T149" s="2" t="s">
         <v>262</v>
       </c>
@@ -14244,12 +14264,12 @@
       <c r="O150" s="59" t="s">
         <v>456</v>
       </c>
-      <c r="P150" s="68" t="s">
+      <c r="P150" s="64" t="s">
         <v>456</v>
       </c>
-      <c r="Q150" s="69"/>
-      <c r="R150" s="59"/>
-      <c r="S150" s="59"/>
+      <c r="Q150" s="65"/>
+      <c r="R150" s="83"/>
+      <c r="S150" s="83"/>
       <c r="T150" s="5" t="s">
         <v>263</v>
       </c>
@@ -14300,12 +14320,12 @@
       <c r="O151" s="59" t="s">
         <v>457</v>
       </c>
-      <c r="P151" s="68" t="s">
+      <c r="P151" s="64" t="s">
         <v>819</v>
       </c>
-      <c r="Q151" s="69"/>
-      <c r="R151" s="59"/>
-      <c r="S151" s="59"/>
+      <c r="Q151" s="65"/>
+      <c r="R151" s="83"/>
+      <c r="S151" s="83"/>
       <c r="T151" s="5" t="s">
         <v>264</v>
       </c>
@@ -14356,12 +14376,12 @@
       <c r="O152" s="59" t="s">
         <v>458</v>
       </c>
-      <c r="P152" s="68" t="s">
+      <c r="P152" s="64" t="s">
         <v>820</v>
       </c>
-      <c r="Q152" s="69"/>
-      <c r="R152" s="59"/>
-      <c r="S152" s="59"/>
+      <c r="Q152" s="65"/>
+      <c r="R152" s="83"/>
+      <c r="S152" s="83"/>
       <c r="T152" s="5" t="s">
         <v>265</v>
       </c>
@@ -14412,12 +14432,12 @@
       <c r="O153" s="59" t="s">
         <v>459</v>
       </c>
-      <c r="P153" s="68" t="s">
+      <c r="P153" s="64" t="s">
         <v>821</v>
       </c>
-      <c r="Q153" s="69"/>
-      <c r="R153" s="59"/>
-      <c r="S153" s="59"/>
+      <c r="Q153" s="65"/>
+      <c r="R153" s="83"/>
+      <c r="S153" s="83"/>
       <c r="T153" s="5" t="s">
         <v>266</v>
       </c>
@@ -14468,12 +14488,12 @@
       <c r="O154" s="59" t="s">
         <v>460</v>
       </c>
-      <c r="P154" s="68" t="s">
+      <c r="P154" s="64" t="s">
         <v>822</v>
       </c>
-      <c r="Q154" s="69"/>
-      <c r="R154" s="59"/>
-      <c r="S154" s="59"/>
+      <c r="Q154" s="65"/>
+      <c r="R154" s="83"/>
+      <c r="S154" s="83"/>
       <c r="T154" s="5" t="s">
         <v>267</v>
       </c>
@@ -14524,12 +14544,12 @@
       <c r="O155" s="59" t="s">
         <v>461</v>
       </c>
-      <c r="P155" s="68" t="s">
+      <c r="P155" s="64" t="s">
         <v>823</v>
       </c>
-      <c r="Q155" s="69"/>
-      <c r="R155" s="59"/>
-      <c r="S155" s="59"/>
+      <c r="Q155" s="65"/>
+      <c r="R155" s="83"/>
+      <c r="S155" s="83"/>
       <c r="T155" s="5" t="s">
         <v>268</v>
       </c>
@@ -14580,12 +14600,12 @@
       <c r="O156" s="59" t="s">
         <v>462</v>
       </c>
-      <c r="P156" s="68" t="s">
+      <c r="P156" s="64" t="s">
         <v>824</v>
       </c>
-      <c r="Q156" s="69"/>
-      <c r="R156" s="59"/>
-      <c r="S156" s="59"/>
+      <c r="Q156" s="65"/>
+      <c r="R156" s="83"/>
+      <c r="S156" s="83"/>
       <c r="T156" s="5" t="s">
         <v>269</v>
       </c>
@@ -14602,7 +14622,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="57.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A157" s="44" t="str">
         <f t="shared" si="12"/>
         <v>..C. - Cardiovascular diseases</v>
@@ -14636,14 +14656,14 @@
       <c r="O157" s="59" t="s">
         <v>463</v>
       </c>
-      <c r="P157" s="66" t="s">
+      <c r="P157" s="62" t="s">
         <v>825</v>
       </c>
-      <c r="Q157" s="67"/>
-      <c r="R157" s="59" t="s">
+      <c r="Q157" s="63"/>
+      <c r="R157" s="83" t="s">
         <v>616</v>
       </c>
-      <c r="S157" s="59" t="s">
+      <c r="S157" s="83" t="s">
         <v>681</v>
       </c>
       <c r="T157" s="2" t="s">
@@ -14695,19 +14715,19 @@
         <v>464</v>
       </c>
       <c r="N158" s="49" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="O158" s="59" t="s">
         <v>464</v>
       </c>
-      <c r="P158" s="68" t="s">
+      <c r="P158" s="64" t="s">
         <v>826</v>
       </c>
-      <c r="Q158" s="69"/>
-      <c r="R158" s="59" t="s">
+      <c r="Q158" s="65"/>
+      <c r="R158" s="83" t="s">
         <v>617</v>
       </c>
-      <c r="S158" s="59" t="s">
+      <c r="S158" s="83" t="s">
         <v>1052</v>
       </c>
       <c r="T158" s="5" t="s">
@@ -14767,14 +14787,14 @@
       <c r="O159" s="59" t="s">
         <v>465</v>
       </c>
-      <c r="P159" s="68" t="s">
+      <c r="P159" s="64" t="s">
         <v>827</v>
       </c>
-      <c r="Q159" s="69"/>
-      <c r="R159" s="59" t="s">
+      <c r="Q159" s="65"/>
+      <c r="R159" s="83" t="s">
         <v>618</v>
       </c>
-      <c r="S159" s="64">
+      <c r="S159" s="85">
         <v>402</v>
       </c>
       <c r="T159" s="5" t="s">
@@ -14834,14 +14854,14 @@
       <c r="O160" s="59" t="s">
         <v>466</v>
       </c>
-      <c r="P160" s="68" t="s">
+      <c r="P160" s="64" t="s">
         <v>828</v>
       </c>
-      <c r="Q160" s="69"/>
-      <c r="R160" s="59" t="s">
+      <c r="Q160" s="65"/>
+      <c r="R160" s="83" t="s">
         <v>619</v>
       </c>
-      <c r="S160" s="59" t="s">
+      <c r="S160" s="83" t="s">
         <v>1029</v>
       </c>
       <c r="T160" s="5" t="s">
@@ -14858,7 +14878,7 @@
       </c>
       <c r="X160" s="2"/>
     </row>
-    <row r="161" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.03. - Stroke</v>
@@ -14900,19 +14920,19 @@
         <v>1226</v>
       </c>
       <c r="N161" s="49" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="O161" s="59" t="s">
         <v>467</v>
       </c>
-      <c r="P161" s="68" t="s">
+      <c r="P161" s="64" t="s">
         <v>829</v>
       </c>
-      <c r="Q161" s="69"/>
-      <c r="R161" s="59" t="s">
+      <c r="Q161" s="65"/>
+      <c r="R161" s="83" t="s">
         <v>620</v>
       </c>
-      <c r="S161" s="59" t="s">
+      <c r="S161" s="83" t="s">
         <v>1056</v>
       </c>
       <c r="T161" s="5" t="s">
@@ -14964,22 +14984,22 @@
         <v>830</v>
       </c>
       <c r="M162" s="49" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="N162" s="49" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="O162" s="59" t="s">
         <v>468</v>
       </c>
-      <c r="P162" s="68" t="s">
+      <c r="P162" s="64" t="s">
         <v>830</v>
       </c>
-      <c r="Q162" s="69"/>
-      <c r="R162" s="59" t="s">
+      <c r="Q162" s="65"/>
+      <c r="R162" s="83" t="s">
         <v>621</v>
       </c>
-      <c r="S162" s="59" t="s">
+      <c r="S162" s="83" t="s">
         <v>1057</v>
       </c>
       <c r="T162" s="5" t="s">
@@ -14994,8 +15014,8 @@
       <c r="W162" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="X162" s="81" t="s">
-        <v>1349</v>
+      <c r="X162" s="76" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="163" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
@@ -15021,30 +15041,30 @@
         <v>C05</v>
       </c>
       <c r="I163" s="5" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>1212</v>
       </c>
       <c r="K163" s="5" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="L163" s="49" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="M163" s="49" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="N163" s="49" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="O163" s="59"/>
-      <c r="P163" s="68"/>
-      <c r="Q163" s="69"/>
-      <c r="R163" s="59"/>
-      <c r="S163" s="59"/>
+      <c r="P163" s="64"/>
+      <c r="Q163" s="65"/>
+      <c r="R163" s="83"/>
+      <c r="S163" s="83"/>
       <c r="T163" s="5" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="U163" s="50"/>
       <c r="V163" s="5"/>
@@ -15078,38 +15098,38 @@
         <v>C99</v>
       </c>
       <c r="I164" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J164" s="5" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K164" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L164" s="19" t="s">
         <v>1325</v>
       </c>
-      <c r="J164" s="5" t="s">
-        <v>1326</v>
-      </c>
-      <c r="K164" s="5" t="s">
-        <v>1327</v>
-      </c>
-      <c r="L164" s="19" t="s">
-        <v>1328</v>
-      </c>
       <c r="M164" s="19" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="N164" s="19" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="O164" s="59" t="s">
         <v>469</v>
       </c>
-      <c r="P164" s="68" t="s">
+      <c r="P164" s="64" t="s">
         <v>831</v>
       </c>
-      <c r="Q164" s="69"/>
-      <c r="R164" s="59" t="s">
+      <c r="Q164" s="65"/>
+      <c r="R164" s="83" t="s">
         <v>622</v>
       </c>
-      <c r="S164" s="59" t="s">
+      <c r="S164" s="83" t="s">
         <v>1102</v>
       </c>
-      <c r="T164" s="79" t="s">
-        <v>1323</v>
+      <c r="T164" s="74" t="s">
+        <v>1320</v>
       </c>
       <c r="U164" s="52" t="s">
         <v>99</v>
@@ -15120,11 +15140,11 @@
       <c r="W164" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="X164" s="81" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="165" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="X164" s="76" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15157,14 +15177,14 @@
       <c r="O165" s="59" t="s">
         <v>470</v>
       </c>
-      <c r="P165" s="66" t="s">
+      <c r="P165" s="62" t="s">
         <v>832</v>
       </c>
-      <c r="Q165" s="67"/>
-      <c r="R165" s="59" t="s">
+      <c r="Q165" s="63"/>
+      <c r="R165" s="83" t="s">
         <v>623</v>
       </c>
-      <c r="S165" s="59" t="s">
+      <c r="S165" s="83" t="s">
         <v>680</v>
       </c>
       <c r="T165" s="2" t="s">
@@ -15195,8 +15215,8 @@
       <c r="D166" s="27" t="s">
         <v>1141</v>
       </c>
-      <c r="E166" s="83" t="s">
-        <v>1354</v>
+      <c r="E166" s="78" t="s">
+        <v>1351</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="40" t="str">
@@ -15220,14 +15240,14 @@
       <c r="O166" s="59" t="s">
         <v>471</v>
       </c>
-      <c r="P166" s="68" t="s">
+      <c r="P166" s="64" t="s">
         <v>833</v>
       </c>
-      <c r="Q166" s="69"/>
-      <c r="R166" s="59" t="s">
+      <c r="Q166" s="65"/>
+      <c r="R166" s="83" t="s">
         <v>624</v>
       </c>
-      <c r="S166" s="59" t="s">
+      <c r="S166" s="83" t="s">
         <v>1028</v>
       </c>
       <c r="T166" s="5" t="s">
@@ -15258,8 +15278,8 @@
       <c r="D167" s="27" t="s">
         <v>1141</v>
       </c>
-      <c r="E167" s="83" t="s">
-        <v>1355</v>
+      <c r="E167" s="78" t="s">
+        <v>1352</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="40" t="str">
@@ -15283,14 +15303,14 @@
       <c r="O167" s="59" t="s">
         <v>472</v>
       </c>
-      <c r="P167" s="68" t="s">
+      <c r="P167" s="64" t="s">
         <v>834</v>
       </c>
-      <c r="Q167" s="69"/>
-      <c r="R167" s="59" t="s">
+      <c r="Q167" s="65"/>
+      <c r="R167" s="83" t="s">
         <v>625</v>
       </c>
-      <c r="S167" s="64">
+      <c r="S167" s="85">
         <v>493</v>
       </c>
       <c r="T167" s="5" t="s">
@@ -15307,7 +15327,7 @@
       </c>
       <c r="X167" s="2"/>
     </row>
-    <row r="168" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.68. - Other respiratory diseases</v>
@@ -15316,13 +15336,13 @@
         <v>157</v>
       </c>
       <c r="C168" s="31" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="D168" s="27" t="s">
         <v>1141</v>
       </c>
-      <c r="E168" s="83" t="s">
-        <v>1356</v>
+      <c r="E168" s="78" t="s">
+        <v>1353</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="40" t="str">
@@ -15346,14 +15366,14 @@
       <c r="O168" s="59" t="s">
         <v>473</v>
       </c>
-      <c r="P168" s="68" t="s">
+      <c r="P168" s="64" t="s">
         <v>835</v>
       </c>
-      <c r="Q168" s="69"/>
-      <c r="R168" s="59" t="s">
+      <c r="Q168" s="65"/>
+      <c r="R168" s="83" t="s">
         <v>626</v>
       </c>
-      <c r="S168" s="59" t="s">
+      <c r="S168" s="83" t="s">
         <v>1055</v>
       </c>
       <c r="T168" s="5" t="s">
@@ -15370,7 +15390,7 @@
       </c>
       <c r="X168" s="2"/>
     </row>
-    <row r="169" spans="1:24" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.09. - Digestive diseases (excluding cirrhosis)</v>
@@ -15408,21 +15428,21 @@
       <c r="O169" s="59" t="s">
         <v>474</v>
       </c>
-      <c r="P169" s="66" t="s">
+      <c r="P169" s="62" t="s">
         <v>836</v>
       </c>
-      <c r="Q169" s="67"/>
-      <c r="R169" s="59" t="s">
+      <c r="Q169" s="63"/>
+      <c r="R169" s="83" t="s">
         <v>627</v>
       </c>
-      <c r="S169" s="59" t="s">
+      <c r="S169" s="83" t="s">
         <v>682</v>
       </c>
-      <c r="T169" s="81" t="s">
-        <v>1332</v>
+      <c r="T169" s="76" t="s">
+        <v>1329</v>
       </c>
       <c r="U169" s="20" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="V169" s="2" t="s">
         <v>281</v>
@@ -15468,14 +15488,14 @@
       <c r="O170" s="59" t="s">
         <v>475</v>
       </c>
-      <c r="P170" s="68" t="s">
+      <c r="P170" s="64" t="s">
         <v>837</v>
       </c>
-      <c r="Q170" s="69"/>
-      <c r="R170" s="59" t="s">
+      <c r="Q170" s="65"/>
+      <c r="R170" s="83" t="s">
         <v>628</v>
       </c>
-      <c r="S170" s="59" t="s">
+      <c r="S170" s="83" t="s">
         <v>1027</v>
       </c>
       <c r="T170" s="5" t="s">
@@ -15492,7 +15512,7 @@
       </c>
       <c r="X170" s="2"/>
     </row>
-    <row r="171" spans="1:24" s="48" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:24" s="48" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A171" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.11. - Cirrhosis of the liver</v>
@@ -15535,14 +15555,14 @@
       <c r="O171" s="59" t="s">
         <v>476</v>
       </c>
-      <c r="P171" s="68" t="s">
+      <c r="P171" s="64" t="s">
         <v>838</v>
       </c>
-      <c r="Q171" s="68"/>
-      <c r="R171" s="59" t="s">
+      <c r="Q171" s="64"/>
+      <c r="R171" s="83" t="s">
         <v>629</v>
       </c>
-      <c r="S171" s="59" t="s">
+      <c r="S171" s="83" t="s">
         <v>1101</v>
       </c>
       <c r="T171" s="5" t="s">
@@ -15595,14 +15615,14 @@
       <c r="O172" s="59" t="s">
         <v>477</v>
       </c>
-      <c r="P172" s="68" t="s">
+      <c r="P172" s="64" t="s">
         <v>839</v>
       </c>
-      <c r="Q172" s="69"/>
-      <c r="R172" s="59" t="s">
+      <c r="Q172" s="65"/>
+      <c r="R172" s="83" t="s">
         <v>630</v>
       </c>
-      <c r="S172" s="59" t="s">
+      <c r="S172" s="83" t="s">
         <v>1022</v>
       </c>
       <c r="T172" s="5" t="s">
@@ -15655,14 +15675,14 @@
       <c r="O173" s="59" t="s">
         <v>840</v>
       </c>
-      <c r="P173" s="68" t="s">
+      <c r="P173" s="64" t="s">
         <v>840</v>
       </c>
-      <c r="Q173" s="69"/>
-      <c r="R173" s="59" t="s">
+      <c r="Q173" s="65"/>
+      <c r="R173" s="83" t="s">
         <v>631</v>
       </c>
-      <c r="S173" s="64">
+      <c r="S173" s="85">
         <v>535</v>
       </c>
       <c r="T173" s="5" t="s">
@@ -15715,14 +15735,14 @@
       <c r="O174" s="59" t="s">
         <v>841</v>
       </c>
-      <c r="P174" s="68" t="s">
+      <c r="P174" s="64" t="s">
         <v>841</v>
       </c>
-      <c r="Q174" s="69"/>
-      <c r="R174" s="59" t="s">
+      <c r="Q174" s="65"/>
+      <c r="R174" s="83" t="s">
         <v>632</v>
       </c>
-      <c r="S174" s="59" t="s">
+      <c r="S174" s="83" t="s">
         <v>1023</v>
       </c>
       <c r="T174" s="5" t="s">
@@ -15775,14 +15795,14 @@
       <c r="O175" s="59" t="s">
         <v>988</v>
       </c>
-      <c r="P175" s="68" t="s">
+      <c r="P175" s="64" t="s">
         <v>842</v>
       </c>
-      <c r="Q175" s="69"/>
-      <c r="R175" s="59" t="s">
+      <c r="Q175" s="65"/>
+      <c r="R175" s="83" t="s">
         <v>633</v>
       </c>
-      <c r="S175" s="59" t="s">
+      <c r="S175" s="83" t="s">
         <v>1026</v>
       </c>
       <c r="T175" s="5" t="s">
@@ -15835,14 +15855,14 @@
       <c r="O176" s="59" t="s">
         <v>989</v>
       </c>
-      <c r="P176" s="68" t="s">
+      <c r="P176" s="64" t="s">
         <v>843</v>
       </c>
-      <c r="Q176" s="69"/>
-      <c r="R176" s="59" t="s">
+      <c r="Q176" s="65"/>
+      <c r="R176" s="83" t="s">
         <v>634</v>
       </c>
-      <c r="S176" s="59" t="s">
+      <c r="S176" s="83" t="s">
         <v>1025</v>
       </c>
       <c r="T176" s="5" t="s">
@@ -15895,14 +15915,14 @@
       <c r="O177" s="59" t="s">
         <v>990</v>
       </c>
-      <c r="P177" s="68" t="s">
+      <c r="P177" s="64" t="s">
         <v>844</v>
       </c>
-      <c r="Q177" s="69"/>
-      <c r="R177" s="59" t="s">
+      <c r="Q177" s="65"/>
+      <c r="R177" s="83" t="s">
         <v>635</v>
       </c>
-      <c r="S177" s="59" t="s">
+      <c r="S177" s="83" t="s">
         <v>1024</v>
       </c>
       <c r="T177" s="5" t="s">
@@ -15919,7 +15939,7 @@
       </c>
       <c r="X177" s="2"/>
     </row>
-    <row r="178" spans="1:24" ht="51" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15959,14 +15979,14 @@
       <c r="O178" s="59" t="s">
         <v>991</v>
       </c>
-      <c r="P178" s="68" t="s">
+      <c r="P178" s="64" t="s">
         <v>845</v>
       </c>
-      <c r="Q178" s="69"/>
-      <c r="R178" s="59" t="s">
+      <c r="Q178" s="65"/>
+      <c r="R178" s="83" t="s">
         <v>636</v>
       </c>
-      <c r="S178" s="59" t="s">
+      <c r="S178" s="83" t="s">
         <v>1054</v>
       </c>
       <c r="T178" s="5" t="s">
@@ -16014,14 +16034,14 @@
       <c r="O179" s="59" t="s">
         <v>953</v>
       </c>
-      <c r="P179" s="66" t="s">
+      <c r="P179" s="62" t="s">
         <v>958</v>
       </c>
-      <c r="Q179" s="66"/>
-      <c r="R179" s="59" t="s">
+      <c r="Q179" s="62"/>
+      <c r="R179" s="83" t="s">
         <v>678</v>
       </c>
-      <c r="S179" s="62" t="s">
+      <c r="S179" s="84" t="s">
         <v>679</v>
       </c>
       <c r="T179" s="2" t="s">
@@ -16078,14 +16098,14 @@
       <c r="O180" s="59" t="s">
         <v>954</v>
       </c>
-      <c r="P180" s="68" t="s">
+      <c r="P180" s="64" t="s">
         <v>846</v>
       </c>
-      <c r="Q180" s="68"/>
-      <c r="R180" s="59" t="s">
+      <c r="Q180" s="64"/>
+      <c r="R180" s="83" t="s">
         <v>637</v>
       </c>
-      <c r="S180" s="59" t="s">
+      <c r="S180" s="83" t="s">
         <v>1021</v>
       </c>
       <c r="T180" s="5" t="s">
@@ -16145,14 +16165,14 @@
       <c r="O181" s="59" t="s">
         <v>955</v>
       </c>
-      <c r="P181" s="68" t="s">
+      <c r="P181" s="64" t="s">
         <v>847</v>
       </c>
-      <c r="Q181" s="69"/>
-      <c r="R181" s="59" t="s">
+      <c r="Q181" s="65"/>
+      <c r="R181" s="83" t="s">
         <v>638</v>
       </c>
-      <c r="S181" s="64">
+      <c r="S181" s="85">
         <v>580</v>
       </c>
       <c r="T181" s="5" t="s">
@@ -16212,14 +16232,14 @@
       <c r="O182" s="59" t="s">
         <v>956</v>
       </c>
-      <c r="P182" s="68" t="s">
+      <c r="P182" s="64" t="s">
         <v>848</v>
       </c>
-      <c r="Q182" s="69"/>
-      <c r="R182" s="59" t="s">
+      <c r="Q182" s="65"/>
+      <c r="R182" s="83" t="s">
         <v>639</v>
       </c>
-      <c r="S182" s="64">
+      <c r="S182" s="85">
         <v>2504</v>
       </c>
       <c r="T182" s="5" t="s">
@@ -16279,14 +16299,14 @@
       <c r="O183" s="59" t="s">
         <v>957</v>
       </c>
-      <c r="P183" s="68" t="s">
+      <c r="P183" s="64" t="s">
         <v>959</v>
       </c>
-      <c r="Q183" s="69"/>
-      <c r="R183" s="59" t="s">
+      <c r="Q183" s="65"/>
+      <c r="R183" s="83" t="s">
         <v>640</v>
       </c>
-      <c r="S183" s="64">
+      <c r="S183" s="85">
         <v>589</v>
       </c>
       <c r="T183" s="5" t="s">
@@ -16339,12 +16359,12 @@
       <c r="O184" s="59" t="s">
         <v>478</v>
       </c>
-      <c r="P184" s="68" t="s">
+      <c r="P184" s="64" t="s">
         <v>478</v>
       </c>
-      <c r="Q184" s="69"/>
-      <c r="R184" s="59"/>
-      <c r="S184" s="59"/>
+      <c r="Q184" s="65"/>
+      <c r="R184" s="83"/>
+      <c r="S184" s="83"/>
       <c r="T184" s="5" t="s">
         <v>884</v>
       </c>
@@ -16395,14 +16415,14 @@
       <c r="O185" s="59" t="s">
         <v>479</v>
       </c>
-      <c r="P185" s="68" t="s">
+      <c r="P185" s="64" t="s">
         <v>849</v>
       </c>
-      <c r="Q185" s="69"/>
-      <c r="R185" s="59" t="s">
+      <c r="Q185" s="65"/>
+      <c r="R185" s="83" t="s">
         <v>641</v>
       </c>
-      <c r="S185" s="59" t="s">
+      <c r="S185" s="83" t="s">
         <v>1017</v>
       </c>
       <c r="T185" s="5" t="s">
@@ -16419,7 +16439,7 @@
       </c>
       <c r="X185" s="2"/>
     </row>
-    <row r="186" spans="1:24" ht="33" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:24" ht="24" x14ac:dyDescent="0.25">
       <c r="A186" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16455,14 +16475,14 @@
       <c r="O186" s="59" t="s">
         <v>480</v>
       </c>
-      <c r="P186" s="68" t="s">
+      <c r="P186" s="64" t="s">
         <v>850</v>
       </c>
-      <c r="Q186" s="69"/>
-      <c r="R186" s="59" t="s">
+      <c r="Q186" s="65"/>
+      <c r="R186" s="83" t="s">
         <v>1018</v>
       </c>
-      <c r="S186" s="59" t="s">
+      <c r="S186" s="83" t="s">
         <v>1053</v>
       </c>
       <c r="T186" s="5" t="s">
@@ -16515,14 +16535,14 @@
       <c r="O187" s="59" t="s">
         <v>481</v>
       </c>
-      <c r="P187" s="68" t="s">
+      <c r="P187" s="64" t="s">
         <v>851</v>
       </c>
-      <c r="Q187" s="69"/>
-      <c r="R187" s="59" t="s">
+      <c r="Q187" s="65"/>
+      <c r="R187" s="83" t="s">
         <v>1019</v>
       </c>
-      <c r="S187" s="59" t="s">
+      <c r="S187" s="83" t="s">
         <v>1020</v>
       </c>
       <c r="T187" s="5" t="s">
@@ -16575,14 +16595,14 @@
       <c r="O188" s="59" t="s">
         <v>482</v>
       </c>
-      <c r="P188" s="68" t="s">
+      <c r="P188" s="64" t="s">
         <v>852</v>
       </c>
-      <c r="Q188" s="69"/>
-      <c r="R188" s="59" t="s">
+      <c r="Q188" s="65"/>
+      <c r="R188" s="83" t="s">
         <v>642</v>
       </c>
-      <c r="S188" s="59" t="s">
+      <c r="S188" s="83" t="s">
         <v>1016</v>
       </c>
       <c r="T188" s="5" t="s">
@@ -16633,14 +16653,14 @@
       <c r="O189" s="59" t="s">
         <v>483</v>
       </c>
-      <c r="P189" s="68" t="s">
+      <c r="P189" s="64" t="s">
         <v>853</v>
       </c>
-      <c r="Q189" s="69"/>
-      <c r="R189" s="59" t="s">
+      <c r="Q189" s="65"/>
+      <c r="R189" s="83" t="s">
         <v>644</v>
       </c>
-      <c r="S189" s="59" t="s">
+      <c r="S189" s="83" t="s">
         <v>643</v>
       </c>
       <c r="T189" s="5" t="s">
@@ -16657,7 +16677,7 @@
       </c>
       <c r="X189" s="2"/>
     </row>
-    <row r="190" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16692,14 +16712,14 @@
       <c r="O190" s="59" t="s">
         <v>484</v>
       </c>
-      <c r="P190" s="66" t="s">
+      <c r="P190" s="62" t="s">
         <v>854</v>
       </c>
-      <c r="Q190" s="67"/>
-      <c r="R190" s="59" t="s">
+      <c r="Q190" s="63"/>
+      <c r="R190" s="83" t="s">
         <v>645</v>
       </c>
-      <c r="S190" s="59" t="s">
+      <c r="S190" s="83" t="s">
         <v>677</v>
       </c>
       <c r="T190" s="2" t="s">
@@ -16752,14 +16772,14 @@
       <c r="O191" s="59" t="s">
         <v>485</v>
       </c>
-      <c r="P191" s="68" t="s">
+      <c r="P191" s="64" t="s">
         <v>855</v>
       </c>
-      <c r="Q191" s="69"/>
-      <c r="R191" s="59" t="s">
+      <c r="Q191" s="65"/>
+      <c r="R191" s="83" t="s">
         <v>646</v>
       </c>
-      <c r="S191" s="59" t="s">
+      <c r="S191" s="83" t="s">
         <v>1014</v>
       </c>
       <c r="T191" s="5" t="s">
@@ -16812,12 +16832,12 @@
       <c r="O192" s="59" t="s">
         <v>486</v>
       </c>
-      <c r="P192" s="68" t="s">
+      <c r="P192" s="64" t="s">
         <v>856</v>
       </c>
-      <c r="Q192" s="69"/>
-      <c r="R192" s="59"/>
-      <c r="S192" s="59"/>
+      <c r="Q192" s="65"/>
+      <c r="R192" s="83"/>
+      <c r="S192" s="83"/>
       <c r="T192" s="5" t="s">
         <v>294</v>
       </c>
@@ -16868,12 +16888,12 @@
       <c r="O193" s="59" t="s">
         <v>487</v>
       </c>
-      <c r="P193" s="68" t="s">
+      <c r="P193" s="64" t="s">
         <v>487</v>
       </c>
-      <c r="Q193" s="69"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
+      <c r="Q193" s="65"/>
+      <c r="R193" s="83"/>
+      <c r="S193" s="83"/>
       <c r="T193" s="5" t="s">
         <v>295</v>
       </c>
@@ -16924,12 +16944,12 @@
       <c r="O194" s="59" t="s">
         <v>488</v>
       </c>
-      <c r="P194" s="68" t="s">
+      <c r="P194" s="64" t="s">
         <v>857</v>
       </c>
-      <c r="Q194" s="69"/>
-      <c r="R194" s="59"/>
-      <c r="S194" s="59"/>
+      <c r="Q194" s="65"/>
+      <c r="R194" s="83"/>
+      <c r="S194" s="83"/>
       <c r="T194" s="5" t="s">
         <v>296</v>
       </c>
@@ -16944,7 +16964,7 @@
       </c>
       <c r="X194" s="2"/>
     </row>
-    <row r="195" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A195" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16968,7 +16988,7 @@
       </c>
       <c r="H195" s="40"/>
       <c r="I195" s="5" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>1232</v>
@@ -16984,14 +17004,14 @@
       <c r="O195" s="59" t="s">
         <v>489</v>
       </c>
-      <c r="P195" s="68" t="s">
+      <c r="P195" s="64" t="s">
         <v>858</v>
       </c>
-      <c r="Q195" s="69"/>
-      <c r="R195" s="59" t="s">
+      <c r="Q195" s="65"/>
+      <c r="R195" s="83" t="s">
         <v>647</v>
       </c>
-      <c r="S195" s="59" t="s">
+      <c r="S195" s="83" t="s">
         <v>1015</v>
       </c>
       <c r="T195" s="5" t="s">
@@ -17010,7 +17030,7 @@
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" s="44" t="str">
-        <f t="shared" ref="A196:A233" si="19">IF(H196&lt;&gt;"",IF(F196&lt;&gt;"",CONCATENATE("....",D196,".",E196,".",F196,". - ",T196),IF(E196&lt;&gt;"",CONCATENATE("...",D196,".",E196,". - ",T196),CONCATENATE("..",D196,". - ",T196))),"")</f>
+        <f t="shared" ref="A196:A232" si="19">IF(H196&lt;&gt;"",IF(F196&lt;&gt;"",CONCATENATE("....",D196,".",E196,".",F196,". - ",T196),IF(E196&lt;&gt;"",CONCATENATE("...",D196,".",E196,". - ",T196),CONCATENATE("..",D196,". - ",T196))),"")</f>
         <v>...D.12. - Congenital anomalies</v>
       </c>
       <c r="B196" s="2">
@@ -17046,14 +17066,14 @@
       <c r="O196" s="59" t="s">
         <v>490</v>
       </c>
-      <c r="P196" s="66" t="s">
+      <c r="P196" s="62" t="s">
         <v>859</v>
       </c>
-      <c r="Q196" s="67"/>
-      <c r="R196" s="59" t="s">
+      <c r="Q196" s="63"/>
+      <c r="R196" s="83" t="s">
         <v>649</v>
       </c>
-      <c r="S196" s="59" t="s">
+      <c r="S196" s="83" t="s">
         <v>648</v>
       </c>
       <c r="T196" s="2" t="s">
@@ -17106,14 +17126,14 @@
       <c r="O197" s="59" t="s">
         <v>491</v>
       </c>
-      <c r="P197" s="68" t="s">
+      <c r="P197" s="64" t="s">
         <v>860</v>
       </c>
-      <c r="Q197" s="69"/>
-      <c r="R197" s="59" t="s">
+      <c r="Q197" s="65"/>
+      <c r="R197" s="83" t="s">
         <v>650</v>
       </c>
-      <c r="S197" s="59" t="s">
+      <c r="S197" s="83" t="s">
         <v>1007</v>
       </c>
       <c r="T197" s="5" t="s">
@@ -17166,14 +17186,14 @@
       <c r="O198" s="59" t="s">
         <v>492</v>
       </c>
-      <c r="P198" s="68" t="s">
+      <c r="P198" s="64" t="s">
         <v>861</v>
       </c>
-      <c r="Q198" s="69"/>
-      <c r="R198" s="59" t="s">
+      <c r="Q198" s="65"/>
+      <c r="R198" s="83" t="s">
         <v>651</v>
       </c>
-      <c r="S198" s="59" t="s">
+      <c r="S198" s="83" t="s">
         <v>1012</v>
       </c>
       <c r="T198" s="5" t="s">
@@ -17226,14 +17246,14 @@
       <c r="O199" s="59" t="s">
         <v>493</v>
       </c>
-      <c r="P199" s="68" t="s">
+      <c r="P199" s="64" t="s">
         <v>493</v>
       </c>
-      <c r="Q199" s="69"/>
-      <c r="R199" s="64">
+      <c r="Q199" s="65"/>
+      <c r="R199" s="85">
         <v>758</v>
       </c>
-      <c r="S199" s="64">
+      <c r="S199" s="85">
         <v>758</v>
       </c>
       <c r="T199" s="5" t="s">
@@ -17286,14 +17306,14 @@
       <c r="O200" s="59" t="s">
         <v>494</v>
       </c>
-      <c r="P200" s="68" t="s">
+      <c r="P200" s="64" t="s">
         <v>862</v>
       </c>
-      <c r="Q200" s="69"/>
-      <c r="R200" s="59" t="s">
+      <c r="Q200" s="65"/>
+      <c r="R200" s="83" t="s">
         <v>652</v>
       </c>
-      <c r="S200" s="59" t="s">
+      <c r="S200" s="83" t="s">
         <v>1010</v>
       </c>
       <c r="T200" s="5" t="s">
@@ -17346,14 +17366,14 @@
       <c r="O201" s="59" t="s">
         <v>495</v>
       </c>
-      <c r="P201" s="68" t="s">
+      <c r="P201" s="64" t="s">
         <v>863</v>
       </c>
-      <c r="Q201" s="69"/>
-      <c r="R201" s="59" t="s">
+      <c r="Q201" s="65"/>
+      <c r="R201" s="83" t="s">
         <v>1008</v>
       </c>
-      <c r="S201" s="59" t="s">
+      <c r="S201" s="83" t="s">
         <v>1009</v>
       </c>
       <c r="T201" s="5" t="s">
@@ -17406,14 +17426,14 @@
       <c r="O202" s="59" t="s">
         <v>496</v>
       </c>
-      <c r="P202" s="68" t="s">
+      <c r="P202" s="64" t="s">
         <v>864</v>
       </c>
-      <c r="Q202" s="69"/>
-      <c r="R202" s="59" t="s">
+      <c r="Q202" s="65"/>
+      <c r="R202" s="83" t="s">
         <v>653</v>
       </c>
-      <c r="S202" s="59" t="s">
+      <c r="S202" s="83" t="s">
         <v>1011</v>
       </c>
       <c r="T202" s="5" t="s">
@@ -17463,12 +17483,12 @@
       <c r="O203" s="59" t="s">
         <v>497</v>
       </c>
-      <c r="P203" s="66" t="s">
+      <c r="P203" s="62" t="s">
         <v>865</v>
       </c>
-      <c r="Q203" s="67"/>
-      <c r="R203" s="59"/>
-      <c r="S203" s="59"/>
+      <c r="Q203" s="63"/>
+      <c r="R203" s="83"/>
+      <c r="S203" s="83"/>
       <c r="T203" s="2" t="s">
         <v>305</v>
       </c>
@@ -17519,12 +17539,12 @@
       <c r="O204" s="59" t="s">
         <v>866</v>
       </c>
-      <c r="P204" s="70" t="s">
+      <c r="P204" s="66" t="s">
         <v>866</v>
       </c>
-      <c r="Q204" s="71"/>
-      <c r="R204" s="59"/>
-      <c r="S204" s="59"/>
+      <c r="Q204" s="67"/>
+      <c r="R204" s="83"/>
+      <c r="S204" s="83"/>
       <c r="T204" s="5" t="s">
         <v>306</v>
       </c>
@@ -17575,12 +17595,12 @@
       <c r="O205" s="59" t="s">
         <v>498</v>
       </c>
-      <c r="P205" s="68" t="s">
+      <c r="P205" s="64" t="s">
         <v>498</v>
       </c>
-      <c r="Q205" s="69"/>
-      <c r="R205" s="59"/>
-      <c r="S205" s="59"/>
+      <c r="Q205" s="65"/>
+      <c r="R205" s="83"/>
+      <c r="S205" s="83"/>
       <c r="T205" s="5" t="s">
         <v>307</v>
       </c>
@@ -17631,12 +17651,12 @@
       <c r="O206" s="59" t="s">
         <v>499</v>
       </c>
-      <c r="P206" s="68" t="s">
+      <c r="P206" s="64" t="s">
         <v>867</v>
       </c>
-      <c r="Q206" s="69"/>
-      <c r="R206" s="59"/>
-      <c r="S206" s="59"/>
+      <c r="Q206" s="65"/>
+      <c r="R206" s="83"/>
+      <c r="S206" s="83"/>
       <c r="T206" s="5" t="s">
         <v>308</v>
       </c>
@@ -17687,12 +17707,12 @@
       <c r="O207" s="59" t="s">
         <v>992</v>
       </c>
-      <c r="P207" s="68" t="s">
+      <c r="P207" s="64" t="s">
         <v>868</v>
       </c>
-      <c r="Q207" s="69"/>
-      <c r="R207" s="59"/>
-      <c r="S207" s="59"/>
+      <c r="Q207" s="65"/>
+      <c r="R207" s="83"/>
+      <c r="S207" s="83"/>
       <c r="T207" s="5" t="s">
         <v>882</v>
       </c>
@@ -17707,7 +17727,7 @@
       </c>
       <c r="X207" s="2"/>
     </row>
-    <row r="208" spans="1:24" ht="57.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" ht="24" x14ac:dyDescent="0.25">
       <c r="A208" s="44" t="str">
         <f t="shared" si="19"/>
         <v>..E. - Injuries</v>
@@ -17741,14 +17761,14 @@
       <c r="O208" s="59" t="s">
         <v>993</v>
       </c>
-      <c r="P208" s="66" t="s">
+      <c r="P208" s="62" t="s">
         <v>1115</v>
       </c>
-      <c r="Q208" s="66"/>
-      <c r="R208" s="60" t="s">
-        <v>1317</v>
-      </c>
-      <c r="S208" s="59" t="s">
+      <c r="Q208" s="62"/>
+      <c r="R208" s="86" t="s">
+        <v>1396</v>
+      </c>
+      <c r="S208" s="83" t="s">
         <v>654</v>
       </c>
       <c r="T208" s="2" t="s">
@@ -17765,7 +17785,7 @@
       </c>
       <c r="X208" s="2"/>
     </row>
-    <row r="209" spans="1:24" ht="41.25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.01. - Unintentional injuries</v>
@@ -17801,14 +17821,14 @@
       <c r="O209" s="59" t="s">
         <v>994</v>
       </c>
-      <c r="P209" s="66" t="s">
+      <c r="P209" s="62" t="s">
         <v>1114</v>
       </c>
-      <c r="Q209" s="66"/>
-      <c r="R209" s="59" t="s">
+      <c r="Q209" s="62"/>
+      <c r="R209" s="83" t="s">
         <v>655</v>
       </c>
-      <c r="S209" s="59" t="s">
+      <c r="S209" s="83" t="s">
         <v>676</v>
       </c>
       <c r="T209" s="2" t="s">
@@ -17825,7 +17845,7 @@
       </c>
       <c r="X209" s="2"/>
     </row>
-    <row r="210" spans="1:24" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:24" ht="36" x14ac:dyDescent="0.25">
       <c r="A210" s="44" t="str">
         <f t="shared" si="19"/>
         <v>....E.01.a. - Road injury</v>
@@ -17846,7 +17866,7 @@
         <v>1126</v>
       </c>
       <c r="G210" s="40" t="str">
-        <f t="shared" ref="G210:G220" si="21">CONCATENATE("c",D210,E210,F210)</f>
+        <f t="shared" ref="G210:G219" si="21">CONCATENATE("c",D210,E210,F210)</f>
         <v>cE01a</v>
       </c>
       <c r="H210" s="40" t="str">
@@ -17870,14 +17890,14 @@
       <c r="O210" s="59" t="s">
         <v>500</v>
       </c>
-      <c r="P210" s="68" t="s">
+      <c r="P210" s="64" t="s">
         <v>869</v>
       </c>
-      <c r="Q210" s="69"/>
-      <c r="R210" s="59" t="s">
+      <c r="Q210" s="65"/>
+      <c r="R210" s="83" t="s">
         <v>656</v>
       </c>
-      <c r="S210" s="59" t="s">
+      <c r="S210" s="83" t="s">
         <v>1004</v>
       </c>
       <c r="T210" s="5" t="s">
@@ -17901,7 +17921,7 @@
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="31" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>1142</v>
@@ -17922,21 +17942,21 @@
       </c>
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
-      <c r="K211" s="84" t="s">
-        <v>1391</v>
-      </c>
-      <c r="L211" s="85" t="s">
-        <v>1390</v>
+      <c r="K211" s="79" t="s">
+        <v>1386</v>
+      </c>
+      <c r="L211" s="80" t="s">
+        <v>1385</v>
       </c>
       <c r="M211" s="19"/>
       <c r="N211" s="19"/>
       <c r="O211" s="59"/>
-      <c r="P211" s="68"/>
-      <c r="Q211" s="69"/>
-      <c r="R211" s="59"/>
-      <c r="S211" s="59"/>
+      <c r="P211" s="64"/>
+      <c r="Q211" s="65"/>
+      <c r="R211" s="83"/>
+      <c r="S211" s="83"/>
       <c r="T211" s="5" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="U211" s="20"/>
       <c r="V211" s="5"/>
@@ -17946,13 +17966,13 @@
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.c. - Other poisonings</v>
+        <v>....E.01.c. - Poisonings (non-substance use)</v>
       </c>
       <c r="B212" s="2">
         <v>200</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>1142</v>
@@ -17973,29 +17993,29 @@
       </c>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
-      <c r="K212" s="84" t="s">
-        <v>1397</v>
-      </c>
-      <c r="L212" s="86" t="s">
-        <v>1396</v>
+      <c r="K212" s="79" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L212" s="81" t="s">
+        <v>1390</v>
       </c>
       <c r="M212" s="49"/>
       <c r="N212" s="49"/>
       <c r="O212" s="59" t="s">
         <v>1116</v>
       </c>
-      <c r="P212" s="68" t="s">
+      <c r="P212" s="64" t="s">
         <v>1117</v>
       </c>
-      <c r="Q212" s="69"/>
-      <c r="R212" s="59" t="s">
+      <c r="Q212" s="65"/>
+      <c r="R212" s="83" t="s">
         <v>657</v>
       </c>
-      <c r="S212" s="59" t="s">
+      <c r="S212" s="83" t="s">
         <v>1006</v>
       </c>
       <c r="T212" s="5" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="U212" s="20" t="s">
         <v>135</v>
@@ -18051,14 +18071,14 @@
       <c r="O213" s="59" t="s">
         <v>501</v>
       </c>
-      <c r="P213" s="68" t="s">
+      <c r="P213" s="64" t="s">
         <v>870</v>
       </c>
-      <c r="Q213" s="69"/>
-      <c r="R213" s="59" t="s">
+      <c r="Q213" s="65"/>
+      <c r="R213" s="83" t="s">
         <v>658</v>
       </c>
-      <c r="S213" s="59" t="s">
+      <c r="S213" s="83" t="s">
         <v>1005</v>
       </c>
       <c r="T213" s="5" t="s">
@@ -18111,14 +18131,14 @@
       <c r="O214" s="59" t="s">
         <v>502</v>
       </c>
-      <c r="P214" s="68" t="s">
+      <c r="P214" s="64" t="s">
         <v>871</v>
       </c>
-      <c r="Q214" s="69"/>
-      <c r="R214" s="59" t="s">
+      <c r="Q214" s="65"/>
+      <c r="R214" s="83" t="s">
         <v>659</v>
       </c>
-      <c r="S214" s="59" t="s">
+      <c r="S214" s="83" t="s">
         <v>1001</v>
       </c>
       <c r="T214" s="5" t="s">
@@ -18173,14 +18193,14 @@
       <c r="O215" s="59" t="s">
         <v>503</v>
       </c>
-      <c r="P215" s="68" t="s">
+      <c r="P215" s="64" t="s">
         <v>872</v>
       </c>
-      <c r="Q215" s="69"/>
-      <c r="R215" s="59" t="s">
+      <c r="Q215" s="65"/>
+      <c r="R215" s="83" t="s">
         <v>660</v>
       </c>
-      <c r="S215" s="59" t="s">
+      <c r="S215" s="83" t="s">
         <v>1000</v>
       </c>
       <c r="T215" s="5" t="s">
@@ -18225,24 +18245,24 @@
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="5" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="L216" s="49" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="M216" s="49"/>
       <c r="N216" s="49"/>
       <c r="O216" s="59" t="s">
         <v>995</v>
       </c>
-      <c r="P216" s="68" t="s">
+      <c r="P216" s="64" t="s">
         <v>997</v>
       </c>
-      <c r="Q216" s="68"/>
-      <c r="R216" s="59" t="s">
+      <c r="Q216" s="64"/>
+      <c r="R216" s="83" t="s">
         <v>661</v>
       </c>
-      <c r="S216" s="59" t="s">
+      <c r="S216" s="83" t="s">
         <v>1002</v>
       </c>
       <c r="T216" s="5" t="s">
@@ -18262,11 +18282,11 @@
     <row r="217" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A217" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.c. - Accidental Firearm</v>
+        <v>....E.01.x. - Accidental Firearm</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="31" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>1142</v>
@@ -18275,44 +18295,43 @@
         <v>1143</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="G217" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01c</v>
-      </c>
-      <c r="H217" s="40" t="str">
-        <f>CONCATENATE(D217,E217,F217)</f>
-        <v>E01c</v>
+        <v>cE01x</v>
+      </c>
+      <c r="H217" s="40" t="s">
+        <v>952</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>1212</v>
       </c>
       <c r="K217" s="5" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="L217" s="49" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="M217" s="49"/>
       <c r="N217" s="49"/>
       <c r="O217" s="59"/>
-      <c r="P217" s="68"/>
-      <c r="Q217" s="68"/>
-      <c r="R217" s="59"/>
-      <c r="S217" s="59"/>
+      <c r="P217" s="64"/>
+      <c r="Q217" s="64"/>
+      <c r="R217" s="83"/>
+      <c r="S217" s="83"/>
       <c r="T217" s="5" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
       <c r="U217" s="20"/>
       <c r="V217" s="5"/>
       <c r="W217" s="45"/>
       <c r="X217" s="2"/>
     </row>
-    <row r="218" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A218" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18354,12 +18373,12 @@
       <c r="O218" s="59" t="s">
         <v>504</v>
       </c>
-      <c r="P218" s="68" t="s">
+      <c r="P218" s="64" t="s">
         <v>873</v>
       </c>
-      <c r="Q218" s="69"/>
-      <c r="R218" s="59"/>
-      <c r="S218" s="59"/>
+      <c r="Q218" s="65"/>
+      <c r="R218" s="83"/>
+      <c r="S218" s="83"/>
       <c r="T218" s="5" t="s">
         <v>886</v>
       </c>
@@ -18374,290 +18393,308 @@
       </c>
       <c r="X218" s="2"/>
     </row>
-    <row r="219" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:24" ht="33" x14ac:dyDescent="0.25">
       <c r="A219" s="44" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="B219" s="2"/>
-      <c r="C219" s="31"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="26"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="40"/>
-      <c r="H219" s="40"/>
-      <c r="I219" s="5"/>
-      <c r="J219" s="5"/>
-      <c r="K219" s="5"/>
-      <c r="L219" s="49"/>
+        <v>....E.01.x. - Other unintentional injuries</v>
+      </c>
+      <c r="B219" s="2">
+        <v>206</v>
+      </c>
+      <c r="C219" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E219" s="26" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G219" s="40" t="str">
+        <f t="shared" si="21"/>
+        <v>cE01x</v>
+      </c>
+      <c r="H219" s="40" t="str">
+        <f>CONCATENATE(D219,E219,F219)</f>
+        <v>E01x</v>
+      </c>
+      <c r="I219" s="5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J219" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="K219" s="5" t="s">
+        <v>1255</v>
+      </c>
+      <c r="L219" s="49" t="s">
+        <v>1256</v>
+      </c>
       <c r="M219" s="49"/>
       <c r="N219" s="49"/>
-      <c r="O219" s="59"/>
-      <c r="P219" s="68"/>
-      <c r="Q219" s="69"/>
-      <c r="R219" s="59"/>
-      <c r="S219" s="59"/>
-      <c r="T219" s="5"/>
-      <c r="U219" s="20"/>
-      <c r="V219" s="5"/>
-      <c r="W219" s="45"/>
-      <c r="X219" s="2"/>
-    </row>
-    <row r="220" spans="1:24" ht="102" x14ac:dyDescent="0.25">
+      <c r="O219" s="59" t="s">
+        <v>996</v>
+      </c>
+      <c r="P219" s="64" t="s">
+        <v>1113</v>
+      </c>
+      <c r="Q219" s="64"/>
+      <c r="R219" s="83" t="s">
+        <v>662</v>
+      </c>
+      <c r="S219" s="83" t="s">
+        <v>1003</v>
+      </c>
+      <c r="T219" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="U219" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="V219" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="W219" s="45" t="s">
+        <v>887</v>
+      </c>
+      <c r="X219" s="22" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A220" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.x. - Other unintentional injuries</v>
+        <v/>
       </c>
       <c r="B220" s="2">
-        <v>206</v>
-      </c>
-      <c r="C220" s="31" t="s">
-        <v>748</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E220" s="26" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F220" s="6" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G220" s="40" t="str">
-        <f t="shared" si="21"/>
-        <v>cE01x</v>
-      </c>
-      <c r="H220" s="40" t="str">
-        <f>CONCATENATE(D220,E220,F220)</f>
-        <v>E01x</v>
-      </c>
-      <c r="I220" s="5" t="s">
-        <v>1257</v>
-      </c>
-      <c r="J220" s="5" t="s">
-        <v>1254</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C220" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D220" s="6"/>
+      <c r="E220" s="26"/>
+      <c r="F220" s="6"/>
+      <c r="G220" s="40"/>
+      <c r="H220" s="40"/>
+      <c r="I220" s="5"/>
+      <c r="J220" s="5"/>
       <c r="K220" s="5" t="s">
-        <v>1255</v>
-      </c>
-      <c r="L220" s="49" t="s">
-        <v>1256</v>
-      </c>
-      <c r="M220" s="49"/>
-      <c r="N220" s="49"/>
+        <v>952</v>
+      </c>
+      <c r="L220" s="19" t="s">
+        <v>952</v>
+      </c>
+      <c r="M220" s="19"/>
+      <c r="N220" s="19"/>
       <c r="O220" s="59" t="s">
-        <v>996</v>
-      </c>
-      <c r="P220" s="68" t="s">
-        <v>1113</v>
-      </c>
-      <c r="Q220" s="68"/>
-      <c r="R220" s="59" t="s">
-        <v>662</v>
-      </c>
-      <c r="S220" s="59" t="s">
-        <v>1003</v>
-      </c>
-      <c r="T220" s="5" t="s">
-        <v>315</v>
+        <v>505</v>
+      </c>
+      <c r="P220" s="62" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q220" s="63"/>
+      <c r="R220" s="83" t="s">
+        <v>664</v>
+      </c>
+      <c r="S220" s="83" t="s">
+        <v>663</v>
+      </c>
+      <c r="T220" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="U220" s="20" t="s">
-        <v>887</v>
-      </c>
-      <c r="V220" s="5" t="s">
-        <v>315</v>
+        <v>139</v>
+      </c>
+      <c r="V220" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="W220" s="45" t="s">
-        <v>887</v>
-      </c>
-      <c r="X220" s="22" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="221" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="X220" s="2"/>
+    </row>
+    <row r="221" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A221" s="44" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>...E.02. - Suicide/Self-harm</v>
       </c>
       <c r="B221" s="2">
-        <v>207</v>
-      </c>
-      <c r="C221" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D221" s="6"/>
-      <c r="E221" s="26"/>
+        <v>208</v>
+      </c>
+      <c r="C221" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E221" s="26" t="s">
+        <v>1144</v>
+      </c>
       <c r="F221" s="6"/>
-      <c r="G221" s="40"/>
-      <c r="H221" s="40"/>
-      <c r="I221" s="5"/>
-      <c r="J221" s="5"/>
+      <c r="G221" s="40" t="str">
+        <f t="shared" ref="G221:G228" si="23">CONCATENATE("c",D221,E221,F221)</f>
+        <v>cE02</v>
+      </c>
+      <c r="H221" s="40" t="str">
+        <f>CONCATENATE(D221,E221,F221)</f>
+        <v>E02</v>
+      </c>
+      <c r="I221" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="J221" s="5" t="s">
+        <v>1212</v>
+      </c>
       <c r="K221" s="5" t="s">
-        <v>952</v>
-      </c>
-      <c r="L221" s="19" t="s">
-        <v>952</v>
-      </c>
-      <c r="M221" s="19"/>
-      <c r="N221" s="19"/>
+        <v>1213</v>
+      </c>
+      <c r="L221" s="49" t="s">
+        <v>1214</v>
+      </c>
+      <c r="M221" s="49"/>
+      <c r="N221" s="49"/>
       <c r="O221" s="59" t="s">
-        <v>505</v>
-      </c>
-      <c r="P221" s="66" t="s">
-        <v>874</v>
-      </c>
-      <c r="Q221" s="67"/>
-      <c r="R221" s="59" t="s">
-        <v>664</v>
-      </c>
-      <c r="S221" s="59" t="s">
-        <v>663</v>
-      </c>
-      <c r="T221" s="2" t="s">
-        <v>316</v>
+        <v>506</v>
+      </c>
+      <c r="P221" s="64" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q221" s="65"/>
+      <c r="R221" s="83" t="s">
+        <v>665</v>
+      </c>
+      <c r="S221" s="83" t="s">
+        <v>999</v>
+      </c>
+      <c r="T221" s="5" t="s">
+        <v>1274</v>
       </c>
       <c r="U221" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="V221" s="2" t="s">
-        <v>316</v>
+        <v>140</v>
+      </c>
+      <c r="V221" s="5" t="s">
+        <v>317</v>
       </c>
       <c r="W221" s="45" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="X221" s="2"/>
     </row>
     <row r="222" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A222" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...E.02. - Suicide/Self-harm</v>
+        <v>...E.03. - Homicide/Interpersonal violence</v>
       </c>
       <c r="B222" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C222" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>1142</v>
       </c>
       <c r="E222" s="26" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="F222" s="6"/>
-      <c r="G222" s="40" t="str">
-        <f t="shared" ref="G222:G229" si="23">CONCATENATE("c",D222,E222,F222)</f>
-        <v>cE02</v>
+      <c r="G222" s="40" t="s">
+        <v>952</v>
       </c>
       <c r="H222" s="40" t="str">
         <f>CONCATENATE(D222,E222,F222)</f>
-        <v>E02</v>
-      </c>
-      <c r="I222" s="5" t="s">
-        <v>1304</v>
-      </c>
+        <v>E03</v>
+      </c>
+      <c r="I222" s="5"/>
       <c r="J222" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="K222" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="L222" s="49" t="s">
-        <v>1214</v>
-      </c>
-      <c r="M222" s="49"/>
-      <c r="N222" s="49"/>
+      <c r="M222" s="19"/>
+      <c r="N222" s="19"/>
       <c r="O222" s="59" t="s">
-        <v>506</v>
-      </c>
-      <c r="P222" s="68" t="s">
-        <v>875</v>
-      </c>
-      <c r="Q222" s="69"/>
-      <c r="R222" s="59" t="s">
-        <v>665</v>
-      </c>
-      <c r="S222" s="59" t="s">
-        <v>999</v>
+        <v>507</v>
+      </c>
+      <c r="P222" s="64" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q222" s="65"/>
+      <c r="R222" s="83" t="s">
+        <v>666</v>
+      </c>
+      <c r="S222" s="83" t="s">
+        <v>998</v>
       </c>
       <c r="T222" s="5" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="U222" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="V222" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="W222" s="45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="X222" s="2"/>
     </row>
-    <row r="223" spans="1:24" ht="255" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A223" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...E.03. - Homicide/Interpersonal violence</v>
-      </c>
-      <c r="B223" s="2">
-        <v>209</v>
-      </c>
-      <c r="C223" s="31" t="s">
-        <v>141</v>
-      </c>
+        <v>....E.03.a. - Homicide excluding legal intervention</v>
+      </c>
+      <c r="B223" s="2"/>
+      <c r="C223" s="31"/>
       <c r="D223" s="6" t="s">
         <v>1142</v>
       </c>
       <c r="E223" s="26" t="s">
         <v>1145</v>
       </c>
-      <c r="F223" s="6"/>
-      <c r="G223" s="40" t="s">
-        <v>952</v>
+      <c r="F223" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G223" s="40" t="str">
+        <f t="shared" si="23"/>
+        <v>cE03a</v>
       </c>
       <c r="H223" s="40" t="str">
-        <f>CONCATENATE(D223,E223,F223)</f>
-        <v>E03</v>
+        <f t="shared" ref="H223:H225" si="24">CONCATENATE(D223,E223,F223)</f>
+        <v>E03a</v>
       </c>
       <c r="I223" s="5" t="s">
-        <v>1379</v>
-      </c>
-      <c r="J223" s="5" t="s">
-        <v>1212</v>
+        <v>1397</v>
+      </c>
+      <c r="J223" s="5"/>
+      <c r="K223" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="L223" s="19" t="s">
+        <v>1372</v>
       </c>
       <c r="M223" s="19"/>
       <c r="N223" s="19"/>
-      <c r="O223" s="59" t="s">
-        <v>507</v>
-      </c>
-      <c r="P223" s="68" t="s">
-        <v>876</v>
-      </c>
-      <c r="Q223" s="69"/>
-      <c r="R223" s="59" t="s">
-        <v>666</v>
-      </c>
-      <c r="S223" s="59" t="s">
-        <v>998</v>
-      </c>
-      <c r="T223" s="5" t="s">
-        <v>1274</v>
-      </c>
-      <c r="U223" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="V223" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="W223" s="45" t="s">
-        <v>141</v>
-      </c>
+      <c r="O223" s="59"/>
+      <c r="P223" s="64"/>
+      <c r="Q223" s="65"/>
+      <c r="R223" s="83"/>
+      <c r="S223" s="83"/>
+      <c r="T223" s="20" t="s">
+        <v>1367</v>
+      </c>
+      <c r="U223" s="46"/>
+      <c r="V223" s="5"/>
+      <c r="W223" s="45"/>
       <c r="X223" s="2"/>
     </row>
-    <row r="224" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.a. - Homicide excluding legal intervention</v>
+        <v>....E.03.b. - Legal intervention</v>
       </c>
       <c r="B224" s="2"/>
       <c r="C224" s="31"/>
@@ -18668,46 +18705,54 @@
         <v>1145</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G224" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03a</v>
+        <v>cE03b</v>
       </c>
       <c r="H224" s="40" t="str">
-        <f t="shared" ref="H224:H226" si="24">CONCATENATE(D224,E224,F224)</f>
-        <v>E03a</v>
-      </c>
-      <c r="I224" s="5"/>
-      <c r="J224" s="5"/>
+        <f t="shared" si="24"/>
+        <v>E03b</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="J224" s="5" t="s">
+        <v>1212</v>
+      </c>
       <c r="K224" s="5" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="L224" s="19" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="M224" s="19"/>
       <c r="N224" s="19"/>
       <c r="O224" s="59"/>
-      <c r="P224" s="68"/>
-      <c r="Q224" s="69"/>
-      <c r="R224" s="59"/>
-      <c r="S224" s="59"/>
+      <c r="P224" s="64"/>
+      <c r="Q224" s="65"/>
+      <c r="R224" s="83"/>
+      <c r="S224" s="83"/>
       <c r="T224" s="20" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="U224" s="46"/>
       <c r="V224" s="5"/>
       <c r="W224" s="45"/>
       <c r="X224" s="2"/>
     </row>
-    <row r="225" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A225" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.b. - Legal intervention</v>
-      </c>
-      <c r="B225" s="2"/>
-      <c r="C225" s="31"/>
+        <v>....E.03.c. - Execution, War, Terroism</v>
+      </c>
+      <c r="B225" s="2">
+        <v>210</v>
+      </c>
+      <c r="C225" s="31" t="s">
+        <v>142</v>
+      </c>
       <c r="D225" s="6" t="s">
         <v>1142</v>
       </c>
@@ -18715,293 +18760,242 @@
         <v>1145</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="G225" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03b</v>
+        <v>cE03c</v>
       </c>
       <c r="H225" s="40" t="str">
         <f t="shared" si="24"/>
-        <v>E03b</v>
-      </c>
-      <c r="I225" s="5"/>
-      <c r="J225" s="5"/>
+        <v>E03c</v>
+      </c>
+      <c r="I225" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="J225" s="5" t="s">
+        <v>1237</v>
+      </c>
       <c r="K225" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="L225" s="49" t="s">
         <v>1371</v>
       </c>
-      <c r="L225" s="19" t="s">
-        <v>1377</v>
-      </c>
-      <c r="M225" s="19"/>
-      <c r="N225" s="19"/>
-      <c r="O225" s="59"/>
-      <c r="P225" s="68"/>
-      <c r="Q225" s="69"/>
-      <c r="R225" s="59"/>
-      <c r="S225" s="59"/>
-      <c r="T225" s="20" t="s">
-        <v>1369</v>
-      </c>
-      <c r="U225" s="46"/>
-      <c r="V225" s="5"/>
-      <c r="W225" s="45"/>
-      <c r="X225" s="2"/>
-    </row>
-    <row r="226" spans="1:24" ht="153" x14ac:dyDescent="0.25">
+      <c r="M225" s="49"/>
+      <c r="N225" s="49"/>
+      <c r="O225" s="59" t="s">
+        <v>508</v>
+      </c>
+      <c r="P225" s="64" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q225" s="65"/>
+      <c r="R225" s="83"/>
+      <c r="S225" s="83"/>
+      <c r="T225" s="5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="U225" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="V225" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="W225" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="X225" s="22" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="226" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A226" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.c. - Execution, War, Terroism</v>
-      </c>
-      <c r="B226" s="2">
-        <v>210</v>
-      </c>
-      <c r="C226" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D226" s="6" t="s">
+        <v/>
+      </c>
+      <c r="B226" s="77" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C226" s="16" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D226" s="54" t="s">
         <v>1142</v>
       </c>
-      <c r="E226" s="26" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F226" s="6" t="s">
-        <v>1130</v>
+      <c r="E226" s="55" t="s">
+        <v>1143</v>
       </c>
       <c r="G226" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03c</v>
-      </c>
-      <c r="H226" s="40" t="str">
-        <f t="shared" si="24"/>
-        <v>E03c</v>
-      </c>
-      <c r="I226" s="5" t="s">
-        <v>1374</v>
-      </c>
-      <c r="J226" s="5" t="s">
-        <v>1237</v>
-      </c>
-      <c r="K226" s="5" t="s">
-        <v>1373</v>
-      </c>
-      <c r="L226" s="49" t="s">
-        <v>1375</v>
-      </c>
-      <c r="M226" s="49"/>
-      <c r="N226" s="49"/>
-      <c r="O226" s="59" t="s">
-        <v>508</v>
-      </c>
-      <c r="P226" s="68" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q226" s="69"/>
-      <c r="R226" s="59"/>
-      <c r="S226" s="59"/>
-      <c r="T226" s="5" t="s">
-        <v>1378</v>
-      </c>
-      <c r="U226" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="V226" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="W226" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="X226" s="22" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="227" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+        <v>cE01</v>
+      </c>
+      <c r="H226" s="40"/>
+      <c r="I226" s="48" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J226" s="48" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K226" s="16" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L226" s="16" t="s">
+        <v>1271</v>
+      </c>
+      <c r="T226" s="48" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="227" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A227" s="44" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="B227" s="82" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C227" s="16" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D227" s="54" t="s">
-        <v>1142</v>
+        <v>...Z.01. - Symptoms, signs and ill-defined conditions, not elsewhere classified</v>
+      </c>
+      <c r="D227" s="56" t="s">
+        <v>1241</v>
       </c>
       <c r="E227" s="55" t="s">
         <v>1143</v>
       </c>
       <c r="G227" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE01</v>
-      </c>
-      <c r="H227" s="40"/>
+        <v>cZ01</v>
+      </c>
+      <c r="H227" s="40" t="str">
+        <f>CONCATENATE(D227,E227,F227)</f>
+        <v>Z01</v>
+      </c>
       <c r="I227" s="48" t="s">
-        <v>1253</v>
+        <v>1221</v>
       </c>
       <c r="J227" s="48" t="s">
-        <v>1270</v>
+        <v>1222</v>
       </c>
       <c r="K227" s="16" t="s">
-        <v>1271</v>
+        <v>1223</v>
       </c>
       <c r="L227" s="16" t="s">
-        <v>1272</v>
+        <v>1252</v>
       </c>
       <c r="T227" s="48" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="228" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A228" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...Z.01. - Symptoms, signs and ill-defined conditions, not elsewhere classified</v>
+        <v/>
       </c>
       <c r="D228" s="56" t="s">
-        <v>1241</v>
+        <v>1137</v>
       </c>
       <c r="E228" s="55" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G228" s="40" t="str">
+        <v>1151</v>
+      </c>
+      <c r="G228" s="42" t="str">
         <f t="shared" si="23"/>
-        <v>cZ01</v>
-      </c>
-      <c r="H228" s="40" t="str">
-        <f>CONCATENATE(D228,E228,F228)</f>
-        <v>Z01</v>
-      </c>
-      <c r="I228" s="48" t="s">
-        <v>1221</v>
+        <v>cA09</v>
+      </c>
+      <c r="H228" s="40"/>
+      <c r="I228" s="16" t="s">
+        <v>1327</v>
       </c>
       <c r="J228" s="48" t="s">
         <v>1222</v>
       </c>
       <c r="K228" s="16" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="L228" s="16" t="s">
-        <v>1252</v>
+        <v>1216</v>
       </c>
       <c r="T228" s="48" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="229" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A229" s="44" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>...Z.02. - Unknown/Missing Value</v>
       </c>
       <c r="D229" s="56" t="s">
-        <v>1137</v>
+        <v>1241</v>
       </c>
       <c r="E229" s="55" t="s">
-        <v>1151</v>
-      </c>
-      <c r="G229" s="42" t="str">
-        <f t="shared" si="23"/>
-        <v>cA09</v>
-      </c>
-      <c r="H229" s="40"/>
-      <c r="I229" s="16" t="s">
-        <v>1330</v>
-      </c>
-      <c r="J229" s="48" t="s">
-        <v>1222</v>
-      </c>
-      <c r="K229" s="16" t="s">
-        <v>1216</v>
-      </c>
-      <c r="L229" s="16" t="s">
-        <v>1216</v>
+        <v>1144</v>
+      </c>
+      <c r="G229" s="43"/>
+      <c r="H229" s="40" t="str">
+        <f t="shared" ref="H229:H232" si="25">CONCATENATE(D229,E229,F229)</f>
+        <v>Z02</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>1215</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A230" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...Z.02. - Unknown/Missing Value</v>
+        <v>...Z.03. - Code does not map</v>
       </c>
       <c r="D230" s="56" t="s">
         <v>1241</v>
       </c>
       <c r="E230" s="55" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="G230" s="43"/>
       <c r="H230" s="40" t="str">
-        <f t="shared" ref="H230:H233" si="25">CONCATENATE(D230,E230,F230)</f>
-        <v>Z02</v>
+        <f t="shared" si="25"/>
+        <v>Z03</v>
+      </c>
+      <c r="I230" s="16" t="s">
+        <v>1257</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="231" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A231" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...Z.03. - Code does not map</v>
+        <v>..Z. - Unknown/Missing Value</v>
       </c>
       <c r="D231" s="56" t="s">
         <v>1241</v>
-      </c>
-      <c r="E231" s="55" t="s">
-        <v>1145</v>
       </c>
       <c r="G231" s="43"/>
       <c r="H231" s="40" t="str">
         <f t="shared" si="25"/>
-        <v>Z03</v>
-      </c>
-      <c r="I231" s="16" t="s">
-        <v>1258</v>
+        <v>Z</v>
       </c>
       <c r="T231" s="48" t="s">
-        <v>1242</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="232" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>..Z. - Unknown/Missing Value</v>
+        <v>...D.99. - Other Chronic Conditions</v>
       </c>
       <c r="D232" s="56" t="s">
-        <v>1241</v>
+        <v>1141</v>
+      </c>
+      <c r="E232" s="55" t="s">
+        <v>1225</v>
       </c>
       <c r="G232" s="43"/>
       <c r="H232" s="40" t="str">
         <f t="shared" si="25"/>
-        <v>Z</v>
+        <v>D99</v>
       </c>
       <c r="T232" s="48" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="233" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A233" s="44" t="str">
-        <f t="shared" si="19"/>
-        <v>...D.99. - Other Chronic Conditions</v>
-      </c>
-      <c r="D233" s="56" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E233" s="55" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G233" s="43"/>
-      <c r="H233" s="40" t="str">
-        <f t="shared" si="25"/>
-        <v>D99</v>
-      </c>
-      <c r="T233" s="48" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X226"/>
+  <autoFilter ref="A1:X225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -19227,25 +19221,25 @@
   </cols>
   <sheetData>
     <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="75" t="s">
+      <c r="C11" s="70" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="72" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D12" s="73" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E12" s="73" t="s">
         <v>1319</v>
-      </c>
-      <c r="D11" s="76" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E11" s="76" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="77" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E12" s="78" t="s">
-        <v>1322</v>
       </c>
     </row>
   </sheetData>

--- a/myCBD/myInfo/gbd.ICD.Map.xlsx
+++ b/myCBD/myInfo/gbd.ICD.Map.xlsx
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="1402">
   <si>
     <t>I. Communicable, maternal, perinatal and nutritional conditions</t>
   </si>
@@ -3533,9 +3533,6 @@
   </si>
   <si>
     <t>b</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
   <si>
     <t>Other Infectious Diseases</t>
@@ -4195,9 +4192,6 @@
     <t xml:space="preserve">J. Digestive diseases </t>
   </si>
   <si>
-    <t>INCLUDED FOR NOW WITH UNINTENTIONAL -- FIX</t>
-  </si>
-  <si>
     <t>E10[0-1,3-9]|E11[0-1,3-9]|E12[0-1,3-9]|E13[0-1,3-9]|E14[0-1,3-9]|R730|R739</t>
   </si>
   <si>
@@ -4470,6 +4464,9 @@
   </si>
   <si>
     <t>Poisonings (non-substance use)</t>
+  </si>
+  <si>
+    <t>INCLUDED ALL INJURY but not elsewhere</t>
   </si>
 </sst>
 </file>
@@ -4651,7 +4648,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4721,6 +4718,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4804,7 +4807,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -5062,6 +5065,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="29">
@@ -5427,7 +5433,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>761</v>
@@ -5436,7 +5442,7 @@
         <v>763</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>1121</v>
@@ -5451,10 +5457,10 @@
         <v>1124</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>384</v>
@@ -5463,19 +5469,19 @@
         <v>759</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="O1" s="59" t="s">
+        <v>1160</v>
+      </c>
+      <c r="P1" s="59" t="s">
         <v>1161</v>
       </c>
-      <c r="P1" s="59" t="s">
-        <v>1162</v>
-      </c>
       <c r="Q1" s="59" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="R1" s="82" t="s">
         <v>509</v>
@@ -5490,10 +5496,10 @@
         <v>762</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="W1" s="45" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>930</v>
@@ -5557,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="6"/>
@@ -5606,10 +5612,10 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="29" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E4" s="26">
         <v>99</v>
@@ -5632,11 +5638,11 @@
       <c r="R4" s="83"/>
       <c r="S4" s="83"/>
       <c r="T4" s="20" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="U4" s="20"/>
       <c r="V4" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="W4" s="45"/>
       <c r="X4" s="2"/>
@@ -5704,10 +5710,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="40" t="str">
@@ -5763,10 +5769,10 @@
         <v>1125</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="40"/>
@@ -5786,11 +5792,11 @@
       <c r="R7" s="83"/>
       <c r="S7" s="83"/>
       <c r="T7" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="U7" s="20"/>
       <c r="V7" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="W7" s="45"/>
       <c r="X7" s="2"/>
@@ -5804,13 +5810,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>1126</v>
@@ -5871,10 +5877,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>1126</v>
@@ -5931,10 +5937,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>1126</v>
@@ -5991,10 +5997,10 @@
         <v>6</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>1126</v>
@@ -6051,10 +6057,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>1126</v>
@@ -6109,10 +6115,10 @@
         <v>8</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>1126</v>
@@ -6166,13 +6172,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>1127</v>
@@ -6231,10 +6237,10 @@
         <v>686</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>1127</v>
@@ -6287,10 +6293,10 @@
         <v>687</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>1127</v>
@@ -6347,7 +6353,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E17" s="26">
         <v>99</v>
@@ -6457,7 +6463,7 @@
         <v>12</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E19" s="26">
         <v>99</v>
@@ -6515,7 +6521,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E20" s="26">
         <v>99</v>
@@ -6573,7 +6579,7 @@
         <v>14</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E21" s="26">
         <v>99</v>
@@ -6631,7 +6637,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E22" s="26">
         <v>99</v>
@@ -6689,10 +6695,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="40" t="str">
@@ -6750,10 +6756,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="40" t="str">
@@ -6811,10 +6817,10 @@
         <v>688</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="40"/>
@@ -6865,10 +6871,10 @@
         <v>689</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="40" t="str">
@@ -6919,10 +6925,10 @@
         <v>690</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>1126</v>
@@ -6973,7 +6979,7 @@
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="34" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="26"/>
@@ -7006,10 +7012,10 @@
         <v>691</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>1127</v>
@@ -7065,10 +7071,10 @@
         <v>692</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="40" t="str">
@@ -7170,7 +7176,7 @@
         <v>18</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E32" s="26">
         <v>99</v>
@@ -7228,7 +7234,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E33" s="26">
         <v>99</v>
@@ -7286,7 +7292,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E34" s="26">
         <v>99</v>
@@ -7344,7 +7350,7 @@
         <v>21</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E35" s="26">
         <v>99</v>
@@ -7402,7 +7408,7 @@
         <v>22</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E36" s="26">
         <v>99</v>
@@ -7460,7 +7466,7 @@
         <v>23</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E37" s="26">
         <v>99</v>
@@ -7514,7 +7520,7 @@
         <v>24</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E38" s="26">
         <v>99</v>
@@ -7568,7 +7574,7 @@
         <v>694</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E39" s="26">
         <v>99</v>
@@ -7626,7 +7632,7 @@
         <v>695</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E40" s="26">
         <v>99</v>
@@ -7684,7 +7690,7 @@
         <v>889</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E41" s="26">
         <v>99</v>
@@ -7738,7 +7744,7 @@
         <v>890</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E42" s="26">
         <v>99</v>
@@ -7796,7 +7802,7 @@
         <v>891</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E43" s="26">
         <v>99</v>
@@ -7850,7 +7856,7 @@
         <v>893</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E44" s="26">
         <v>99</v>
@@ -7908,7 +7914,7 @@
         <v>894</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E45" s="26">
         <v>99</v>
@@ -8021,7 +8027,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E47" s="26">
         <v>99</v>
@@ -8079,7 +8085,7 @@
         <v>26</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E48" s="26">
         <v>99</v>
@@ -8133,7 +8139,7 @@
         <v>27</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E49" s="26">
         <v>99</v>
@@ -8187,7 +8193,7 @@
         <v>696</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E50" s="26">
         <v>99</v>
@@ -8241,7 +8247,7 @@
         <v>880</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E51" s="26">
         <v>99</v>
@@ -8253,16 +8259,16 @@
       </c>
       <c r="H51" s="40"/>
       <c r="I51" s="5" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="K51" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L51" s="19" t="s">
         <v>1230</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>1231</v>
       </c>
       <c r="M51" s="19"/>
       <c r="N51" s="19"/>
@@ -8292,7 +8298,7 @@
         <v>880</v>
       </c>
       <c r="X51" s="5" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
@@ -8307,10 +8313,10 @@
         <v>28</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="40"/>
@@ -8367,10 +8373,10 @@
         <v>29</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>1126</v>
@@ -8389,13 +8395,13 @@
         <v>404</v>
       </c>
       <c r="L53" s="75" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="M53" s="75" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="N53" s="75" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="O53" s="59" t="s">
         <v>404</v>
@@ -8436,10 +8442,10 @@
         <v>30</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>1127</v>
@@ -8505,10 +8511,10 @@
         <v>31</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="40" t="str">
@@ -8569,10 +8575,10 @@
         <v>32</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="40" t="s">
@@ -8631,10 +8637,10 @@
         <v>33</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="40" t="str">
@@ -8645,16 +8651,16 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="M57" s="16" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="N57" s="16" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="O57" s="59" t="s">
         <v>408</v>
@@ -8682,7 +8688,7 @@
         <v>33</v>
       </c>
       <c r="X57" s="5" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
@@ -8697,10 +8703,10 @@
         <v>34</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="40" t="str">
@@ -8761,10 +8767,10 @@
         <v>35</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="40" t="str">
@@ -8781,7 +8787,7 @@
         <v>370</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="N59" s="16" t="s">
         <v>370</v>
@@ -8812,7 +8818,7 @@
         <v>35</v>
       </c>
       <c r="X59" s="5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
@@ -8827,10 +8833,10 @@
         <v>36</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="40" t="str">
@@ -8891,10 +8897,10 @@
         <v>37</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="40" t="str">
@@ -8911,10 +8917,10 @@
         <v>372</v>
       </c>
       <c r="M61" s="16" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="N61" s="16" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="O61" s="59" t="s">
         <v>412</v>
@@ -8955,10 +8961,10 @@
         <v>38</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="40" t="str">
@@ -8975,10 +8981,10 @@
         <v>373</v>
       </c>
       <c r="M62" s="16" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="N62" s="16" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="O62" s="59" t="s">
         <v>413</v>
@@ -9019,10 +9025,10 @@
         <v>39</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="40" t="s">
@@ -9081,10 +9087,10 @@
         <v>40</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="40" t="str">
@@ -9139,10 +9145,10 @@
         <v>41</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="40" t="str">
@@ -9197,10 +9203,10 @@
         <v>42</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="40" t="str">
@@ -9255,10 +9261,10 @@
         <v>43</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="40" t="str">
@@ -9267,16 +9273,16 @@
       </c>
       <c r="H67" s="40"/>
       <c r="I67" s="5" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="L67" s="19" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="M67" s="19"/>
       <c r="N67" s="19"/>
@@ -9319,7 +9325,7 @@
         <v>44</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E68" s="26"/>
       <c r="F68" s="6"/>
@@ -9374,7 +9380,7 @@
         <v>45</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E69" s="26">
         <v>99</v>
@@ -9391,7 +9397,7 @@
         <v>420</v>
       </c>
       <c r="L69" s="16" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="O69" s="59" t="s">
         <v>420</v>
@@ -9432,7 +9438,7 @@
         <v>46</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E70" s="26">
         <v>99</v>
@@ -9490,7 +9496,7 @@
         <v>47</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E71" s="26">
         <v>99</v>
@@ -9544,7 +9550,7 @@
         <v>48</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E72" s="26">
         <v>99</v>
@@ -9602,7 +9608,7 @@
         <v>697</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E73" s="26">
         <v>99</v>
@@ -9682,7 +9688,7 @@
       </c>
       <c r="Q74" s="59"/>
       <c r="R74" s="86" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="S74" s="83" t="s">
         <v>557</v>
@@ -9708,10 +9714,10 @@
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="35" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E75" s="26"/>
       <c r="F75" s="6"/>
@@ -9732,10 +9738,10 @@
       <c r="R75" s="83"/>
       <c r="S75" s="83"/>
       <c r="T75" s="20" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="V75" s="45" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="X75" s="2"/>
     </row>
@@ -9751,7 +9757,7 @@
         <v>51</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E76" s="26"/>
       <c r="F76" s="6"/>
@@ -9784,7 +9790,7 @@
         <v>558</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="U76" s="20" t="s">
         <v>51</v>
@@ -9809,10 +9815,10 @@
         <v>52</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F77" s="6"/>
       <c r="G77" s="40" t="str">
@@ -9826,10 +9832,10 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="L77" s="49" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="M77" s="49"/>
       <c r="N77" s="49"/>
@@ -9868,10 +9874,10 @@
         <v>698</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F78" s="6"/>
       <c r="G78" s="40" t="str">
@@ -9880,16 +9886,16 @@
       </c>
       <c r="H78" s="40"/>
       <c r="I78" s="18" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="J78" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K78" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L78" s="19" t="s">
         <v>1265</v>
-      </c>
-      <c r="L78" s="19" t="s">
-        <v>1266</v>
       </c>
       <c r="M78" s="19"/>
       <c r="N78" s="19"/>
@@ -9932,10 +9938,10 @@
         <v>699</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="40" t="str">
@@ -9944,16 +9950,16 @@
       </c>
       <c r="H79" s="40"/>
       <c r="I79" s="19" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J79" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K79" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="L79" s="49" t="s">
         <v>1166</v>
-      </c>
-      <c r="L79" s="49" t="s">
-        <v>1167</v>
       </c>
       <c r="M79" s="49"/>
       <c r="N79" s="49"/>
@@ -9996,10 +10002,10 @@
         <v>700</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F80" s="6"/>
       <c r="G80" s="40" t="str">
@@ -10056,10 +10062,10 @@
         <v>53</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F81" s="6"/>
       <c r="G81" s="40" t="str">
@@ -10071,16 +10077,16 @@
         <v>B02</v>
       </c>
       <c r="I81" s="18" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K81" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="L81" s="49" t="s">
         <v>1168</v>
-      </c>
-      <c r="L81" s="49" t="s">
-        <v>1169</v>
       </c>
       <c r="M81" s="49"/>
       <c r="N81" s="49"/>
@@ -10123,10 +10129,10 @@
         <v>54</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F82" s="6"/>
       <c r="G82" s="40" t="str">
@@ -10138,16 +10144,16 @@
         <v>B03</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="J82" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K82" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L82" s="49" t="s">
         <v>1170</v>
-      </c>
-      <c r="L82" s="49" t="s">
-        <v>1171</v>
       </c>
       <c r="M82" s="49"/>
       <c r="N82" s="49"/>
@@ -10192,10 +10198,10 @@
         <v>55</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="40" t="str">
@@ -10207,16 +10213,16 @@
         <v>B04</v>
       </c>
       <c r="I83" s="16" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J83" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K83" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="L83" s="49" t="s">
         <v>1239</v>
-      </c>
-      <c r="L83" s="49" t="s">
-        <v>1240</v>
       </c>
       <c r="M83" s="49"/>
       <c r="N83" s="49"/>
@@ -10259,10 +10265,10 @@
         <v>56</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="40" t="str">
@@ -10274,16 +10280,16 @@
         <v>B05</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="J84" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K84" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="L84" s="49" t="s">
         <v>1172</v>
-      </c>
-      <c r="L84" s="49" t="s">
-        <v>1173</v>
       </c>
       <c r="M84" s="49"/>
       <c r="N84" s="49"/>
@@ -10326,10 +10332,10 @@
         <v>57</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="40" t="str">
@@ -10341,16 +10347,16 @@
         <v>B06</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J85" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K85" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L85" s="49" t="s">
         <v>1174</v>
-      </c>
-      <c r="L85" s="49" t="s">
-        <v>1175</v>
       </c>
       <c r="M85" s="49"/>
       <c r="N85" s="49"/>
@@ -10393,10 +10399,10 @@
         <v>58</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="40" t="str">
@@ -10408,16 +10414,16 @@
         <v>B07</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J86" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="L86" s="49" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="M86" s="49"/>
       <c r="N86" s="49"/>
@@ -10460,10 +10466,10 @@
         <v>59</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="40" t="s">
@@ -10474,7 +10480,7 @@
         <v>B08</v>
       </c>
       <c r="J87" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K87" s="5" t="s">
         <v>952</v>
@@ -10519,10 +10525,10 @@
         <v>701</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="40" t="str">
@@ -10531,16 +10537,16 @@
       </c>
       <c r="H88" s="40"/>
       <c r="I88" s="18" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="J88" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K88" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L88" s="49" t="s">
         <v>1243</v>
-      </c>
-      <c r="L88" s="49" t="s">
-        <v>1244</v>
       </c>
       <c r="M88" s="49"/>
       <c r="N88" s="49"/>
@@ -10583,10 +10589,10 @@
         <v>702</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="40" t="str">
@@ -10595,16 +10601,16 @@
       </c>
       <c r="H89" s="40"/>
       <c r="I89" s="18" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="J89" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K89" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L89" s="49" t="s">
         <v>1245</v>
-      </c>
-      <c r="L89" s="49" t="s">
-        <v>1246</v>
       </c>
       <c r="M89" s="49"/>
       <c r="N89" s="49"/>
@@ -10647,10 +10653,10 @@
         <v>60</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="40" t="str">
@@ -10662,16 +10668,16 @@
         <v>B09</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="J90" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K90" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="L90" s="49" t="s">
         <v>1178</v>
-      </c>
-      <c r="L90" s="49" t="s">
-        <v>1179</v>
       </c>
       <c r="M90" s="49"/>
       <c r="N90" s="49"/>
@@ -10709,10 +10715,10 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="37" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E91" s="26">
         <v>10</v>
@@ -10724,7 +10730,7 @@
         <v>B10</v>
       </c>
       <c r="J91" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K91" s="5"/>
       <c r="L91" s="49"/>
@@ -10736,11 +10742,11 @@
       <c r="R91" s="83"/>
       <c r="S91" s="83"/>
       <c r="T91" s="5" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="U91" s="20"/>
       <c r="V91" s="5" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="W91" s="45"/>
       <c r="X91" s="2"/>
@@ -10757,10 +10763,10 @@
         <v>61</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F92" s="6"/>
       <c r="G92" s="40" t="str">
@@ -10769,16 +10775,16 @@
       </c>
       <c r="H92" s="40"/>
       <c r="I92" s="5" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="J92" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K92" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="L92" s="49" t="s">
         <v>1180</v>
-      </c>
-      <c r="L92" s="49" t="s">
-        <v>1181</v>
       </c>
       <c r="M92" s="49"/>
       <c r="N92" s="49"/>
@@ -10821,7 +10827,7 @@
         <v>62</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E93" s="26">
         <v>10</v>
@@ -10833,16 +10839,16 @@
       </c>
       <c r="H93" s="40"/>
       <c r="I93" s="5" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="J93" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="L93" s="49" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="M93" s="49"/>
       <c r="N93" s="49"/>
@@ -10885,7 +10891,7 @@
         <v>63</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E94" s="26">
         <v>11</v>
@@ -10900,16 +10906,16 @@
         <v>B11</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="J94" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K94" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L94" s="49" t="s">
         <v>1206</v>
-      </c>
-      <c r="L94" s="49" t="s">
-        <v>1207</v>
       </c>
       <c r="M94" s="49"/>
       <c r="N94" s="49"/>
@@ -10952,10 +10958,10 @@
         <v>64</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F95" s="6"/>
       <c r="G95" s="40" t="str">
@@ -10967,16 +10973,16 @@
         <v>B12</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="J95" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K95" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L95" s="49" t="s">
         <v>1182</v>
-      </c>
-      <c r="L95" s="49" t="s">
-        <v>1183</v>
       </c>
       <c r="M95" s="49"/>
       <c r="N95" s="49"/>
@@ -11019,7 +11025,7 @@
         <v>703</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E96" s="26">
         <v>99</v>
@@ -11031,16 +11037,16 @@
       </c>
       <c r="H96" s="40"/>
       <c r="I96" s="19" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="J96" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K96" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="L96" s="49" t="s">
         <v>1184</v>
-      </c>
-      <c r="L96" s="49" t="s">
-        <v>1185</v>
       </c>
       <c r="M96" s="49"/>
       <c r="N96" s="49"/>
@@ -11083,7 +11089,7 @@
         <v>704</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E97" s="26">
         <v>13</v>
@@ -11098,16 +11104,16 @@
         <v>B13</v>
       </c>
       <c r="I97" s="19" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K97" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L97" s="49" t="s">
         <v>1208</v>
-      </c>
-      <c r="L97" s="49" t="s">
-        <v>1209</v>
       </c>
       <c r="M97" s="49"/>
       <c r="N97" s="49"/>
@@ -11150,7 +11156,7 @@
         <v>705</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E98" s="26">
         <v>14</v>
@@ -11165,16 +11171,16 @@
         <v>B14</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="J98" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K98" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L98" s="49" t="s">
         <v>1248</v>
-      </c>
-      <c r="L98" s="49" t="s">
-        <v>1249</v>
       </c>
       <c r="M98" s="49"/>
       <c r="N98" s="49"/>
@@ -11217,7 +11223,7 @@
         <v>706</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E99" s="26">
         <v>15</v>
@@ -11232,16 +11238,16 @@
         <v>B15</v>
       </c>
       <c r="I99" s="16" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="J99" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K99" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="L99" s="19" t="s">
         <v>1186</v>
-      </c>
-      <c r="L99" s="19" t="s">
-        <v>1187</v>
       </c>
       <c r="M99" s="19"/>
       <c r="N99" s="19"/>
@@ -11284,7 +11290,7 @@
         <v>707</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E100" s="26">
         <v>99</v>
@@ -11296,16 +11302,16 @@
       </c>
       <c r="H100" s="40"/>
       <c r="I100" s="19" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="J100" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K100" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L100" s="49" t="s">
         <v>1188</v>
-      </c>
-      <c r="L100" s="49" t="s">
-        <v>1189</v>
       </c>
       <c r="M100" s="49"/>
       <c r="N100" s="49"/>
@@ -11348,7 +11354,7 @@
         <v>708</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E101" s="26">
         <v>99</v>
@@ -11360,16 +11366,16 @@
       </c>
       <c r="H101" s="40"/>
       <c r="I101" s="19" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="J101" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K101" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="L101" s="49" t="s">
         <v>1190</v>
-      </c>
-      <c r="L101" s="49" t="s">
-        <v>1191</v>
       </c>
       <c r="M101" s="49"/>
       <c r="N101" s="49"/>
@@ -11412,7 +11418,7 @@
         <v>709</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E102" s="26">
         <v>99</v>
@@ -11424,16 +11430,16 @@
       </c>
       <c r="H102" s="40"/>
       <c r="I102" s="19" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="J102" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K102" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L102" s="49" t="s">
         <v>1192</v>
-      </c>
-      <c r="L102" s="49" t="s">
-        <v>1193</v>
       </c>
       <c r="M102" s="49"/>
       <c r="N102" s="49"/>
@@ -11476,7 +11482,7 @@
         <v>710</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E103" s="26">
         <v>99</v>
@@ -11536,7 +11542,7 @@
         <v>711</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E104" s="26">
         <v>16</v>
@@ -11596,7 +11602,7 @@
         <v>712</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E105" s="26">
         <v>16</v>
@@ -11661,7 +11667,7 @@
         <v>713</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E106" s="26">
         <v>16</v>
@@ -11726,13 +11732,13 @@
         <v>714</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E107" s="26">
         <v>16</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G107" s="40" t="str">
         <f t="shared" si="10"/>
@@ -11791,7 +11797,7 @@
         <v>715</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E108" s="26">
         <v>17</v>
@@ -11854,7 +11860,7 @@
         <v>716</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E109" s="26">
         <v>99</v>
@@ -11869,16 +11875,16 @@
         <v>B99</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K109" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L109" s="49" t="s">
         <v>1210</v>
-      </c>
-      <c r="L109" s="49" t="s">
-        <v>1211</v>
       </c>
       <c r="M109" s="49"/>
       <c r="N109" s="49"/>
@@ -11917,7 +11923,7 @@
         <v>65</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E110" s="26">
         <v>99</v>
@@ -11929,10 +11935,10 @@
       </c>
       <c r="H110" s="40"/>
       <c r="K110" s="5" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="M110" s="5"/>
       <c r="N110" s="5"/>
@@ -11975,10 +11981,10 @@
         <v>66</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F111" s="6"/>
       <c r="G111" s="40" t="str">
@@ -11990,22 +11996,22 @@
         <v>D01</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="L111" s="49" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="M111" s="49" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="N111" s="49" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="O111" s="59" t="s">
         <v>975</v>
@@ -12033,7 +12039,7 @@
         <v>66</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
@@ -12048,10 +12054,10 @@
         <v>67</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F112" s="6"/>
       <c r="G112" s="40" t="s">
@@ -12064,18 +12070,18 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="L112" s="19" t="s">
         <v>1305</v>
-      </c>
-      <c r="L112" s="19" t="s">
-        <v>1306</v>
       </c>
       <c r="M112" s="19"/>
       <c r="N112" s="19"/>
       <c r="O112" s="59" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P112" s="62" t="s">
         <v>1305</v>
-      </c>
-      <c r="P112" s="62" t="s">
-        <v>1306</v>
       </c>
       <c r="Q112" s="65"/>
       <c r="R112" s="83" t="s">
@@ -12110,10 +12116,10 @@
         <v>717</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E113" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F113" s="6"/>
       <c r="G113" s="40" t="str">
@@ -12170,10 +12176,10 @@
         <v>718</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F114" s="6"/>
       <c r="G114" s="40" t="str">
@@ -12230,10 +12236,10 @@
         <v>719</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="40" t="str">
@@ -12290,10 +12296,10 @@
         <v>720</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E116" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="40" t="str">
@@ -12404,13 +12410,13 @@
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="32" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E118" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="40" t="s">
@@ -12432,11 +12438,11 @@
       <c r="R118" s="83"/>
       <c r="S118" s="83"/>
       <c r="T118" s="2" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="U118" s="20"/>
       <c r="V118" s="2" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="W118" s="45"/>
       <c r="X118" s="2"/>
@@ -12448,13 +12454,13 @@
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="32" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="40"/>
@@ -12474,11 +12480,11 @@
       <c r="R119" s="83"/>
       <c r="S119" s="83"/>
       <c r="T119" s="2" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="U119" s="20"/>
       <c r="V119" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="W119" s="45"/>
       <c r="X119" s="2"/>
@@ -12490,7 +12496,7 @@
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="35" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="26"/>
@@ -12575,10 +12581,10 @@
         <v>723</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E122" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F122" s="6"/>
       <c r="G122" s="40" t="str">
@@ -12635,10 +12641,10 @@
         <v>724</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E123" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F123" s="6"/>
       <c r="G123" s="40" t="str">
@@ -12695,10 +12701,10 @@
         <v>725</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F124" s="6"/>
       <c r="G124" s="40" t="str">
@@ -12755,10 +12761,10 @@
         <v>69</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E125" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F125" s="6"/>
       <c r="G125" s="40" t="str">
@@ -12772,13 +12778,13 @@
         <v>443</v>
       </c>
       <c r="L125" s="49" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="M125" s="49" t="s">
         <v>443</v>
       </c>
       <c r="N125" s="49" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="O125" s="59" t="s">
         <v>443</v>
@@ -12819,10 +12825,10 @@
         <v>70</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E126" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>1126</v>
@@ -12836,24 +12842,24 @@
         <v>D04a</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K126" s="5" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="L126" s="19" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="M126" s="19"/>
       <c r="N126" s="19"/>
       <c r="O126" s="59" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="P126" s="62" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="Q126" s="65"/>
       <c r="R126" s="83" t="s">
@@ -12941,10 +12947,10 @@
         <v>668</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>1127</v>
@@ -12958,14 +12964,14 @@
         <v>D04b</v>
       </c>
       <c r="I128" s="79" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="L128" s="49" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="M128" s="49"/>
       <c r="N128" s="49"/>
@@ -13008,13 +13014,13 @@
         <v>669</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E129" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G129" s="40" t="str">
         <f t="shared" si="11"/>
@@ -13073,13 +13079,13 @@
         <v>726</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E130" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G130" s="40" t="str">
         <f t="shared" si="11"/>
@@ -13138,10 +13144,10 @@
         <v>727</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E131" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F131" s="6"/>
       <c r="G131" s="40" t="str">
@@ -13193,10 +13199,10 @@
         <v>728</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E132" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F132" s="6"/>
       <c r="G132" s="40" t="str">
@@ -13205,16 +13211,16 @@
       </c>
       <c r="H132" s="40"/>
       <c r="I132" s="79" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="L132" s="19" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="M132" s="19"/>
       <c r="N132" s="19"/>
@@ -13244,7 +13250,7 @@
         <v>728</v>
       </c>
       <c r="X132" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.25">
@@ -13259,10 +13265,10 @@
         <v>72</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E133" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F133" s="6"/>
       <c r="G133" s="40" t="str">
@@ -13315,10 +13321,10 @@
         <v>73</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E134" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F134" s="6"/>
       <c r="G134" s="40" t="str">
@@ -13375,10 +13381,10 @@
         <v>729</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E135" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F135" s="6"/>
       <c r="G135" s="40" t="str">
@@ -13480,10 +13486,10 @@
         <v>730</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E137" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F137" s="6"/>
       <c r="G137" s="40" t="str">
@@ -13536,10 +13542,10 @@
         <v>731</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E138" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F138" s="6"/>
       <c r="G138" s="40" t="str">
@@ -13592,10 +13598,10 @@
         <v>75</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E139" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F139" s="6"/>
       <c r="G139" s="40" t="str">
@@ -13648,10 +13654,10 @@
         <v>76</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E140" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F140" s="6"/>
       <c r="G140" s="40" t="str">
@@ -13763,10 +13769,10 @@
         <v>732</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E142" s="26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F142" s="6"/>
       <c r="G142" s="40" t="str">
@@ -13826,10 +13832,10 @@
         <v>79</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E143" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F143" s="6"/>
       <c r="G143" s="40" t="str">
@@ -13886,10 +13892,10 @@
         <v>80</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E144" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F144" s="6"/>
       <c r="G144" s="40" t="str">
@@ -13946,10 +13952,10 @@
         <v>81</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E145" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F145" s="6"/>
       <c r="G145" s="40" t="str">
@@ -14006,10 +14012,10 @@
         <v>82</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E146" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="40" t="str">
@@ -14062,10 +14068,10 @@
         <v>83</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E147" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F147" s="6"/>
       <c r="G147" s="40" t="str">
@@ -14118,10 +14124,10 @@
         <v>84</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E148" s="26" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="F148" s="6"/>
       <c r="G148" s="40" t="str">
@@ -14133,16 +14139,16 @@
         <v>D06</v>
       </c>
       <c r="I148" s="57" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="J148" s="18" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K148" s="5" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="L148" s="58" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="M148" s="58"/>
       <c r="N148" s="58"/>
@@ -14240,7 +14246,7 @@
         <v>86</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E150" s="26">
         <v>99</v>
@@ -14296,7 +14302,7 @@
         <v>87</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E151" s="26">
         <v>99</v>
@@ -14352,7 +14358,7 @@
         <v>733</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E152" s="26">
         <v>99</v>
@@ -14408,7 +14414,7 @@
         <v>89</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E153" s="26">
         <v>99</v>
@@ -14464,7 +14470,7 @@
         <v>90</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E154" s="26">
         <v>99</v>
@@ -14481,7 +14487,7 @@
         <v>460</v>
       </c>
       <c r="L154" s="49" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="M154" s="49"/>
       <c r="N154" s="49"/>
@@ -14520,7 +14526,7 @@
         <v>91</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E155" s="26">
         <v>99</v>
@@ -14576,7 +14582,7 @@
         <v>92</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E156" s="26">
         <v>99</v>
@@ -14634,7 +14640,7 @@
         <v>93</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E157" s="26"/>
       <c r="F157" s="6"/>
@@ -14692,7 +14698,7 @@
         <v>94</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E158" s="26">
         <v>99</v>
@@ -14715,7 +14721,7 @@
         <v>464</v>
       </c>
       <c r="N158" s="49" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="O158" s="59" t="s">
         <v>464</v>
@@ -14756,10 +14762,10 @@
         <v>95</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E159" s="26" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F159" s="6"/>
       <c r="G159" s="40" t="str">
@@ -14823,10 +14829,10 @@
         <v>96</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E160" s="26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F160" s="6"/>
       <c r="G160" s="40" t="str">
@@ -14890,10 +14896,10 @@
         <v>97</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E161" s="26" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="40" t="str">
@@ -14905,22 +14911,22 @@
         <v>C03</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J161" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K161" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L161" s="49" t="s">
         <v>1226</v>
       </c>
-      <c r="L161" s="49" t="s">
-        <v>1227</v>
-      </c>
       <c r="M161" s="49" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="N161" s="49" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="O161" s="59" t="s">
         <v>467</v>
@@ -14961,10 +14967,10 @@
         <v>98</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E162" s="26" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="F162" s="6"/>
       <c r="G162" s="40" t="str">
@@ -14984,10 +14990,10 @@
         <v>830</v>
       </c>
       <c r="M162" s="49" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="N162" s="49" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="O162" s="59" t="s">
         <v>468</v>
@@ -15015,7 +15021,7 @@
         <v>98</v>
       </c>
       <c r="X162" s="76" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="163" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
@@ -15026,10 +15032,10 @@
       <c r="B163" s="2"/>
       <c r="C163" s="36"/>
       <c r="D163" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E163" s="26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F163" s="6"/>
       <c r="G163" s="40" t="str">
@@ -15041,22 +15047,22 @@
         <v>C05</v>
       </c>
       <c r="I163" s="5" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="J163" s="5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K163" s="5" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="L163" s="49" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="M163" s="49" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="N163" s="49" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="O163" s="59"/>
       <c r="P163" s="64"/>
@@ -15064,7 +15070,7 @@
       <c r="R163" s="83"/>
       <c r="S163" s="83"/>
       <c r="T163" s="5" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="U163" s="50"/>
       <c r="V163" s="5"/>
@@ -15083,7 +15089,7 @@
         <v>99</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E164" s="26">
         <v>99</v>
@@ -15098,22 +15104,22 @@
         <v>C99</v>
       </c>
       <c r="I164" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="J164" s="5" t="s">
         <v>1322</v>
       </c>
-      <c r="J164" s="5" t="s">
+      <c r="K164" s="5" t="s">
         <v>1323</v>
       </c>
-      <c r="K164" s="5" t="s">
+      <c r="L164" s="19" t="s">
         <v>1324</v>
       </c>
-      <c r="L164" s="19" t="s">
-        <v>1325</v>
-      </c>
       <c r="M164" s="19" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="N164" s="19" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="O164" s="59" t="s">
         <v>469</v>
@@ -15129,7 +15135,7 @@
         <v>1102</v>
       </c>
       <c r="T164" s="74" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="U164" s="52" t="s">
         <v>99</v>
@@ -15141,7 +15147,7 @@
         <v>99</v>
       </c>
       <c r="X164" s="76" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.25">
@@ -15213,10 +15219,10 @@
         <v>101</v>
       </c>
       <c r="D166" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E166" s="78" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="40" t="str">
@@ -15276,10 +15282,10 @@
         <v>102</v>
       </c>
       <c r="D167" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E167" s="78" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="F167" s="6"/>
       <c r="G167" s="40" t="str">
@@ -15336,13 +15342,13 @@
         <v>157</v>
       </c>
       <c r="C168" s="31" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D168" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E168" s="78" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="F168" s="6"/>
       <c r="G168" s="40" t="str">
@@ -15402,10 +15408,10 @@
         <v>104</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E169" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F169" s="6"/>
       <c r="G169" s="40" t="s">
@@ -15439,10 +15445,10 @@
         <v>682</v>
       </c>
       <c r="T169" s="76" t="s">
+        <v>1328</v>
+      </c>
+      <c r="U169" s="20" t="s">
         <v>1329</v>
-      </c>
-      <c r="U169" s="20" t="s">
-        <v>1330</v>
       </c>
       <c r="V169" s="2" t="s">
         <v>281</v>
@@ -15464,10 +15470,10 @@
         <v>105</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E170" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F170" s="6"/>
       <c r="G170" s="40" t="str">
@@ -15524,10 +15530,10 @@
         <v>106</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E171" s="26" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F171" s="6"/>
       <c r="G171" s="40" t="str">
@@ -15539,16 +15545,16 @@
         <v>D11</v>
       </c>
       <c r="I171" s="16" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J171" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K171" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="L171" s="49" t="s">
         <v>1201</v>
-      </c>
-      <c r="L171" s="49" t="s">
-        <v>1202</v>
       </c>
       <c r="M171" s="49"/>
       <c r="N171" s="49"/>
@@ -15591,10 +15597,10 @@
         <v>107</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E172" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F172" s="6"/>
       <c r="G172" s="40" t="str">
@@ -15651,10 +15657,10 @@
         <v>734</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E173" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="40" t="str">
@@ -15711,10 +15717,10 @@
         <v>735</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E174" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F174" s="6"/>
       <c r="G174" s="40" t="str">
@@ -15771,10 +15777,10 @@
         <v>667</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E175" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F175" s="6"/>
       <c r="G175" s="40" t="str">
@@ -15831,10 +15837,10 @@
         <v>736</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E176" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="40" t="str">
@@ -15891,10 +15897,10 @@
         <v>737</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E177" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F177" s="6"/>
       <c r="G177" s="40" t="str">
@@ -15951,10 +15957,10 @@
         <v>738</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E178" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F178" s="6"/>
       <c r="G178" s="40" t="str">
@@ -15963,16 +15969,16 @@
       </c>
       <c r="H178" s="40"/>
       <c r="I178" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J178" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="K178" s="5" t="s">
         <v>1203</v>
       </c>
-      <c r="J178" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="K178" s="5" t="s">
+      <c r="L178" s="49" t="s">
         <v>1204</v>
-      </c>
-      <c r="L178" s="49" t="s">
-        <v>1205</v>
       </c>
       <c r="M178" s="49"/>
       <c r="N178" s="49"/>
@@ -16070,10 +16076,10 @@
         <v>109</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E180" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F180" s="6"/>
       <c r="G180" s="40" t="s">
@@ -16134,10 +16140,10 @@
         <v>739</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E181" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>1126</v>
@@ -16201,10 +16207,10 @@
         <v>740</v>
       </c>
       <c r="D182" s="27" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E182" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>1127</v>
@@ -16268,13 +16274,13 @@
         <v>741</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E183" s="26" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G183" s="40" t="str">
         <f t="shared" si="18"/>
@@ -16335,7 +16341,7 @@
         <v>742</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E184" s="26">
         <v>99</v>
@@ -16391,7 +16397,7 @@
         <v>110</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E185" s="26">
         <v>99</v>
@@ -16451,7 +16457,7 @@
         <v>743</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E186" s="26">
         <v>99</v>
@@ -16511,7 +16517,7 @@
         <v>112</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E187" s="26">
         <v>99</v>
@@ -16571,7 +16577,7 @@
         <v>113</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E188" s="26">
         <v>99</v>
@@ -16631,7 +16637,7 @@
         <v>114</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E189" s="26">
         <v>99</v>
@@ -16748,7 +16754,7 @@
         <v>116</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E191" s="26">
         <v>99</v>
@@ -16808,7 +16814,7 @@
         <v>117</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E192" s="26">
         <v>99</v>
@@ -16864,7 +16870,7 @@
         <v>118</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E193" s="26">
         <v>99</v>
@@ -16920,7 +16926,7 @@
         <v>119</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E194" s="26">
         <v>99</v>
@@ -16976,7 +16982,7 @@
         <v>120</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E195" s="26">
         <v>99</v>
@@ -16988,16 +16994,16 @@
       </c>
       <c r="H195" s="40"/>
       <c r="I195" s="5" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="J195" s="5" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="K195" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L195" s="49" t="s">
         <v>1198</v>
-      </c>
-      <c r="L195" s="49" t="s">
-        <v>1199</v>
       </c>
       <c r="M195" s="49"/>
       <c r="N195" s="49"/>
@@ -17040,10 +17046,10 @@
         <v>121</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E196" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F196" s="6"/>
       <c r="G196" s="40" t="s">
@@ -17102,10 +17108,10 @@
         <v>122</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E197" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F197" s="6"/>
       <c r="G197" s="40" t="str">
@@ -17162,10 +17168,10 @@
         <v>123</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E198" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F198" s="6"/>
       <c r="G198" s="40" t="str">
@@ -17222,10 +17228,10 @@
         <v>124</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E199" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F199" s="6"/>
       <c r="G199" s="40" t="str">
@@ -17282,10 +17288,10 @@
         <v>125</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E200" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F200" s="6"/>
       <c r="G200" s="40" t="str">
@@ -17342,10 +17348,10 @@
         <v>126</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E201" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F201" s="6"/>
       <c r="G201" s="40" t="str">
@@ -17402,10 +17408,10 @@
         <v>127</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E202" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F202" s="6"/>
       <c r="G202" s="40" t="str">
@@ -17515,7 +17521,7 @@
         <v>129</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E204" s="26">
         <v>99</v>
@@ -17571,7 +17577,7 @@
         <v>130</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E205" s="26">
         <v>99</v>
@@ -17627,7 +17633,7 @@
         <v>131</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E206" s="26">
         <v>99</v>
@@ -17683,7 +17689,7 @@
         <v>744</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E207" s="26">
         <v>99</v>
@@ -17739,7 +17745,7 @@
         <v>132</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E208" s="26"/>
       <c r="F208" s="6"/>
@@ -17766,7 +17772,7 @@
       </c>
       <c r="Q208" s="62"/>
       <c r="R208" s="86" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="S208" s="83" t="s">
         <v>654</v>
@@ -17788,7 +17794,7 @@
     <row r="209" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...E.01. - Unintentional injuries</v>
+        <v/>
       </c>
       <c r="B209" s="2">
         <v>198</v>
@@ -17797,17 +17803,14 @@
         <v>133</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>1142</v>
+        <v>952</v>
       </c>
       <c r="E209" s="26" t="s">
-        <v>1143</v>
+        <v>952</v>
       </c>
       <c r="F209" s="6"/>
       <c r="G209" s="40"/>
-      <c r="H209" s="40" t="str">
-        <f>CONCATENATE(D209,E209,F209)</f>
-        <v>E01</v>
-      </c>
+      <c r="H209" s="40"/>
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="5" t="s">
@@ -17848,7 +17851,7 @@
     <row r="210" spans="1:24" ht="36" x14ac:dyDescent="0.25">
       <c r="A210" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.a. - Road injury</v>
+        <v>....E.01. . - Road injury</v>
       </c>
       <c r="B210" s="2">
         <v>199</v>
@@ -17857,33 +17860,33 @@
         <v>134</v>
       </c>
       <c r="D210" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E210" s="26" t="s">
         <v>1142</v>
       </c>
-      <c r="E210" s="26" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F210" s="6" t="s">
-        <v>1126</v>
+      <c r="F210" s="88" t="s">
+        <v>952</v>
       </c>
       <c r="G210" s="40" t="str">
         <f t="shared" ref="G210:G219" si="21">CONCATENATE("c",D210,E210,F210)</f>
-        <v>cE01a</v>
+        <v xml:space="preserve">cE01 </v>
       </c>
       <c r="H210" s="40" t="str">
         <f>CONCATENATE(D210,E210,F210)</f>
-        <v>E01a</v>
+        <v xml:space="preserve">E01 </v>
       </c>
       <c r="I210" s="5" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="J210" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K210" s="5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L210" s="19" t="s">
         <v>1194</v>
-      </c>
-      <c r="L210" s="19" t="s">
-        <v>1195</v>
       </c>
       <c r="M210" s="19"/>
       <c r="N210" s="19"/>
@@ -17917,36 +17920,36 @@
     <row r="211" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A211" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.b. - Substance use-associated poisonings</v>
+        <v>....E.02. . - Substance use-associated poisonings</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="31" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E211" s="26" t="s">
         <v>1143</v>
       </c>
-      <c r="F211" s="6" t="s">
-        <v>1127</v>
+      <c r="F211" s="88" t="s">
+        <v>952</v>
       </c>
       <c r="G211" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01b</v>
+        <v xml:space="preserve">cE02 </v>
       </c>
       <c r="H211" s="40" t="str">
         <f t="shared" ref="H211:H212" si="22">CONCATENATE(D211,E211,F211)</f>
-        <v>E01b</v>
+        <v xml:space="preserve">E02 </v>
       </c>
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="79" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="L211" s="80" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="M211" s="19"/>
       <c r="N211" s="19"/>
@@ -17956,7 +17959,7 @@
       <c r="R211" s="83"/>
       <c r="S211" s="83"/>
       <c r="T211" s="5" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="U211" s="20"/>
       <c r="V211" s="5"/>
@@ -17966,38 +17969,38 @@
     <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.c. - Poisonings (non-substance use)</v>
+        <v>....E.03. . - Poisonings (non-substance use)</v>
       </c>
       <c r="B212" s="2">
         <v>200</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E212" s="26" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F212" s="6" t="s">
-        <v>1130</v>
+        <v>1144</v>
+      </c>
+      <c r="F212" s="88" t="s">
+        <v>952</v>
       </c>
       <c r="G212" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01c</v>
+        <v xml:space="preserve">cE03 </v>
       </c>
       <c r="H212" s="40" t="str">
         <f t="shared" si="22"/>
-        <v>E01c</v>
+        <v xml:space="preserve">E03 </v>
       </c>
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
       <c r="K212" s="79" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="L212" s="81" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="M212" s="49"/>
       <c r="N212" s="49"/>
@@ -18015,7 +18018,7 @@
         <v>1006</v>
       </c>
       <c r="T212" s="5" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="U212" s="20" t="s">
         <v>135</v>
@@ -18031,7 +18034,7 @@
     <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.d. - Falls</v>
+        <v>....E.04. . - Falls</v>
       </c>
       <c r="B213" s="2">
         <v>201</v>
@@ -18040,21 +18043,21 @@
         <v>136</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E213" s="26" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F213" s="6" t="s">
-        <v>1153</v>
+        <v>1145</v>
+      </c>
+      <c r="F213" s="88" t="s">
+        <v>952</v>
       </c>
       <c r="G213" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01d</v>
+        <v xml:space="preserve">cE04 </v>
       </c>
       <c r="H213" s="40" t="str">
         <f>CONCATENATE(D213,E213,F213)</f>
-        <v>E01d</v>
+        <v xml:space="preserve">E04 </v>
       </c>
       <c r="I213" s="5" t="s">
         <v>952</v>
@@ -18107,17 +18110,17 @@
         <v>137</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E214" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G214" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H214" s="40"/>
       <c r="K214" s="5" t="s">
@@ -18167,17 +18170,17 @@
         <v>745</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E215" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G215" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H215" s="40"/>
       <c r="I215" s="5"/>
@@ -18229,26 +18232,26 @@
         <v>746</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E216" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G216" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H216" s="40"/>
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="L216" s="49" t="s">
         <v>1379</v>
-      </c>
-      <c r="L216" s="49" t="s">
-        <v>1381</v>
       </c>
       <c r="M216" s="49"/>
       <c r="N216" s="49"/>
@@ -18282,39 +18285,39 @@
     <row r="217" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A217" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.x. - Accidental Firearm</v>
+        <v>....E.05. . - Accidental Firearm</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="31" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E217" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G217" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H217" s="40" t="s">
         <v>952</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K217" s="5" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="L217" s="49" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="M217" s="49"/>
       <c r="N217" s="49"/>
@@ -18324,7 +18327,7 @@
       <c r="R217" s="83"/>
       <c r="S217" s="83"/>
       <c r="T217" s="5" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="U217" s="20"/>
       <c r="V217" s="5"/>
@@ -18343,30 +18346,30 @@
         <v>747</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E218" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G218" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H218" s="40"/>
       <c r="I218" s="5" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="J218" s="5" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K218" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="L218" s="49" t="s">
         <v>1196</v>
-      </c>
-      <c r="L218" s="49" t="s">
-        <v>1197</v>
       </c>
       <c r="M218" s="49"/>
       <c r="N218" s="49"/>
@@ -18396,7 +18399,7 @@
     <row r="219" spans="1:24" ht="33" x14ac:dyDescent="0.25">
       <c r="A219" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01.x. - Other unintentional injuries</v>
+        <v>....E.05. . - Other unintentional injuries</v>
       </c>
       <c r="B219" s="2">
         <v>206</v>
@@ -18405,33 +18408,33 @@
         <v>748</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E219" s="26" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>1128</v>
+        <v>952</v>
       </c>
       <c r="G219" s="40" t="str">
         <f t="shared" si="21"/>
-        <v>cE01x</v>
+        <v xml:space="preserve">cE05 </v>
       </c>
       <c r="H219" s="40" t="str">
         <f>CONCATENATE(D219,E219,F219)</f>
-        <v>E01x</v>
+        <v xml:space="preserve">E05 </v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="J219" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K219" s="5" t="s">
         <v>1254</v>
       </c>
-      <c r="K219" s="5" t="s">
+      <c r="L219" s="49" t="s">
         <v>1255</v>
-      </c>
-      <c r="L219" s="49" t="s">
-        <v>1256</v>
       </c>
       <c r="M219" s="49"/>
       <c r="N219" s="49"/>
@@ -18461,7 +18464,7 @@
         <v>887</v>
       </c>
       <c r="X219" s="22" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="220" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
@@ -18520,7 +18523,7 @@
     <row r="221" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A221" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...E.02. - Suicide/Self-harm</v>
+        <v>...E.07. - Suicide/Self-harm</v>
       </c>
       <c r="B221" s="2">
         <v>208</v>
@@ -18529,31 +18532,31 @@
         <v>140</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E221" s="26" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="F221" s="6"/>
       <c r="G221" s="40" t="str">
         <f t="shared" ref="G221:G228" si="23">CONCATENATE("c",D221,E221,F221)</f>
-        <v>cE02</v>
+        <v>cE07</v>
       </c>
       <c r="H221" s="40" t="str">
         <f>CONCATENATE(D221,E221,F221)</f>
-        <v>E02</v>
+        <v>E07</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="J221" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="K221" s="5" t="s">
         <v>1212</v>
       </c>
-      <c r="K221" s="5" t="s">
+      <c r="L221" s="49" t="s">
         <v>1213</v>
-      </c>
-      <c r="L221" s="49" t="s">
-        <v>1214</v>
       </c>
       <c r="M221" s="49"/>
       <c r="N221" s="49"/>
@@ -18571,7 +18574,7 @@
         <v>999</v>
       </c>
       <c r="T221" s="5" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="U221" s="20" t="s">
         <v>140</v>
@@ -18587,7 +18590,7 @@
     <row r="222" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A222" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>...E.03. - Homicide/Interpersonal violence</v>
+        <v>...E.08. - Homicide/Interpersonal violence</v>
       </c>
       <c r="B222" s="2">
         <v>209</v>
@@ -18596,10 +18599,10 @@
         <v>141</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E222" s="26" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F222" s="6"/>
       <c r="G222" s="40" t="s">
@@ -18607,11 +18610,11 @@
       </c>
       <c r="H222" s="40" t="str">
         <f>CONCATENATE(D222,E222,F222)</f>
-        <v>E03</v>
+        <v>E08</v>
       </c>
       <c r="I222" s="5"/>
       <c r="J222" s="5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="M222" s="19"/>
       <c r="N222" s="19"/>
@@ -18629,7 +18632,7 @@
         <v>998</v>
       </c>
       <c r="T222" s="5" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="U222" s="20" t="s">
         <v>141</v>
@@ -18645,36 +18648,36 @@
     <row r="223" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A223" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.a. - Homicide excluding legal intervention</v>
+        <v>....E.08.a. - Homicide excluding legal intervention</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" s="31"/>
       <c r="D223" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E223" s="26" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F223" s="6" t="s">
         <v>1126</v>
       </c>
       <c r="G223" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03a</v>
+        <v>cE08a</v>
       </c>
       <c r="H223" s="40" t="str">
         <f t="shared" ref="H223:H225" si="24">CONCATENATE(D223,E223,F223)</f>
-        <v>E03a</v>
+        <v>E08a</v>
       </c>
       <c r="I223" s="5" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="J223" s="5"/>
       <c r="K223" s="5" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="L223" s="19" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="M223" s="19"/>
       <c r="N223" s="19"/>
@@ -18684,7 +18687,7 @@
       <c r="R223" s="83"/>
       <c r="S223" s="83"/>
       <c r="T223" s="20" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="U223" s="46"/>
       <c r="V223" s="5"/>
@@ -18694,38 +18697,38 @@
     <row r="224" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.b. - Legal intervention</v>
+        <v>....E.08.b. - Legal intervention</v>
       </c>
       <c r="B224" s="2"/>
       <c r="C224" s="31"/>
       <c r="D224" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E224" s="26" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>1127</v>
       </c>
       <c r="G224" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03b</v>
+        <v>cE08b</v>
       </c>
       <c r="H224" s="40" t="str">
         <f t="shared" si="24"/>
-        <v>E03b</v>
+        <v>E08b</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="J224" s="5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K224" s="5" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="L224" s="19" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="M224" s="19"/>
       <c r="N224" s="19"/>
@@ -18735,7 +18738,7 @@
       <c r="R224" s="83"/>
       <c r="S224" s="83"/>
       <c r="T224" s="20" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="U224" s="46"/>
       <c r="V224" s="5"/>
@@ -18745,7 +18748,7 @@
     <row r="225" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A225" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03.c. - Execution, War, Terroism</v>
+        <v>....E.08.c. - Execution, War, Terroism</v>
       </c>
       <c r="B225" s="2">
         <v>210</v>
@@ -18754,33 +18757,33 @@
         <v>142</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E225" s="26" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G225" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE03c</v>
+        <v>cE08c</v>
       </c>
       <c r="H225" s="40" t="str">
         <f t="shared" si="24"/>
-        <v>E03c</v>
+        <v>E08c</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="J225" s="5" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K225" s="5" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="L225" s="49" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="M225" s="49"/>
       <c r="N225" s="49"/>
@@ -18794,7 +18797,7 @@
       <c r="R225" s="83"/>
       <c r="S225" s="83"/>
       <c r="T225" s="5" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="U225" s="20" t="s">
         <v>142</v>
@@ -18806,7 +18809,7 @@
         <v>142</v>
       </c>
       <c r="X225" s="22" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="226" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
@@ -18815,36 +18818,36 @@
         <v/>
       </c>
       <c r="B226" s="77" t="s">
-        <v>1331</v>
+        <v>1401</v>
       </c>
       <c r="C226" s="16" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D226" s="54" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E226" s="55" t="s">
-        <v>1143</v>
+        <v>952</v>
       </c>
       <c r="G226" s="40" t="str">
         <f t="shared" si="23"/>
-        <v>cE01</v>
+        <v xml:space="preserve">cE </v>
       </c>
       <c r="H226" s="40"/>
       <c r="I226" s="48" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="J226" s="48" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K226" s="16" t="s">
         <v>1269</v>
       </c>
-      <c r="K226" s="16" t="s">
+      <c r="L226" s="16" t="s">
         <v>1270</v>
       </c>
-      <c r="L226" s="16" t="s">
-        <v>1271</v>
-      </c>
       <c r="T226" s="48" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="227" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
@@ -18853,10 +18856,10 @@
         <v>...Z.01. - Symptoms, signs and ill-defined conditions, not elsewhere classified</v>
       </c>
       <c r="D227" s="56" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E227" s="55" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G227" s="40" t="str">
         <f t="shared" si="23"/>
@@ -18867,19 +18870,19 @@
         <v>Z01</v>
       </c>
       <c r="I227" s="48" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J227" s="48" t="s">
         <v>1221</v>
       </c>
-      <c r="J227" s="48" t="s">
+      <c r="K227" s="16" t="s">
         <v>1222</v>
       </c>
-      <c r="K227" s="16" t="s">
+      <c r="L227" s="16" t="s">
+        <v>1251</v>
+      </c>
+      <c r="T227" s="48" t="s">
         <v>1223</v>
-      </c>
-      <c r="L227" s="16" t="s">
-        <v>1252</v>
-      </c>
-      <c r="T227" s="48" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="228" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
@@ -18888,10 +18891,10 @@
         <v/>
       </c>
       <c r="D228" s="56" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E228" s="55" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G228" s="42" t="str">
         <f t="shared" si="23"/>
@@ -18899,19 +18902,19 @@
       </c>
       <c r="H228" s="40"/>
       <c r="I228" s="16" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="J228" s="48" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="K228" s="16" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="L228" s="16" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="T228" s="48" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.25">
@@ -18920,10 +18923,10 @@
         <v>...Z.02. - Unknown/Missing Value</v>
       </c>
       <c r="D229" s="56" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E229" s="55" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G229" s="43"/>
       <c r="H229" s="40" t="str">
@@ -18931,7 +18934,7 @@
         <v>Z02</v>
       </c>
       <c r="T229" s="48" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="230" spans="1:24" x14ac:dyDescent="0.25">
@@ -18940,10 +18943,10 @@
         <v>...Z.03. - Code does not map</v>
       </c>
       <c r="D230" s="56" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E230" s="55" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G230" s="43"/>
       <c r="H230" s="40" t="str">
@@ -18951,10 +18954,10 @@
         <v>Z03</v>
       </c>
       <c r="I230" s="16" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="T230" s="48" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="231" spans="1:24" x14ac:dyDescent="0.25">
@@ -18963,7 +18966,7 @@
         <v>..Z. - Unknown/Missing Value</v>
       </c>
       <c r="D231" s="56" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G231" s="43"/>
       <c r="H231" s="40" t="str">
@@ -18971,7 +18974,7 @@
         <v>Z</v>
       </c>
       <c r="T231" s="48" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="232" spans="1:24" x14ac:dyDescent="0.25">
@@ -18980,10 +18983,10 @@
         <v>...D.99. - Other Chronic Conditions</v>
       </c>
       <c r="D232" s="56" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E232" s="55" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G232" s="43"/>
       <c r="H232" s="40" t="str">
@@ -18991,7 +18994,7 @@
         <v>D99</v>
       </c>
       <c r="T232" s="48" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
   </sheetData>
@@ -19222,24 +19225,24 @@
   <sheetData>
     <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="70" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D11" s="71" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E11" s="71" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="12" spans="3:5" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="72" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D12" s="73" t="s">
         <v>1317</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="E12" s="73" t="s">
         <v>1318</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>1319</v>
       </c>
     </row>
   </sheetData>

--- a/myCBD/myInfo/gbd.ICD.Map.xlsx
+++ b/myCBD/myInfo/gbd.ICD.Map.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0.CBD\myCBD\myInfo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="10935"/>
   </bookViews>
@@ -19,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$X$225</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -36,7 +31,7 @@
     <author>Dauphine, David (CDPH-CHSI)</author>
   </authors>
   <commentList>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C57" authorId="1" shapeId="0">
+    <comment ref="C57" authorId="1">
       <text>
         <r>
           <rPr>
@@ -84,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P126" authorId="2" shapeId="0">
+    <comment ref="P126" authorId="2">
       <text>
         <r>
           <rPr>
@@ -113,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2869" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1418">
   <si>
     <t>I. Communicable, maternal, perinatal and nutritional conditions</t>
   </si>
@@ -4339,9 +4334,6 @@
     <t>Y35[0-4]|Y35[6-9]|Y890</t>
   </si>
   <si>
-    <t>Execution, War, Terroism</t>
-  </si>
-  <si>
     <t>W32-W34.9</t>
   </si>
   <si>
@@ -4373,12 +4365,6 @@
     <t>2. Non-SA Poisonings</t>
   </si>
   <si>
-    <t>X42|X44</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> X42, X44</t>
-  </si>
-  <si>
     <t>DELETED X42 and X44 per CDPH review (1/9/2019) - to Substance Use - associated poisonings;</t>
   </si>
   <si>
@@ -4388,19 +4374,10 @@
     <t>F1[3,6,8,9]|P044</t>
   </si>
   <si>
-    <t>X4[0,1,3,6-9]</t>
-  </si>
-  <si>
-    <t>X40, X41, X43, X46-X49</t>
-  </si>
-  <si>
     <t>E.2. Substance use disorders</t>
   </si>
   <si>
     <t>Substance use disorders</t>
-  </si>
-  <si>
-    <t>Substance use-associated poisonings</t>
   </si>
   <si>
     <r>
@@ -4463,16 +4440,82 @@
     <t>Added P044  ; as above moved X41 to Poisonings (non-substance)</t>
   </si>
   <si>
-    <t>Poisonings (non-substance use)</t>
-  </si>
-  <si>
     <t>INCLUDED ALL INJURY but not elsewhere</t>
+  </si>
+  <si>
+    <t>Drug poisonings</t>
+  </si>
+  <si>
+    <t>Poisonings (non-drug)</t>
+  </si>
+  <si>
+    <t>(moved x40,x41, and x 43 Up one</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> X40- X44</t>
+  </si>
+  <si>
+    <t>X46-X49</t>
+  </si>
+  <si>
+    <t>X4[6-9]</t>
+  </si>
+  <si>
+    <t>Gonorrhea</t>
+  </si>
+  <si>
+    <t>Diarrheal diseases</t>
+  </si>
+  <si>
+    <t>Maternal hemorrhage</t>
+  </si>
+  <si>
+    <t>Esophagus cancer</t>
+  </si>
+  <si>
+    <t>Leukemia</t>
+  </si>
+  <si>
+    <t>Autism and Asperger syndrome</t>
+  </si>
+  <si>
+    <t>Childhood behavioral disorders</t>
+  </si>
+  <si>
+    <t>Other mental and behavioral disorders</t>
+  </si>
+  <si>
+    <t>Ischemic heart disease</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease due to diabetes</t>
+  </si>
+  <si>
+    <t>Execution, War, Terrorism</t>
+  </si>
+  <si>
+    <t>Obstructed labor</t>
+  </si>
+  <si>
+    <t>Iron-deficiency anemia</t>
+  </si>
+  <si>
+    <t>Nasopharynx</t>
+  </si>
+  <si>
+    <t>Gallbladder and biliary tract cancer</t>
+  </si>
+  <si>
+    <t>Other haemoglobinopathies and hemolytic anemias</t>
+  </si>
+  <si>
+    <t>X4[0-4]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.;###0."/>
   </numFmts>
@@ -5157,7 +5200,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5192,7 +5235,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6032,7 +6075,7 @@
         <v>1047</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>149</v>
+        <v>1401</v>
       </c>
       <c r="U11" s="20" t="s">
         <v>6</v>
@@ -6386,7 +6429,7 @@
         <v>1059</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>155</v>
+        <v>1402</v>
       </c>
       <c r="U17" s="20" t="s">
         <v>10</v>
@@ -8676,7 +8719,7 @@
         <v>1066</v>
       </c>
       <c r="T57" s="5" t="s">
-        <v>193</v>
+        <v>1403</v>
       </c>
       <c r="U57" s="20" t="s">
         <v>33</v>
@@ -8872,7 +8915,7 @@
         <v>1065</v>
       </c>
       <c r="T60" s="5" t="s">
-        <v>196</v>
+        <v>1412</v>
       </c>
       <c r="U60" s="20" t="s">
         <v>36</v>
@@ -9583,7 +9626,7 @@
         <v>1033</v>
       </c>
       <c r="T72" s="5" t="s">
-        <v>208</v>
+        <v>1413</v>
       </c>
       <c r="U72" s="20" t="s">
         <v>48</v>
@@ -9688,7 +9731,7 @@
       </c>
       <c r="Q74" s="59"/>
       <c r="R74" s="86" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
       <c r="S74" s="83" t="s">
         <v>557</v>
@@ -9977,7 +10020,7 @@
         <v>1087</v>
       </c>
       <c r="T79" s="5" t="s">
-        <v>214</v>
+        <v>1414</v>
       </c>
       <c r="U79" s="50" t="s">
         <v>896</v>
@@ -10053,7 +10096,7 @@
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="44" t="str">
         <f t="shared" si="5"/>
-        <v>...B.02. - Oesophagus cancer</v>
+        <v>...B.02. - Esophagus cancer</v>
       </c>
       <c r="B81" s="2">
         <v>75</v>
@@ -10104,7 +10147,7 @@
         <v>1089</v>
       </c>
       <c r="T81" s="5" t="s">
-        <v>216</v>
+        <v>1404</v>
       </c>
       <c r="U81" s="50" t="s">
         <v>53</v>
@@ -11329,7 +11372,7 @@
         <v>1075</v>
       </c>
       <c r="T100" s="5" t="s">
-        <v>897</v>
+        <v>1415</v>
       </c>
       <c r="U100" s="20" t="s">
         <v>707</v>
@@ -11788,7 +11831,7 @@
     <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="44" t="str">
         <f t="shared" si="5"/>
-        <v>...B.17. - Leukaemia</v>
+        <v>...B.17. - Leukemia</v>
       </c>
       <c r="B108" s="2">
         <v>101</v>
@@ -11835,7 +11878,7 @@
         <v>1030</v>
       </c>
       <c r="T108" s="5" t="s">
-        <v>235</v>
+        <v>1405</v>
       </c>
       <c r="U108" s="20" t="s">
         <v>715</v>
@@ -12271,7 +12314,7 @@
         <v>1105</v>
       </c>
       <c r="T115" s="5" t="s">
-        <v>242</v>
+        <v>1416</v>
       </c>
       <c r="U115" s="5" t="s">
         <v>719</v>
@@ -12454,7 +12497,7 @@
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="32" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>1140</v>
@@ -12480,7 +12523,7 @@
       <c r="R119" s="83"/>
       <c r="S119" s="83"/>
       <c r="T119" s="2" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="U119" s="20"/>
       <c r="V119" s="2" t="s">
@@ -12964,14 +13007,14 @@
         <v>D04b</v>
       </c>
       <c r="I128" s="79" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="L128" s="49" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="M128" s="49"/>
       <c r="N128" s="49"/>
@@ -13211,16 +13254,16 @@
       </c>
       <c r="H132" s="40"/>
       <c r="I132" s="79" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="J132" s="5" t="s">
         <v>1159</v>
       </c>
       <c r="K132" s="5" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="L132" s="19" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="M132" s="19"/>
       <c r="N132" s="19"/>
@@ -13412,7 +13455,7 @@
       <c r="R135" s="83"/>
       <c r="S135" s="83"/>
       <c r="T135" s="5" t="s">
-        <v>914</v>
+        <v>1406</v>
       </c>
       <c r="U135" s="5" t="s">
         <v>918</v>
@@ -13461,7 +13504,7 @@
       <c r="R136" s="83"/>
       <c r="S136" s="83"/>
       <c r="T136" s="5" t="s">
-        <v>915</v>
+        <v>1407</v>
       </c>
       <c r="U136" s="5" t="s">
         <v>74</v>
@@ -13685,7 +13728,7 @@
       <c r="R140" s="83"/>
       <c r="S140" s="83"/>
       <c r="T140" s="5" t="s">
-        <v>253</v>
+        <v>1408</v>
       </c>
       <c r="U140" s="20" t="s">
         <v>76</v>
@@ -14820,7 +14863,7 @@
     <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="44" t="str">
         <f t="shared" si="12"/>
-        <v>...C.02. - Ischaemic heart disease</v>
+        <v>...C.02. - Ischemic heart disease</v>
       </c>
       <c r="B160" s="2">
         <v>150</v>
@@ -14871,7 +14914,7 @@
         <v>1029</v>
       </c>
       <c r="T160" s="5" t="s">
-        <v>273</v>
+        <v>1409</v>
       </c>
       <c r="U160" s="50" t="s">
         <v>96</v>
@@ -16198,7 +16241,7 @@
     <row r="182" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A182" s="44" t="str">
         <f t="shared" si="12"/>
-        <v>....D.10.b. - Chronic kidney diesease due to diabetes</v>
+        <v>....D.10.b. - Chronic kidney disease due to diabetes</v>
       </c>
       <c r="B182" s="2">
         <v>171</v>
@@ -16249,7 +16292,7 @@
         <v>2504</v>
       </c>
       <c r="T182" s="5" t="s">
-        <v>926</v>
+        <v>1410</v>
       </c>
       <c r="U182" s="5" t="s">
         <v>928</v>
@@ -17772,7 +17815,7 @@
       </c>
       <c r="Q208" s="62"/>
       <c r="R208" s="86" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="S208" s="83" t="s">
         <v>654</v>
@@ -17851,7 +17894,7 @@
     <row r="210" spans="1:24" ht="36" x14ac:dyDescent="0.25">
       <c r="A210" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.01. . - Road injury</v>
+        <v>...E.01. - Road injury</v>
       </c>
       <c r="B210" s="2">
         <v>199</v>
@@ -17865,16 +17908,14 @@
       <c r="E210" s="26" t="s">
         <v>1142</v>
       </c>
-      <c r="F210" s="88" t="s">
-        <v>952</v>
-      </c>
+      <c r="F210" s="88"/>
       <c r="G210" s="40" t="str">
         <f t="shared" ref="G210:G219" si="21">CONCATENATE("c",D210,E210,F210)</f>
-        <v xml:space="preserve">cE01 </v>
+        <v>cE01</v>
       </c>
       <c r="H210" s="40" t="str">
         <f>CONCATENATE(D210,E210,F210)</f>
-        <v xml:space="preserve">E01 </v>
+        <v>E01</v>
       </c>
       <c r="I210" s="5" t="s">
         <v>1234</v>
@@ -17917,14 +17958,14 @@
       </c>
       <c r="X210" s="2"/>
     </row>
-    <row r="211" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:24" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.02. . - Substance use-associated poisonings</v>
+        <v>...E.02. - Drug poisonings</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="31" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>1141</v>
@@ -17932,24 +17973,24 @@
       <c r="E211" s="26" t="s">
         <v>1143</v>
       </c>
-      <c r="F211" s="88" t="s">
-        <v>952</v>
-      </c>
+      <c r="F211" s="88"/>
       <c r="G211" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE02 </v>
+        <v>cE02</v>
       </c>
       <c r="H211" s="40" t="str">
         <f t="shared" ref="H211:H212" si="22">CONCATENATE(D211,E211,F211)</f>
-        <v xml:space="preserve">E02 </v>
-      </c>
-      <c r="I211" s="5"/>
+        <v>E02</v>
+      </c>
+      <c r="I211" t="s">
+        <v>952</v>
+      </c>
       <c r="J211" s="5"/>
       <c r="K211" s="79" t="s">
-        <v>1384</v>
+        <v>1398</v>
       </c>
       <c r="L211" s="80" t="s">
-        <v>1383</v>
+        <v>1417</v>
       </c>
       <c r="M211" s="19"/>
       <c r="N211" s="19"/>
@@ -17959,23 +18000,23 @@
       <c r="R211" s="83"/>
       <c r="S211" s="83"/>
       <c r="T211" s="5" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="U211" s="20"/>
       <c r="V211" s="5"/>
       <c r="W211" s="45"/>
       <c r="X211" s="2"/>
     </row>
-    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:24" ht="51" x14ac:dyDescent="0.25">
       <c r="A212" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.03. . - Poisonings (non-substance use)</v>
+        <v>...E.03. - Poisonings (non-drug)</v>
       </c>
       <c r="B212" s="2">
         <v>200</v>
       </c>
       <c r="C212" s="31" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>1141</v>
@@ -17983,24 +18024,24 @@
       <c r="E212" s="26" t="s">
         <v>1144</v>
       </c>
-      <c r="F212" s="88" t="s">
-        <v>952</v>
-      </c>
+      <c r="F212" s="88"/>
       <c r="G212" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE03 </v>
+        <v>cE03</v>
       </c>
       <c r="H212" s="40" t="str">
         <f t="shared" si="22"/>
-        <v xml:space="preserve">E03 </v>
+        <v>E03</v>
       </c>
       <c r="I212" s="5"/>
-      <c r="J212" s="5"/>
+      <c r="J212" s="5" t="s">
+        <v>1397</v>
+      </c>
       <c r="K212" s="79" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="L212" s="81" t="s">
-        <v>1388</v>
+        <v>1400</v>
       </c>
       <c r="M212" s="49"/>
       <c r="N212" s="49"/>
@@ -18018,7 +18059,7 @@
         <v>1006</v>
       </c>
       <c r="T212" s="5" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="U212" s="20" t="s">
         <v>135</v>
@@ -18034,7 +18075,7 @@
     <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.04. . - Falls</v>
+        <v>...E.04. - Falls</v>
       </c>
       <c r="B213" s="2">
         <v>201</v>
@@ -18048,16 +18089,14 @@
       <c r="E213" s="26" t="s">
         <v>1145</v>
       </c>
-      <c r="F213" s="88" t="s">
-        <v>952</v>
-      </c>
+      <c r="F213" s="88"/>
       <c r="G213" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE04 </v>
+        <v>cE04</v>
       </c>
       <c r="H213" s="40" t="str">
         <f>CONCATENATE(D213,E213,F213)</f>
-        <v xml:space="preserve">E04 </v>
+        <v>E04</v>
       </c>
       <c r="I213" s="5" t="s">
         <v>952</v>
@@ -18115,12 +18154,10 @@
       <c r="E214" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F214" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F214" s="6"/>
       <c r="G214" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
+        <v>cE05</v>
       </c>
       <c r="H214" s="40"/>
       <c r="K214" s="5" t="s">
@@ -18175,12 +18212,10 @@
       <c r="E215" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F215" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F215" s="6"/>
       <c r="G215" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
+        <v>cE05</v>
       </c>
       <c r="H215" s="40"/>
       <c r="I215" s="5"/>
@@ -18237,21 +18272,19 @@
       <c r="E216" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F216" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F216" s="6"/>
       <c r="G216" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
+        <v>cE05</v>
       </c>
       <c r="H216" s="40"/>
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="5" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="L216" s="49" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="M216" s="49"/>
       <c r="N216" s="49"/>
@@ -18285,11 +18318,11 @@
     <row r="217" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A217" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.05. . - Accidental Firearm</v>
+        <v/>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="31" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>1141</v>
@@ -18297,27 +18330,23 @@
       <c r="E217" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F217" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F217" s="6"/>
       <c r="G217" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
-      </c>
-      <c r="H217" s="40" t="s">
-        <v>952</v>
-      </c>
+        <v>cE05</v>
+      </c>
+      <c r="H217" s="40"/>
       <c r="I217" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>1211</v>
       </c>
       <c r="K217" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L217" s="49" t="s">
         <v>1373</v>
-      </c>
-      <c r="L217" s="49" t="s">
-        <v>1374</v>
       </c>
       <c r="M217" s="49"/>
       <c r="N217" s="49"/>
@@ -18327,7 +18356,7 @@
       <c r="R217" s="83"/>
       <c r="S217" s="83"/>
       <c r="T217" s="5" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="U217" s="20"/>
       <c r="V217" s="5"/>
@@ -18351,12 +18380,10 @@
       <c r="E218" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F218" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F218" s="6"/>
       <c r="G218" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
+        <v>cE05</v>
       </c>
       <c r="H218" s="40"/>
       <c r="I218" s="5" t="s">
@@ -18399,7 +18426,7 @@
     <row r="219" spans="1:24" ht="33" x14ac:dyDescent="0.25">
       <c r="A219" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.05. . - Other unintentional injuries</v>
+        <v>...E.05. - Other unintentional injuries</v>
       </c>
       <c r="B219" s="2">
         <v>206</v>
@@ -18413,19 +18440,17 @@
       <c r="E219" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="F219" s="6" t="s">
-        <v>952</v>
-      </c>
+      <c r="F219" s="6"/>
       <c r="G219" s="40" t="str">
         <f t="shared" si="21"/>
-        <v xml:space="preserve">cE05 </v>
+        <v>cE05</v>
       </c>
       <c r="H219" s="40" t="str">
         <f>CONCATENATE(D219,E219,F219)</f>
-        <v xml:space="preserve">E05 </v>
+        <v>E05</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="J219" s="5" t="s">
         <v>1253</v>
@@ -18666,11 +18691,11 @@
         <v>cE08a</v>
       </c>
       <c r="H223" s="40" t="str">
-        <f t="shared" ref="H223:H225" si="24">CONCATENATE(D223,E223,F223)</f>
+        <f t="shared" ref="H223:H226" si="24">CONCATENATE(D223,E223,F223)</f>
         <v>E08a</v>
       </c>
       <c r="I223" s="5" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="J223" s="5"/>
       <c r="K223" s="5" t="s">
@@ -18719,7 +18744,7 @@
         <v>E08b</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="J224" s="5" t="s">
         <v>1211</v>
@@ -18748,7 +18773,7 @@
     <row r="225" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A225" s="44" t="str">
         <f t="shared" si="19"/>
-        <v>....E.08.c. - Execution, War, Terroism</v>
+        <v>....E.08.c. - Execution, War, Terrorism</v>
       </c>
       <c r="B225" s="2">
         <v>210</v>
@@ -18774,7 +18799,7 @@
         <v>E08c</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
       <c r="J225" s="5" t="s">
         <v>1236</v>
@@ -18797,7 +18822,7 @@
       <c r="R225" s="83"/>
       <c r="S225" s="83"/>
       <c r="T225" s="5" t="s">
-        <v>1372</v>
+        <v>1411</v>
       </c>
       <c r="U225" s="20" t="s">
         <v>142</v>
@@ -18815,10 +18840,10 @@
     <row r="226" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A226" s="44" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>...E.99. - Injuries of unknown intent (e.g., unintentional or self-harm), including overdoses and deaths by firearm</v>
       </c>
       <c r="B226" s="77" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="C226" s="16" t="s">
         <v>1275</v>
@@ -18827,13 +18852,16 @@
         <v>1141</v>
       </c>
       <c r="E226" s="55" t="s">
-        <v>952</v>
+        <v>1224</v>
       </c>
       <c r="G226" s="40" t="str">
         <f t="shared" si="23"/>
-        <v xml:space="preserve">cE </v>
-      </c>
-      <c r="H226" s="40"/>
+        <v>cE99</v>
+      </c>
+      <c r="H226" s="40" t="str">
+        <f t="shared" si="24"/>
+        <v>E99</v>
+      </c>
       <c r="I226" s="48" t="s">
         <v>1252</v>
       </c>

--- a/myCBD/myInfo/gbd.ICD.Map.xlsx
+++ b/myCBD/myInfo/gbd.ICD.Map.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$X$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$Y$225</definedName>
   </definedNames>
   <calcPr calcId="145621"/>
   <extLst>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="1418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="1422">
   <si>
     <t>I. Communicable, maternal, perinatal and nutritional conditions</t>
   </si>
@@ -4510,6 +4510,18 @@
   </si>
   <si>
     <t>X4[0-4]</t>
+  </si>
+  <si>
+    <t>shortName</t>
+  </si>
+  <si>
+    <t>HIV/STDs</t>
+  </si>
+  <si>
+    <t>Other cardiovascular</t>
+  </si>
+  <si>
+    <t>Lung cancers</t>
   </si>
 </sst>
 </file>
@@ -5444,7 +5456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X232"/>
+  <dimension ref="A1:Y232"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.42578125" style="44" customWidth="1"/>
@@ -5466,15 +5478,15 @@
     <col min="17" max="17" width="38.42578125" style="69" customWidth="1"/>
     <col min="18" max="18" width="62.140625" style="87" customWidth="1"/>
     <col min="19" max="19" width="40.7109375" style="87" customWidth="1"/>
-    <col min="20" max="20" width="50.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="50.85546875" style="48" customWidth="1"/>
-    <col min="22" max="22" width="50.85546875" style="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="50.85546875" style="46" customWidth="1"/>
-    <col min="24" max="24" width="50.42578125" style="46" customWidth="1"/>
-    <col min="25" max="16384" width="8.85546875" style="46"/>
+    <col min="20" max="21" width="50.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="50.85546875" style="48" customWidth="1"/>
+    <col min="23" max="23" width="50.85546875" style="46" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="50.85546875" style="46" customWidth="1"/>
+    <col min="25" max="25" width="50.42578125" style="46" customWidth="1"/>
+    <col min="26" max="16384" width="8.85546875" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>1157</v>
       </c>
@@ -5535,22 +5547,25 @@
       <c r="T1" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="U1" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="V1" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="W1" s="45" t="s">
+      <c r="X1" s="45" t="s">
         <v>1162</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="str">
-        <f>CONCATENATE(".",V2)</f>
+        <f>CONCATENATE(".",W2)</f>
         <v>.All CAUSES</v>
       </c>
       <c r="B2" s="2">
@@ -5592,9 +5607,12 @@
       <c r="W2" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="X2" s="6"/>
-    </row>
-    <row r="3" spans="1:24" ht="41.25" x14ac:dyDescent="0.25">
+      <c r="X2" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="Y2" s="6"/>
+    </row>
+    <row r="3" spans="1:25" ht="41.25" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="str">
         <f>IF(H3&lt;&gt;"",IF(F3&lt;&gt;"",CONCATENATE("....",D3,".",E3,".",F3,". - ",T3),IF(E3&lt;&gt;"",CONCATENATE("...",D3,".",E3,". - ",T3),CONCATENATE("..",D3,". - ",T3))),"")</f>
         <v>..A. - Communicable, maternal, perinatal and nutritional conditions</v>
@@ -5637,18 +5655,21 @@
       <c r="T3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="U3" s="20" t="s">
+      <c r="U3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="V3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="W3" s="45" t="s">
+      <c r="X3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="X3" s="2"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y3" s="2"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="44" t="str">
         <f t="shared" ref="A4:A67" si="0">IF(H4&lt;&gt;"",IF(F4&lt;&gt;"",CONCATENATE("....",D4,".",E4,".",F4,". - ",T4),IF(E4&lt;&gt;"",CONCATENATE("...",D4,".",E4,". - ",T4),CONCATENATE("..",D4,". - ",T4))),"")</f>
         <v>...A.99. - Other Infectious Diseases</v>
@@ -5683,14 +5704,17 @@
       <c r="T4" s="20" t="s">
         <v>1128</v>
       </c>
-      <c r="U4" s="20"/>
-      <c r="V4" s="3" t="s">
+      <c r="U4" s="20" t="s">
         <v>1128</v>
       </c>
-      <c r="W4" s="45"/>
-      <c r="X4" s="2"/>
-    </row>
-    <row r="5" spans="1:24" ht="24" x14ac:dyDescent="0.25">
+      <c r="V4" s="20"/>
+      <c r="W4" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="2"/>
+    </row>
+    <row r="5" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -5730,18 +5754,21 @@
       <c r="T5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="U5" s="20" t="s">
+      <c r="U5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="V5" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="W5" s="45" t="s">
+      <c r="X5" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="X5" s="2"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y5" s="2"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.01. - Tuberculosis</v>
@@ -5791,18 +5818,21 @@
       <c r="T6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="U6" s="20" t="s">
+      <c r="U6" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="V6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="V6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="W6" s="45" t="s">
+      <c r="X6" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="X6" s="2"/>
-    </row>
-    <row r="7" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y6" s="2"/>
+    </row>
+    <row r="7" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.02. - HIV/ and other Sexually transmitted diseases (STDs)</v>
@@ -5837,14 +5867,17 @@
       <c r="T7" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="U7" s="20"/>
-      <c r="V7" s="2" t="s">
+      <c r="U7" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="V7" s="20"/>
+      <c r="W7" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="W7" s="45"/>
-      <c r="X7" s="2"/>
-    </row>
-    <row r="8" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="X7" s="45"/>
+      <c r="Y7" s="2"/>
+    </row>
+    <row r="8" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.02.a. - Sexually transmitted diseases (STDs) excluding HIV</v>
@@ -5897,18 +5930,21 @@
       <c r="T8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="U8" s="20" t="s">
+      <c r="U8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="V8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="W8" s="45" t="s">
+      <c r="X8" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="2"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y8" s="2"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -5957,18 +5993,21 @@
       <c r="T9" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="U9" s="20" t="s">
+      <c r="U9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="V9" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="V9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="W9" s="45" t="s">
+      <c r="X9" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="X9" s="2"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6017,18 +6056,21 @@
       <c r="T10" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="U10" s="20" t="s">
+      <c r="U10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="V10" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="V10" s="5" t="s">
+      <c r="W10" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="W10" s="45" t="s">
+      <c r="X10" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6077,18 +6119,21 @@
       <c r="T11" s="5" t="s">
         <v>1401</v>
       </c>
-      <c r="U11" s="20" t="s">
+      <c r="U11" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V11" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="V11" s="5" t="s">
+      <c r="W11" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="W11" s="45" t="s">
+      <c r="X11" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="X11" s="2"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6133,20 +6178,23 @@
       <c r="T12" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="U12" s="20" t="s">
+      <c r="U12" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="V12" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="V12" s="5" t="s">
+      <c r="W12" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="W12" s="45" t="s">
+      <c r="X12" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6195,18 +6243,21 @@
       <c r="T13" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="U13" s="20" t="s">
+      <c r="U13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="V13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="V13" s="5" t="s">
+      <c r="W13" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="W13" s="45" t="s">
+      <c r="X13" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="X13" s="2"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.02.b. - HIV/AIDS</v>
@@ -6257,18 +6308,21 @@
       <c r="T14" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="U14" s="20" t="s">
+      <c r="U14" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="V14" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V14" s="5" t="s">
+      <c r="W14" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="W14" s="45" t="s">
+      <c r="X14" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="X14" s="2"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y14" s="2"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6313,18 +6367,21 @@
       <c r="T15" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="U15" s="20" t="s">
+      <c r="U15" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="V15" s="20" t="s">
         <v>686</v>
       </c>
-      <c r="V15" s="5" t="s">
+      <c r="W15" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="W15" s="45" t="s">
+      <c r="X15" s="45" t="s">
         <v>686</v>
       </c>
-      <c r="X15" s="2"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y15" s="2"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6373,18 +6430,21 @@
       <c r="T16" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="U16" s="20" t="s">
+      <c r="U16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="V16" s="20" t="s">
         <v>687</v>
       </c>
-      <c r="V16" s="5" t="s">
+      <c r="W16" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="W16" s="45" t="s">
+      <c r="X16" s="45" t="s">
         <v>687</v>
       </c>
-      <c r="X16" s="2"/>
-    </row>
-    <row r="17" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y16" s="2"/>
+    </row>
+    <row r="17" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6431,18 +6491,21 @@
       <c r="T17" s="5" t="s">
         <v>1402</v>
       </c>
-      <c r="U17" s="20" t="s">
+      <c r="U17" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="V17" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="V17" s="5" t="s">
+      <c r="W17" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="W17" s="45" t="s">
+      <c r="X17" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="X17" s="2"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6484,17 +6547,20 @@
       <c r="T18" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="U18" s="20" t="s">
+      <c r="U18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="V18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="V18" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="W18" s="45" t="s">
+      <c r="X18" s="45" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6541,18 +6607,21 @@
       <c r="T19" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="U19" s="20" t="s">
+      <c r="U19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="V19" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="V19" s="5" t="s">
+      <c r="W19" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="W19" s="45" t="s">
+      <c r="X19" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="X19" s="2"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y19" s="2"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6599,18 +6668,21 @@
       <c r="T20" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="20" t="s">
+      <c r="U20" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="V20" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="V20" s="5" t="s">
+      <c r="W20" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="W20" s="45" t="s">
+      <c r="X20" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="X20" s="2"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y20" s="2"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6657,18 +6729,21 @@
       <c r="T21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="U21" s="20" t="s">
+      <c r="U21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="V21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="V21" s="5" t="s">
+      <c r="W21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="W21" s="45" t="s">
+      <c r="X21" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="X21" s="2"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y21" s="2"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6715,18 +6790,21 @@
       <c r="T22" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="U22" s="20" t="s">
+      <c r="U22" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="V22" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="V22" s="5" t="s">
+      <c r="W22" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="W22" s="45" t="s">
+      <c r="X22" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="X22" s="2"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y22" s="2"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.04. - Meningitis</v>
@@ -6776,18 +6854,21 @@
       <c r="T23" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="U23" s="20" t="s">
+      <c r="U23" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="V23" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="V23" s="5" t="s">
+      <c r="W23" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="W23" s="45" t="s">
+      <c r="X23" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="X23" s="2"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y23" s="2"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.05. - Encephalitis</v>
@@ -6837,18 +6918,21 @@
       <c r="T24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="U24" s="20" t="s">
+      <c r="U24" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="V24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="V24" s="5" t="s">
+      <c r="W24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="W24" s="45" t="s">
+      <c r="X24" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="X24" s="2"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y24" s="2"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.06. - Hepatitis</v>
@@ -6891,18 +6975,21 @@
       <c r="T25" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="U25" s="20" t="s">
+      <c r="U25" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="V25" s="20" t="s">
         <v>688</v>
       </c>
-      <c r="V25" s="5" t="s">
+      <c r="W25" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="W25" s="45" t="s">
+      <c r="X25" s="45" t="s">
         <v>688</v>
       </c>
-      <c r="X25" s="2"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y25" s="2"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6945,18 +7032,21 @@
       <c r="T26" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="U26" s="20" t="s">
+      <c r="U26" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="V26" s="20" t="s">
         <v>689</v>
       </c>
-      <c r="V26" s="5" t="s">
+      <c r="W26" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="W26" s="45" t="s">
+      <c r="X26" s="45" t="s">
         <v>689</v>
       </c>
-      <c r="X26" s="2"/>
-    </row>
-    <row r="27" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y26" s="2"/>
+    </row>
+    <row r="27" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.06.a. - Acute hepatitis B</v>
@@ -7004,18 +7094,21 @@
       <c r="T27" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="U27" s="20" t="s">
+      <c r="U27" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="V27" s="20" t="s">
         <v>690</v>
       </c>
-      <c r="V27" s="5" t="s">
+      <c r="W27" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="W27" s="45" t="s">
+      <c r="X27" s="45" t="s">
         <v>690</v>
       </c>
-      <c r="X27" s="2"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y27" s="2"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7038,12 +7131,13 @@
       <c r="R28" s="83"/>
       <c r="S28" s="83"/>
       <c r="T28" s="5"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="45"/>
-      <c r="X28" s="2"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U28" s="5"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="2"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.06.b. - Acute hepatitis C</v>
@@ -7091,18 +7185,21 @@
       <c r="T29" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="U29" s="20" t="s">
+      <c r="U29" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="V29" s="20" t="s">
         <v>691</v>
       </c>
-      <c r="V29" s="5" t="s">
+      <c r="W29" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="W29" s="45" t="s">
+      <c r="X29" s="45" t="s">
         <v>691</v>
       </c>
-      <c r="X29" s="2"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y29" s="2"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7145,18 +7242,21 @@
       <c r="T30" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="U30" s="20" t="s">
+      <c r="U30" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="V30" s="20" t="s">
         <v>888</v>
       </c>
-      <c r="V30" s="5" t="s">
+      <c r="W30" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="W30" s="45" t="s">
+      <c r="X30" s="45" t="s">
         <v>888</v>
       </c>
-      <c r="X30" s="2"/>
-    </row>
-    <row r="31" spans="1:24" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="Y30" s="2"/>
+    </row>
+    <row r="31" spans="1:25" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A31" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7196,18 +7296,21 @@
       <c r="T31" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="U31" s="20" t="s">
+      <c r="U31" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="V31" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="V31" s="2" t="s">
+      <c r="W31" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="W31" s="45" t="s">
+      <c r="X31" s="45" t="s">
         <v>693</v>
       </c>
-      <c r="X31" s="2"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y31" s="2"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7254,18 +7357,21 @@
       <c r="T32" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="U32" s="20" t="s">
+      <c r="U32" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="V32" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="V32" s="5" t="s">
+      <c r="W32" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="W32" s="45" t="s">
+      <c r="X32" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="X32" s="2"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32" s="2"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7312,18 +7418,21 @@
       <c r="T33" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="U33" s="20" t="s">
+      <c r="U33" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="V33" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="V33" s="5" t="s">
+      <c r="W33" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="W33" s="45" t="s">
+      <c r="X33" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="X33" s="2"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33" s="2"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7370,18 +7479,21 @@
       <c r="T34" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="U34" s="20" t="s">
+      <c r="U34" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="V34" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="V34" s="5" t="s">
+      <c r="W34" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="W34" s="45" t="s">
+      <c r="X34" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="X34" s="2"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y34" s="2"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7428,18 +7540,21 @@
       <c r="T35" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="20" t="s">
+      <c r="U35" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="V35" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="V35" s="5" t="s">
+      <c r="W35" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="W35" s="45" t="s">
+      <c r="X35" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="X35" s="2"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y35" s="2"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7486,18 +7601,21 @@
       <c r="T36" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="U36" s="20" t="s">
+      <c r="U36" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="V36" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="V36" s="5" t="s">
+      <c r="W36" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="W36" s="45" t="s">
+      <c r="X36" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="X36" s="2"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y36" s="2"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7540,18 +7658,21 @@
       <c r="T37" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="U37" s="20" t="s">
+      <c r="U37" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="V37" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="V37" s="5" t="s">
+      <c r="W37" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="W37" s="45" t="s">
+      <c r="X37" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="X37" s="2"/>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y37" s="2"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7594,18 +7715,21 @@
       <c r="T38" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="U38" s="20" t="s">
+      <c r="U38" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="V38" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="V38" s="5" t="s">
+      <c r="W38" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="W38" s="45" t="s">
+      <c r="X38" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="X38" s="2"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y38" s="2"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7652,18 +7776,21 @@
       <c r="T39" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="U39" s="20" t="s">
+      <c r="U39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="V39" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="V39" s="5" t="s">
+      <c r="W39" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="W39" s="45" t="s">
+      <c r="X39" s="45" t="s">
         <v>694</v>
       </c>
-      <c r="X39" s="2"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y39" s="2"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7710,18 +7837,21 @@
       <c r="T40" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="U40" s="20" t="s">
+      <c r="U40" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="V40" s="20" t="s">
         <v>695</v>
       </c>
-      <c r="V40" s="5" t="s">
+      <c r="W40" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="W40" s="45" t="s">
+      <c r="X40" s="45" t="s">
         <v>695</v>
       </c>
-      <c r="X40" s="2"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y40" s="2"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7764,18 +7894,21 @@
       <c r="T41" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="U41" s="20" t="s">
+      <c r="U41" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="V41" s="20" t="s">
         <v>889</v>
       </c>
-      <c r="V41" s="5" t="s">
+      <c r="W41" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="W41" s="45" t="s">
+      <c r="X41" s="45" t="s">
         <v>889</v>
       </c>
-      <c r="X41" s="2"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y41" s="2"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7822,18 +7955,21 @@
       <c r="T42" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="U42" s="20" t="s">
+      <c r="U42" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="V42" s="20" t="s">
         <v>890</v>
       </c>
-      <c r="V42" s="5" t="s">
+      <c r="W42" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="W42" s="45" t="s">
+      <c r="X42" s="45" t="s">
         <v>890</v>
       </c>
-      <c r="X42" s="2"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y42" s="2"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7876,18 +8012,21 @@
       <c r="T43" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="U43" s="20" t="s">
+      <c r="U43" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="V43" s="20" t="s">
         <v>891</v>
       </c>
-      <c r="V43" s="5" t="s">
+      <c r="W43" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="W43" s="45" t="s">
+      <c r="X43" s="45" t="s">
         <v>891</v>
       </c>
-      <c r="X43" s="2"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y43" s="2"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7934,18 +8073,21 @@
       <c r="T44" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="U44" s="20" t="s">
+      <c r="U44" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="V44" s="20" t="s">
         <v>892</v>
       </c>
-      <c r="V44" s="5" t="s">
+      <c r="W44" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="W44" s="45" t="s">
+      <c r="X44" s="45" t="s">
         <v>892</v>
       </c>
-      <c r="X44" s="2"/>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y44" s="2"/>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -7992,18 +8134,21 @@
       <c r="T45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="U45" s="20" t="s">
+      <c r="U45" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="V45" s="20" t="s">
         <v>894</v>
       </c>
-      <c r="V45" s="5" t="s">
+      <c r="W45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="W45" s="45" t="s">
+      <c r="X45" s="45" t="s">
         <v>894</v>
       </c>
-      <c r="X45" s="2"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y45" s="2"/>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8047,18 +8192,21 @@
       <c r="T46" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="U46" s="20" t="s">
+      <c r="U46" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="V46" s="20" t="s">
         <v>879</v>
       </c>
-      <c r="V46" s="2" t="s">
+      <c r="W46" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="W46" s="45" t="s">
+      <c r="X46" s="45" t="s">
         <v>879</v>
       </c>
-      <c r="X46" s="2"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y46" s="2"/>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8105,18 +8253,21 @@
       <c r="T47" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="U47" s="20" t="s">
+      <c r="U47" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="V47" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="V47" s="5" t="s">
+      <c r="W47" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="W47" s="45" t="s">
+      <c r="X47" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="X47" s="2"/>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y47" s="2"/>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8159,18 +8310,21 @@
       <c r="T48" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="U48" s="20" t="s">
+      <c r="U48" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="V48" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="V48" s="5" t="s">
+      <c r="W48" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="W48" s="45" t="s">
+      <c r="X48" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="X48" s="2"/>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y48" s="2"/>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8213,18 +8367,21 @@
       <c r="T49" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="U49" s="20" t="s">
+      <c r="U49" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="V49" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="V49" s="5" t="s">
+      <c r="W49" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="W49" s="45" t="s">
+      <c r="X49" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="X49" s="2"/>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y49" s="2"/>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8267,18 +8424,21 @@
       <c r="T50" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="U50" s="20" t="s">
+      <c r="U50" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="V50" s="20" t="s">
         <v>895</v>
       </c>
-      <c r="V50" s="5" t="s">
+      <c r="W50" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="W50" s="45" t="s">
+      <c r="X50" s="45" t="s">
         <v>895</v>
       </c>
-      <c r="X50" s="2"/>
-    </row>
-    <row r="51" spans="1:24" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="Y50" s="2"/>
+    </row>
+    <row r="51" spans="1:25" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8331,20 +8491,23 @@
       <c r="T51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="U51" s="20" t="s">
+      <c r="U51" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="V51" s="20" t="s">
         <v>880</v>
       </c>
-      <c r="V51" s="5" t="s">
+      <c r="W51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="W51" s="45" t="s">
+      <c r="X51" s="45" t="s">
         <v>880</v>
       </c>
-      <c r="X51" s="5" t="s">
+      <c r="Y51" s="5" t="s">
         <v>1308</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.07. - Respiratory infections</v>
@@ -8393,18 +8556,21 @@
       <c r="T52" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="U52" s="20" t="s">
+      <c r="U52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="V52" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="V52" s="2" t="s">
+      <c r="W52" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="W52" s="45" t="s">
+      <c r="X52" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="X52" s="2"/>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y52" s="2"/>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.07.a. - Lower respiratory infections</v>
@@ -8462,18 +8628,21 @@
       <c r="T53" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="U53" s="20" t="s">
+      <c r="U53" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="V53" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="V53" s="5" t="s">
+      <c r="W53" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="W53" s="45" t="s">
+      <c r="X53" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="X53" s="2"/>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y53" s="2"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="44" t="str">
         <f t="shared" si="0"/>
         <v>....A.07.b. - Upper respiratory infections</v>
@@ -8531,18 +8700,21 @@
       <c r="T54" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="U54" s="20" t="s">
+      <c r="U54" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="V54" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="V54" s="5" t="s">
+      <c r="W54" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="W54" s="45" t="s">
+      <c r="X54" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="X54" s="2"/>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y54" s="2"/>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8595,18 +8767,21 @@
       <c r="T55" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="U55" s="20" t="s">
+      <c r="U55" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="V55" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="V55" s="5" t="s">
+      <c r="W55" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="W55" s="45" t="s">
+      <c r="X55" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="X55" s="2"/>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y55" s="2"/>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.08. - Maternal conditions</v>
@@ -8657,18 +8832,21 @@
       <c r="T56" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="U56" s="20" t="s">
+      <c r="U56" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V56" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="V56" s="2" t="s">
+      <c r="W56" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="W56" s="45" t="s">
+      <c r="X56" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="X56" s="2"/>
-    </row>
-    <row r="57" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y56" s="2"/>
+    </row>
+    <row r="57" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8721,20 +8899,23 @@
       <c r="T57" s="5" t="s">
         <v>1403</v>
       </c>
-      <c r="U57" s="20" t="s">
+      <c r="U57" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V57" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="V57" s="5" t="s">
+      <c r="W57" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="W57" s="45" t="s">
+      <c r="X57" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="X57" s="5" t="s">
+      <c r="Y57" s="5" t="s">
         <v>1356</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8787,18 +8968,21 @@
       <c r="T58" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="U58" s="20" t="s">
+      <c r="U58" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="V58" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="V58" s="5" t="s">
+      <c r="W58" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="W58" s="45" t="s">
+      <c r="X58" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="X58" s="2"/>
-    </row>
-    <row r="59" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y58" s="2"/>
+    </row>
+    <row r="59" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8851,20 +9035,23 @@
       <c r="T59" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="U59" s="20" t="s">
+      <c r="U59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="V59" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="V59" s="5" t="s">
+      <c r="W59" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="W59" s="45" t="s">
+      <c r="X59" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="X59" s="5" t="s">
+      <c r="Y59" s="5" t="s">
         <v>1358</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8917,18 +9104,21 @@
       <c r="T60" s="5" t="s">
         <v>1412</v>
       </c>
-      <c r="U60" s="20" t="s">
+      <c r="U60" s="5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="V60" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="V60" s="5" t="s">
+      <c r="W60" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="W60" s="45" t="s">
+      <c r="X60" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="X60" s="2"/>
-    </row>
-    <row r="61" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y60" s="2"/>
+    </row>
+    <row r="61" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8981,18 +9171,21 @@
       <c r="T61" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="U61" s="20" t="s">
+      <c r="U61" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="V61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="V61" s="5" t="s">
+      <c r="W61" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="W61" s="45" t="s">
+      <c r="X61" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="X61" s="2"/>
-    </row>
-    <row r="62" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y61" s="2"/>
+    </row>
+    <row r="62" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9045,18 +9238,21 @@
       <c r="T62" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="U62" s="20" t="s">
+      <c r="U62" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="V62" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="V62" s="5" t="s">
+      <c r="W62" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="W62" s="45" t="s">
+      <c r="X62" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="X62" s="2"/>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y62" s="2"/>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="44" t="str">
         <f t="shared" si="0"/>
         <v>...A.09. - Neonatal conditions</v>
@@ -9107,18 +9303,21 @@
       <c r="T63" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="U63" s="20" t="s">
+      <c r="U63" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="V63" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="V63" s="2" t="s">
+      <c r="W63" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="W63" s="45" t="s">
+      <c r="X63" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="X63" s="2"/>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y63" s="2"/>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9165,18 +9364,21 @@
       <c r="T64" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="U64" s="20" t="s">
+      <c r="U64" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="V64" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="V64" s="5" t="s">
+      <c r="W64" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="W64" s="45" t="s">
+      <c r="X64" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="X64" s="2"/>
-    </row>
-    <row r="65" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y64" s="2"/>
+    </row>
+    <row r="65" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A65" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9223,18 +9425,21 @@
       <c r="T65" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="U65" s="20" t="s">
+      <c r="U65" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="V65" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="V65" s="5" t="s">
+      <c r="W65" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="W65" s="45" t="s">
+      <c r="X65" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="X65" s="2"/>
-    </row>
-    <row r="66" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y65" s="2"/>
+    </row>
+    <row r="66" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9281,18 +9486,21 @@
       <c r="T66" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="U66" s="20" t="s">
+      <c r="U66" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="V66" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="V66" s="5" t="s">
+      <c r="W66" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="W66" s="45" t="s">
+      <c r="X66" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="X66" s="2"/>
-    </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y66" s="2"/>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9345,18 +9553,21 @@
       <c r="T67" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="U67" s="20" t="s">
+      <c r="U67" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="V67" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="V67" s="5" t="s">
+      <c r="W67" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="W67" s="45" t="s">
+      <c r="X67" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="X67" s="2"/>
-    </row>
-    <row r="68" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y67" s="2"/>
+    </row>
+    <row r="68" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A68" s="44" t="str">
         <f t="shared" ref="A68:A131" si="5">IF(H68&lt;&gt;"",IF(F68&lt;&gt;"",CONCATENATE("....",D68,".",E68,".",F68,". - ",T68),IF(E68&lt;&gt;"",CONCATENATE("...",D68,".",E68,". - ",T68),CONCATENATE("..",D68,". - ",T68))),"")</f>
         <v/>
@@ -9400,18 +9611,21 @@
       <c r="T68" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="U68" s="20" t="s">
+      <c r="U68" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="V68" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="V68" s="2" t="s">
+      <c r="W68" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="W68" s="45" t="s">
+      <c r="X68" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="X68" s="2"/>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y68" s="2"/>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9458,18 +9672,21 @@
       <c r="T69" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="U69" s="20" t="s">
+      <c r="U69" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="V69" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="V69" s="5" t="s">
+      <c r="W69" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="W69" s="45" t="s">
+      <c r="X69" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="X69" s="2"/>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y69" s="2"/>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9516,18 +9733,21 @@
       <c r="T70" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="U70" s="20" t="s">
+      <c r="U70" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="V70" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="V70" s="5" t="s">
+      <c r="W70" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="W70" s="45" t="s">
+      <c r="X70" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="X70" s="2"/>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y70" s="2"/>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9570,18 +9790,21 @@
       <c r="T71" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="U71" s="20" t="s">
+      <c r="U71" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="V71" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="V71" s="5" t="s">
+      <c r="W71" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="W71" s="45" t="s">
+      <c r="X71" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="X71" s="2"/>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y71" s="2"/>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9628,18 +9851,21 @@
       <c r="T72" s="5" t="s">
         <v>1413</v>
       </c>
-      <c r="U72" s="20" t="s">
+      <c r="U72" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="V72" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="V72" s="5" t="s">
+      <c r="W72" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="W72" s="45" t="s">
+      <c r="X72" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="X72" s="2"/>
-    </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y72" s="2"/>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9686,18 +9912,21 @@
       <c r="T73" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="U73" s="20" t="s">
+      <c r="U73" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="V73" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="V73" s="5" t="s">
+      <c r="W73" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="W73" s="45" t="s">
+      <c r="X73" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="X73" s="2"/>
-    </row>
-    <row r="74" spans="1:24" ht="84" x14ac:dyDescent="0.25">
+      <c r="Y73" s="2"/>
+    </row>
+    <row r="74" spans="1:25" ht="84" x14ac:dyDescent="0.25">
       <c r="A74" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9739,18 +9968,21 @@
       <c r="T74" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="U74" s="20" t="s">
+      <c r="U74" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="V74" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="V74" s="2" t="s">
+      <c r="W74" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="W74" s="45" t="s">
+      <c r="X74" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="X74" s="2"/>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y74" s="2"/>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="44" t="str">
         <f t="shared" si="5"/>
         <v>..D. - Other Chronic</v>
@@ -9783,12 +10015,15 @@
       <c r="T75" s="20" t="s">
         <v>1155</v>
       </c>
-      <c r="V75" s="45" t="s">
+      <c r="U75" s="20" t="s">
         <v>1155</v>
       </c>
-      <c r="X75" s="2"/>
-    </row>
-    <row r="76" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="W75" s="45" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Y75" s="2"/>
+    </row>
+    <row r="76" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="44" t="str">
         <f t="shared" si="5"/>
         <v>..B. - Cancer/Malignant neoplasms</v>
@@ -9835,18 +10070,21 @@
       <c r="T76" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="U76" s="20" t="s">
+      <c r="U76" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="V76" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="V76" s="2" t="s">
+      <c r="W76" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="W76" s="45" t="s">
+      <c r="X76" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="X76" s="2"/>
-    </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y76" s="2"/>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.01. - Mouth and oropharynx cancers</v>
@@ -9894,18 +10132,21 @@
       <c r="T77" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="U77" s="50" t="s">
+      <c r="U77" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="V77" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="V77" s="5" t="s">
+      <c r="W77" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="W77" s="51" t="s">
+      <c r="X77" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="X77" s="2"/>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y77" s="2"/>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -9958,18 +10199,21 @@
       <c r="T78" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="U78" s="50" t="s">
+      <c r="U78" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="V78" s="50" t="s">
         <v>698</v>
       </c>
-      <c r="V78" s="5" t="s">
+      <c r="W78" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="W78" s="51" t="s">
+      <c r="X78" s="51" t="s">
         <v>698</v>
       </c>
-      <c r="X78" s="2"/>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y78" s="2"/>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10022,18 +10266,21 @@
       <c r="T79" s="5" t="s">
         <v>1414</v>
       </c>
-      <c r="U79" s="50" t="s">
+      <c r="U79" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="V79" s="50" t="s">
         <v>896</v>
       </c>
-      <c r="V79" s="5" t="s">
+      <c r="W79" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="W79" s="51" t="s">
+      <c r="X79" s="51" t="s">
         <v>896</v>
       </c>
-      <c r="X79" s="2"/>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y79" s="2"/>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10082,18 +10329,21 @@
       <c r="T80" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="U80" s="50" t="s">
+      <c r="U80" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="V80" s="50" t="s">
         <v>700</v>
       </c>
-      <c r="V80" s="5" t="s">
+      <c r="W80" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="W80" s="51" t="s">
+      <c r="X80" s="51" t="s">
         <v>700</v>
       </c>
-      <c r="X80" s="2"/>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y80" s="2"/>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.02. - Esophagus cancer</v>
@@ -10149,18 +10399,21 @@
       <c r="T81" s="5" t="s">
         <v>1404</v>
       </c>
-      <c r="U81" s="50" t="s">
+      <c r="U81" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="V81" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="V81" s="5" t="s">
+      <c r="W81" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="W81" s="51" t="s">
+      <c r="X81" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="X81" s="2"/>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y81" s="2"/>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.03. - Stomach cancer</v>
@@ -10216,20 +10469,23 @@
       <c r="T82" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="U82" s="50" t="s">
+      <c r="U82" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="V82" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="V82" s="5" t="s">
+      <c r="W82" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="W82" s="51" t="s">
+      <c r="X82" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="X82" s="2" t="s">
+      <c r="Y82" s="2" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A83" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.04. - Colon and rectum cancers</v>
@@ -10285,18 +10541,21 @@
       <c r="T83" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="U83" s="50" t="s">
+      <c r="U83" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="V83" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="V83" s="5" t="s">
+      <c r="W83" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="W83" s="51" t="s">
+      <c r="X83" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="X83" s="2"/>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y83" s="2"/>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.05. - Liver cancer</v>
@@ -10352,18 +10611,21 @@
       <c r="T84" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="U84" s="50" t="s">
+      <c r="U84" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="V84" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="V84" s="5" t="s">
+      <c r="W84" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="W84" s="51" t="s">
+      <c r="X84" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="X84" s="2"/>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y84" s="2"/>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.06. - Pancreas cancer</v>
@@ -10419,18 +10681,21 @@
       <c r="T85" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="U85" s="50" t="s">
+      <c r="U85" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="V85" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="V85" s="5" t="s">
+      <c r="W85" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="W85" s="51" t="s">
+      <c r="X85" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="X85" s="2"/>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y85" s="2"/>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.07. - Trachea, bronchus and lung cancers</v>
@@ -10486,18 +10751,21 @@
       <c r="T86" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="U86" s="50" t="s">
+      <c r="U86" s="5" t="s">
+        <v>1421</v>
+      </c>
+      <c r="V86" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="V86" s="5" t="s">
+      <c r="W86" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="W86" s="51" t="s">
+      <c r="X86" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="X86" s="2"/>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y86" s="2"/>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.08. - Melanoma and other skin cancers</v>
@@ -10545,18 +10813,21 @@
       <c r="T87" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="U87" s="50" t="s">
+      <c r="U87" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="V87" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="V87" s="5" t="s">
+      <c r="W87" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="W87" s="51" t="s">
+      <c r="X87" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="X87" s="2"/>
-    </row>
-    <row r="88" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y87" s="2"/>
+    </row>
+    <row r="88" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A88" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10609,18 +10880,21 @@
       <c r="T88" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="U88" s="50" t="s">
+      <c r="U88" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="V88" s="50" t="s">
         <v>701</v>
       </c>
-      <c r="V88" s="5" t="s">
+      <c r="W88" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="W88" s="51" t="s">
+      <c r="X88" s="51" t="s">
         <v>701</v>
       </c>
-      <c r="X88" s="2"/>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y88" s="2"/>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10673,18 +10947,21 @@
       <c r="T89" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="U89" s="50" t="s">
+      <c r="U89" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="V89" s="50" t="s">
         <v>702</v>
       </c>
-      <c r="V89" s="5" t="s">
+      <c r="W89" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="W89" s="51" t="s">
+      <c r="X89" s="51" t="s">
         <v>702</v>
       </c>
-      <c r="X89" s="2"/>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y89" s="2"/>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.09. - Breast cancer</v>
@@ -10740,18 +11017,21 @@
       <c r="T90" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="U90" s="20" t="s">
+      <c r="U90" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="V90" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="V90" s="5" t="s">
+      <c r="W90" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="W90" s="45" t="s">
+      <c r="X90" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="X90" s="2"/>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y90" s="2"/>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.10. - Uterine cancer</v>
@@ -10787,14 +11067,17 @@
       <c r="T91" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="U91" s="20"/>
-      <c r="V91" s="5" t="s">
+      <c r="U91" s="5" t="s">
         <v>1266</v>
       </c>
-      <c r="W91" s="45"/>
-      <c r="X91" s="2"/>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="V91" s="20"/>
+      <c r="W91" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="X91" s="45"/>
+      <c r="Y91" s="2"/>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10847,18 +11130,21 @@
       <c r="T92" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="U92" s="20" t="s">
+      <c r="U92" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="V92" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="V92" s="5" t="s">
+      <c r="W92" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="W92" s="45" t="s">
+      <c r="X92" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="X92" s="2"/>
-    </row>
-    <row r="93" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y92" s="2"/>
+    </row>
+    <row r="93" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A93" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -10911,18 +11197,21 @@
       <c r="T93" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="U93" s="20" t="s">
+      <c r="U93" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="V93" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="V93" s="5" t="s">
+      <c r="W93" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="W93" s="45" t="s">
+      <c r="X93" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="X93" s="2"/>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y93" s="2"/>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.11. - Ovary cancer</v>
@@ -10978,18 +11267,21 @@
       <c r="T94" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="U94" s="20" t="s">
+      <c r="U94" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="V94" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="V94" s="5" t="s">
+      <c r="W94" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="W94" s="45" t="s">
+      <c r="X94" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="X94" s="2"/>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y94" s="2"/>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.12. - Prostate cancer</v>
@@ -11045,18 +11337,21 @@
       <c r="T95" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="U95" s="20" t="s">
+      <c r="U95" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="V95" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="V95" s="5" t="s">
+      <c r="W95" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="W95" s="45" t="s">
+      <c r="X95" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="X95" s="2"/>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y95" s="2"/>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11109,18 +11404,21 @@
       <c r="T96" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="U96" s="20" t="s">
+      <c r="U96" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="V96" s="20" t="s">
         <v>703</v>
       </c>
-      <c r="V96" s="5" t="s">
+      <c r="W96" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="W96" s="45" t="s">
+      <c r="X96" s="45" t="s">
         <v>703</v>
       </c>
-      <c r="X96" s="2"/>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y96" s="2"/>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.13. - Kidney, renal pelvis and ureter cancer</v>
@@ -11176,18 +11474,21 @@
       <c r="T97" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="U97" s="20" t="s">
+      <c r="U97" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="V97" s="20" t="s">
         <v>704</v>
       </c>
-      <c r="V97" s="5" t="s">
+      <c r="W97" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="W97" s="45" t="s">
+      <c r="X97" s="45" t="s">
         <v>704</v>
       </c>
-      <c r="X97" s="2"/>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y97" s="2"/>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.14. - Bladder cancer</v>
@@ -11243,18 +11544,21 @@
       <c r="T98" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="U98" s="20" t="s">
+      <c r="U98" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="V98" s="20" t="s">
         <v>705</v>
       </c>
-      <c r="V98" s="5" t="s">
+      <c r="W98" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="W98" s="45" t="s">
+      <c r="X98" s="45" t="s">
         <v>705</v>
       </c>
-      <c r="X98" s="2"/>
-    </row>
-    <row r="99" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y98" s="2"/>
+    </row>
+    <row r="99" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A99" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.15. - Brain and nervous system cancers</v>
@@ -11310,18 +11614,21 @@
       <c r="T99" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="U99" s="20" t="s">
+      <c r="U99" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="V99" s="20" t="s">
         <v>706</v>
       </c>
-      <c r="V99" s="5" t="s">
+      <c r="W99" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="W99" s="45" t="s">
+      <c r="X99" s="45" t="s">
         <v>706</v>
       </c>
-      <c r="X99" s="2"/>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y99" s="2"/>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11374,18 +11681,21 @@
       <c r="T100" s="5" t="s">
         <v>1415</v>
       </c>
-      <c r="U100" s="20" t="s">
+      <c r="U100" s="5" t="s">
+        <v>1415</v>
+      </c>
+      <c r="V100" s="20" t="s">
         <v>707</v>
       </c>
-      <c r="V100" s="5" t="s">
+      <c r="W100" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="W100" s="45" t="s">
+      <c r="X100" s="45" t="s">
         <v>707</v>
       </c>
-      <c r="X100" s="2"/>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y100" s="2"/>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11438,18 +11748,21 @@
       <c r="T101" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="U101" s="20" t="s">
+      <c r="U101" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="V101" s="20" t="s">
         <v>708</v>
       </c>
-      <c r="V101" s="5" t="s">
+      <c r="W101" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="W101" s="45" t="s">
+      <c r="X101" s="45" t="s">
         <v>708</v>
       </c>
-      <c r="X101" s="2"/>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y101" s="2"/>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11502,18 +11815,21 @@
       <c r="T102" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="U102" s="20" t="s">
+      <c r="U102" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="V102" s="20" t="s">
         <v>709</v>
       </c>
-      <c r="V102" s="5" t="s">
+      <c r="W102" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="W102" s="45" t="s">
+      <c r="X102" s="45" t="s">
         <v>709</v>
       </c>
-      <c r="X102" s="2"/>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y102" s="2"/>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -11562,18 +11878,21 @@
       <c r="T103" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="U103" s="20" t="s">
+      <c r="U103" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="V103" s="20" t="s">
         <v>710</v>
       </c>
-      <c r="V103" s="5" t="s">
+      <c r="W103" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="W103" s="45" t="s">
+      <c r="X103" s="45" t="s">
         <v>710</v>
       </c>
-      <c r="X103" s="2"/>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y103" s="2"/>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.16. - Lymphomas and multiple myeloma</v>
@@ -11622,18 +11941,21 @@
       <c r="T104" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="U104" s="20" t="s">
+      <c r="U104" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="V104" s="20" t="s">
         <v>904</v>
       </c>
-      <c r="V104" s="5" t="s">
+      <c r="W104" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="W104" s="45" t="s">
+      <c r="X104" s="45" t="s">
         <v>904</v>
       </c>
-      <c r="X104" s="2"/>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y104" s="2"/>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....B.16.a. - Hodgkin lymphoma</v>
@@ -11688,17 +12010,20 @@
         <v>901</v>
       </c>
       <c r="U105" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="V105" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="V105" s="5" t="s">
+      <c r="W105" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="W105" s="5" t="s">
+      <c r="X105" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="X105" s="2"/>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y105" s="2"/>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....B.16.b. - Non-Hodgkin lymphoma</v>
@@ -11753,17 +12078,20 @@
         <v>902</v>
       </c>
       <c r="U106" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="V106" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="V106" s="5" t="s">
+      <c r="W106" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="W106" s="5" t="s">
+      <c r="X106" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="X106" s="2"/>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y106" s="2"/>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....B.16.c. - Multiple myeloma</v>
@@ -11818,17 +12146,20 @@
         <v>903</v>
       </c>
       <c r="U107" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="V107" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="V107" s="5" t="s">
+      <c r="W107" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="W107" s="5" t="s">
+      <c r="X107" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="X107" s="2"/>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y107" s="2"/>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.17. - Leukemia</v>
@@ -11880,18 +12211,21 @@
       <c r="T108" s="5" t="s">
         <v>1405</v>
       </c>
-      <c r="U108" s="20" t="s">
+      <c r="U108" s="5" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V108" s="20" t="s">
         <v>715</v>
       </c>
-      <c r="V108" s="5" t="s">
+      <c r="W108" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="W108" s="45" t="s">
+      <c r="X108" s="45" t="s">
         <v>715</v>
       </c>
-      <c r="X108" s="2"/>
-    </row>
-    <row r="109" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y108" s="2"/>
+    </row>
+    <row r="109" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A109" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...B.99. - Other malignant neoplasms</v>
@@ -11943,18 +12277,21 @@
       <c r="T109" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="U109" s="20" t="s">
+      <c r="U109" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="V109" s="20" t="s">
         <v>905</v>
       </c>
-      <c r="V109" s="5" t="s">
+      <c r="W109" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="W109" s="45" t="s">
+      <c r="X109" s="45" t="s">
         <v>905</v>
       </c>
-      <c r="X109" s="2"/>
-    </row>
-    <row r="110" spans="1:24" ht="114.75" x14ac:dyDescent="0.25">
+      <c r="Y109" s="2"/>
+    </row>
+    <row r="110" spans="1:25" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A110" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12001,18 +12338,21 @@
       <c r="T110" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="U110" s="20" t="s">
+      <c r="U110" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="V110" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="V110" s="5" t="s">
+      <c r="W110" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="W110" s="45" t="s">
+      <c r="X110" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="X110" s="2"/>
-    </row>
-    <row r="111" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="Y110" s="2"/>
+    </row>
+    <row r="111" spans="1:25" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A111" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...D.01. - Diabetes mellitus</v>
@@ -12072,20 +12412,23 @@
       <c r="T111" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="U111" s="20" t="s">
+      <c r="U111" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="V111" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="V111" s="5" t="s">
+      <c r="W111" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="W111" s="45" t="s">
+      <c r="X111" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="X111" s="2" t="s">
+      <c r="Y111" s="2" t="s">
         <v>1334</v>
       </c>
     </row>
-    <row r="112" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A112" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...D.02. - Endocrine, blood, immune disorders</v>
@@ -12136,18 +12479,21 @@
       <c r="T112" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="U112" s="20" t="s">
+      <c r="U112" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="V112" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="V112" s="5" t="s">
+      <c r="W112" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="W112" s="45" t="s">
+      <c r="X112" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="X112" s="2"/>
-    </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y112" s="2"/>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12197,17 +12543,20 @@
         <v>240</v>
       </c>
       <c r="U113" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="V113" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="V113" s="5" t="s">
+      <c r="W113" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="W113" s="5" t="s">
+      <c r="X113" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="X113" s="2"/>
-    </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y113" s="2"/>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12257,17 +12606,20 @@
         <v>241</v>
       </c>
       <c r="U114" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="V114" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="V114" s="5" t="s">
+      <c r="W114" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="W114" s="5" t="s">
+      <c r="X114" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="X114" s="2"/>
-    </row>
-    <row r="115" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y114" s="2"/>
+    </row>
+    <row r="115" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A115" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12317,17 +12669,20 @@
         <v>1416</v>
       </c>
       <c r="U115" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="V115" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="V115" s="5" t="s">
+      <c r="W115" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="W115" s="5" t="s">
+      <c r="X115" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="X115" s="2"/>
-    </row>
-    <row r="116" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y115" s="2"/>
+    </row>
+    <row r="116" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A116" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12377,17 +12732,20 @@
         <v>243</v>
       </c>
       <c r="U116" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="V116" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="V116" s="5" t="s">
+      <c r="W116" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="W116" s="5" t="s">
+      <c r="X116" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="X116" s="2"/>
-    </row>
-    <row r="117" spans="1:24" ht="18" x14ac:dyDescent="0.25">
+      <c r="Y116" s="2"/>
+    </row>
+    <row r="117" spans="1:25" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12435,18 +12793,21 @@
       <c r="T117" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="U117" s="20" t="s">
+      <c r="U117" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="V117" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="V117" s="2" t="s">
+      <c r="W117" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="W117" s="45" t="s">
+      <c r="X117" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="X117" s="2"/>
-    </row>
-    <row r="118" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y117" s="2"/>
+    </row>
+    <row r="118" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A118" s="44" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">...D.03. - Mental Health disorders </v>
@@ -12483,14 +12844,17 @@
       <c r="T118" s="2" t="s">
         <v>1347</v>
       </c>
-      <c r="U118" s="20"/>
-      <c r="V118" s="2" t="s">
+      <c r="U118" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="V118" s="20"/>
+      <c r="W118" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="W118" s="45"/>
-      <c r="X118" s="2"/>
-    </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X118" s="45"/>
+      <c r="Y118" s="2"/>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="44" t="str">
         <f t="shared" si="5"/>
         <v>...D.04. - Substance use disorders</v>
@@ -12525,14 +12889,17 @@
       <c r="T119" s="2" t="s">
         <v>1386</v>
       </c>
-      <c r="U119" s="20"/>
-      <c r="V119" s="2" t="s">
+      <c r="U119" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V119" s="20"/>
+      <c r="W119" s="2" t="s">
         <v>1156</v>
       </c>
-      <c r="W119" s="45"/>
-      <c r="X119" s="2"/>
-    </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X119" s="45"/>
+      <c r="Y119" s="2"/>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12558,12 +12925,13 @@
       <c r="R120" s="83"/>
       <c r="S120" s="83"/>
       <c r="T120" s="2"/>
-      <c r="U120" s="20"/>
-      <c r="V120" s="2"/>
-      <c r="W120" s="45"/>
-      <c r="X120" s="2"/>
-    </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U120" s="2"/>
+      <c r="V120" s="20"/>
+      <c r="W120" s="2"/>
+      <c r="X120" s="45"/>
+      <c r="Y120" s="2"/>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12601,18 +12969,21 @@
       <c r="T121" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="U121" s="20" t="s">
+      <c r="U121" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="V121" s="2" t="s">
+      <c r="V121" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="W121" s="45" t="s">
+      <c r="W121" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="X121" s="2"/>
-    </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X121" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y121" s="2"/>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12661,18 +13032,21 @@
       <c r="T122" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="U122" s="20" t="s">
+      <c r="U122" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="V122" s="2" t="s">
+      <c r="V122" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="W122" s="45" t="s">
+      <c r="W122" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="X122" s="2"/>
-    </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="X122" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y122" s="2"/>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12721,18 +13095,21 @@
       <c r="T123" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="U123" s="20" t="s">
+      <c r="U123" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="V123" s="20" t="s">
         <v>907</v>
       </c>
-      <c r="V123" s="2" t="s">
+      <c r="W123" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="W123" s="45" t="s">
+      <c r="X123" s="45" t="s">
         <v>907</v>
       </c>
-      <c r="X123" s="2"/>
-    </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y123" s="2"/>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12781,18 +13158,21 @@
       <c r="T124" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="U124" s="50" t="s">
+      <c r="U124" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="V124" s="50" t="s">
         <v>725</v>
       </c>
-      <c r="V124" s="5" t="s">
+      <c r="W124" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="W124" s="51" t="s">
+      <c r="X124" s="51" t="s">
         <v>725</v>
       </c>
-      <c r="X124" s="2"/>
-    </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y124" s="2"/>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12845,18 +13225,21 @@
       <c r="T125" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="U125" s="50" t="s">
+      <c r="U125" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="V125" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="V125" s="5" t="s">
+      <c r="W125" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="W125" s="51" t="s">
+      <c r="X125" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="X125" s="2"/>
-    </row>
-    <row r="126" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y125" s="2"/>
+    </row>
+    <row r="126" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A126" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.a. - Alcohol use disorders</v>
@@ -12914,18 +13297,21 @@
       <c r="T126" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="U126" s="50" t="s">
+      <c r="U126" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="V126" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="V126" s="5" t="s">
+      <c r="W126" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="W126" s="51" t="s">
+      <c r="X126" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="X126" s="2"/>
-    </row>
-    <row r="127" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y126" s="2"/>
+    </row>
+    <row r="127" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A127" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -12967,18 +13353,21 @@
       <c r="T127" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="U127" s="50" t="s">
+      <c r="U127" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="V127" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="V127" s="5" t="s">
+      <c r="W127" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="W127" s="51" t="s">
+      <c r="X127" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="X127" s="2"/>
-    </row>
-    <row r="128" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y127" s="2"/>
+    </row>
+    <row r="128" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A128" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.b. - Opioid use disorders</v>
@@ -13035,17 +13424,20 @@
         <v>909</v>
       </c>
       <c r="U128" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="V128" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="V128" s="5" t="s">
+      <c r="W128" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="W128" s="5" t="s">
+      <c r="X128" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="X128" s="2"/>
-    </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y128" s="2"/>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.c. - Cocaine use disorders</v>
@@ -13100,17 +13492,20 @@
         <v>910</v>
       </c>
       <c r="U129" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="V129" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="V129" s="5" t="s">
+      <c r="W129" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="W129" s="5" t="s">
+      <c r="X129" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="X129" s="2"/>
-    </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y129" s="2"/>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="44" t="str">
         <f t="shared" si="5"/>
         <v>....D.04.d. - Amphetamine use disorders</v>
@@ -13165,17 +13560,20 @@
         <v>911</v>
       </c>
       <c r="U130" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="V130" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="V130" s="5" t="s">
+      <c r="W130" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="W130" s="5" t="s">
+      <c r="X130" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="X130" s="2"/>
-    </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y130" s="2"/>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="44" t="str">
         <f t="shared" si="5"/>
         <v/>
@@ -13220,17 +13618,20 @@
         <v>912</v>
       </c>
       <c r="U131" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="V131" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="V131" s="5" t="s">
+      <c r="W131" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="W131" s="5" t="s">
+      <c r="X131" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="X131" s="2"/>
-    </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y131" s="2"/>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="44" t="str">
         <f t="shared" ref="A132:A195" si="12">IF(H132&lt;&gt;"",IF(F132&lt;&gt;"",CONCATENATE("....",D132,".",E132,".",F132,". - ",T132),IF(E132&lt;&gt;"",CONCATENATE("...",D132,".",E132,". - ",T132),CONCATENATE("..",D132,". - ",T132))),"")</f>
         <v/>
@@ -13284,19 +13685,22 @@
         <v>913</v>
       </c>
       <c r="U132" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="V132" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="V132" s="5" t="s">
+      <c r="W132" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="W132" s="5" t="s">
+      <c r="X132" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="X132" s="2" t="s">
+      <c r="Y132" s="2" t="s">
         <v>1233</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13341,18 +13745,21 @@
       <c r="T133" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="U133" s="50" t="s">
+      <c r="U133" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="V133" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="V133" s="5" t="s">
+      <c r="W133" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="W133" s="51" t="s">
+      <c r="X133" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="X133" s="2"/>
-    </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y133" s="2"/>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13401,18 +13808,21 @@
       <c r="T134" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="U134" s="50" t="s">
+      <c r="U134" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="V134" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="V134" s="5" t="s">
+      <c r="W134" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="W134" s="51" t="s">
+      <c r="X134" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="X134" s="2"/>
-    </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y134" s="2"/>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13458,17 +13868,20 @@
         <v>1406</v>
       </c>
       <c r="U135" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="V135" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="V135" s="5" t="s">
+      <c r="W135" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="W135" s="5" t="s">
+      <c r="X135" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="X135" s="2"/>
-    </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y135" s="2"/>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13507,17 +13920,20 @@
         <v>1407</v>
       </c>
       <c r="U136" s="5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V136" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="V136" s="5" t="s">
+      <c r="W136" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="W136" s="5" t="s">
+      <c r="X136" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="X136" s="2"/>
-    </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y136" s="2"/>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13563,17 +13979,20 @@
         <v>916</v>
       </c>
       <c r="U137" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="V137" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="V137" s="5" t="s">
+      <c r="W137" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="W137" s="5" t="s">
+      <c r="X137" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="X137" s="2"/>
-    </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y137" s="2"/>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13619,17 +14038,20 @@
         <v>917</v>
       </c>
       <c r="U138" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="V138" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="V138" s="5" t="s">
+      <c r="W138" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="W138" s="5" t="s">
+      <c r="X138" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="X138" s="2"/>
-    </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y138" s="2"/>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13674,18 +14096,21 @@
       <c r="T139" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="U139" s="50" t="s">
+      <c r="U139" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="V139" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="V139" s="5" t="s">
+      <c r="W139" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="W139" s="51" t="s">
+      <c r="X139" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="X139" s="2"/>
-    </row>
-    <row r="140" spans="1:24" ht="33" x14ac:dyDescent="0.25">
+      <c r="Y139" s="2"/>
+    </row>
+    <row r="140" spans="1:25" ht="33" x14ac:dyDescent="0.25">
       <c r="A140" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13730,18 +14155,21 @@
       <c r="T140" s="5" t="s">
         <v>1408</v>
       </c>
-      <c r="U140" s="20" t="s">
+      <c r="U140" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V140" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="V140" s="5" t="s">
+      <c r="W140" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="W140" s="45" t="s">
+      <c r="X140" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="X140" s="2"/>
-    </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y140" s="2"/>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13787,20 +14215,23 @@
       <c r="T141" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="U141" s="20" t="s">
+      <c r="U141" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="V141" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="V141" s="2" t="s">
+      <c r="W141" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="W141" s="45" t="s">
+      <c r="X141" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="X141" s="2" t="s">
+      <c r="Y141" s="2" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.05. - Alzheimer’s disease and other dementias</v>
@@ -13852,18 +14283,21 @@
       <c r="T142" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="U142" s="20" t="s">
+      <c r="U142" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="V142" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="V142" s="5" t="s">
+      <c r="W142" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="W142" s="45" t="s">
+      <c r="X142" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="X142" s="2"/>
-    </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y142" s="2"/>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13912,18 +14346,21 @@
       <c r="T143" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="U143" s="50" t="s">
+      <c r="U143" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="V143" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="V143" s="5" t="s">
+      <c r="W143" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="W143" s="51" t="s">
+      <c r="X143" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="X143" s="2"/>
-    </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y143" s="2"/>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -13972,18 +14409,21 @@
       <c r="T144" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="U144" s="50" t="s">
+      <c r="U144" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="V144" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="V144" s="5" t="s">
+      <c r="W144" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="W144" s="51" t="s">
+      <c r="X144" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="X144" s="2"/>
-    </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y144" s="2"/>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14032,18 +14472,21 @@
       <c r="T145" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="U145" s="50" t="s">
+      <c r="U145" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="V145" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="V145" s="5" t="s">
+      <c r="W145" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="W145" s="51" t="s">
+      <c r="X145" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="X145" s="2"/>
-    </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y145" s="2"/>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14088,18 +14531,21 @@
       <c r="T146" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="U146" s="50" t="s">
+      <c r="U146" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="V146" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="V146" s="5" t="s">
+      <c r="W146" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="W146" s="51" t="s">
+      <c r="X146" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="X146" s="2"/>
-    </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y146" s="2"/>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14144,18 +14590,21 @@
       <c r="T147" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="U147" s="50" t="s">
+      <c r="U147" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="V147" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="V147" s="5" t="s">
+      <c r="W147" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="W147" s="51" t="s">
+      <c r="X147" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="X147" s="2"/>
-    </row>
-    <row r="148" spans="1:24" ht="51" x14ac:dyDescent="0.25">
+      <c r="Y147" s="2"/>
+    </row>
+    <row r="148" spans="1:25" ht="51" x14ac:dyDescent="0.25">
       <c r="A148" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.06. - Other neurological conditions</v>
@@ -14211,18 +14660,21 @@
       <c r="T148" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="U148" s="50" t="s">
+      <c r="U148" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="V148" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="V148" s="5" t="s">
+      <c r="W148" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="W148" s="51" t="s">
+      <c r="X148" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="X148" s="2"/>
-    </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y148" s="2"/>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14264,20 +14716,23 @@
       <c r="T149" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="U149" s="20" t="s">
+      <c r="U149" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="V149" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="V149" s="2" t="s">
+      <c r="W149" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="W149" s="45" t="s">
+      <c r="X149" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="X149" s="2" t="s">
+      <c r="Y149" s="2" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14322,18 +14777,21 @@
       <c r="T150" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="U150" s="52" t="s">
+      <c r="U150" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="V150" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="V150" s="5" t="s">
+      <c r="W150" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="W150" s="53" t="s">
+      <c r="X150" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="X150" s="2"/>
-    </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y150" s="2"/>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14378,18 +14836,21 @@
       <c r="T151" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="U151" s="52" t="s">
+      <c r="U151" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="V151" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="V151" s="5" t="s">
+      <c r="W151" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="W151" s="53" t="s">
+      <c r="X151" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="X151" s="2"/>
-    </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y151" s="2"/>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14434,18 +14895,21 @@
       <c r="T152" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="U152" s="52" t="s">
+      <c r="U152" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="V152" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="V152" s="5" t="s">
+      <c r="W152" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="W152" s="53" t="s">
+      <c r="X152" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="X152" s="2"/>
-    </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y152" s="2"/>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14490,18 +14954,21 @@
       <c r="T153" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="U153" s="52" t="s">
+      <c r="U153" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="V153" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="V153" s="5" t="s">
+      <c r="W153" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="W153" s="53" t="s">
+      <c r="X153" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="X153" s="2"/>
-    </row>
-    <row r="154" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y153" s="2"/>
+    </row>
+    <row r="154" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A154" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14546,18 +15013,21 @@
       <c r="T154" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="U154" s="52" t="s">
+      <c r="U154" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="V154" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="V154" s="5" t="s">
+      <c r="W154" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="W154" s="53" t="s">
+      <c r="X154" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="X154" s="2"/>
-    </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y154" s="2"/>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14602,18 +15072,21 @@
       <c r="T155" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="U155" s="52" t="s">
+      <c r="U155" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="V155" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="V155" s="5" t="s">
+      <c r="W155" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="W155" s="53" t="s">
+      <c r="X155" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="X155" s="2"/>
-    </row>
-    <row r="156" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y155" s="2"/>
+    </row>
+    <row r="156" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A156" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14658,20 +15131,23 @@
       <c r="T156" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="U156" s="52" t="s">
+      <c r="U156" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="V156" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="V156" s="5" t="s">
+      <c r="W156" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="W156" s="53" t="s">
+      <c r="X156" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="X156" s="2" t="s">
+      <c r="Y156" s="2" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="157" spans="1:24" ht="42" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="42" x14ac:dyDescent="0.25">
       <c r="A157" s="44" t="str">
         <f t="shared" si="12"/>
         <v>..C. - Cardiovascular diseases</v>
@@ -14718,18 +15194,21 @@
       <c r="T157" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="U157" s="20" t="s">
+      <c r="U157" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="V157" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="V157" s="2" t="s">
+      <c r="W157" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="W157" s="45" t="s">
+      <c r="X157" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="X157" s="2"/>
-    </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y157" s="2"/>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -14782,18 +15261,21 @@
       <c r="T158" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="U158" s="50" t="s">
+      <c r="U158" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="V158" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="V158" s="5" t="s">
+      <c r="W158" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="W158" s="51" t="s">
+      <c r="X158" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="X158" s="2"/>
-    </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y158" s="2"/>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.01. - Hypertensive heart disease</v>
@@ -14849,18 +15331,21 @@
       <c r="T159" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="U159" s="50" t="s">
+      <c r="U159" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="V159" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="V159" s="5" t="s">
+      <c r="W159" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="W159" s="51" t="s">
+      <c r="X159" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="X159" s="2"/>
-    </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y159" s="2"/>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.02. - Ischemic heart disease</v>
@@ -14916,18 +15401,21 @@
       <c r="T160" s="5" t="s">
         <v>1409</v>
       </c>
-      <c r="U160" s="50" t="s">
+      <c r="U160" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="V160" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="V160" s="5" t="s">
+      <c r="W160" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="W160" s="51" t="s">
+      <c r="X160" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="X160" s="2"/>
-    </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y160" s="2"/>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.03. - Stroke</v>
@@ -14987,18 +15475,21 @@
       <c r="T161" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="U161" s="50" t="s">
+      <c r="U161" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="V161" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="V161" s="5" t="s">
+      <c r="W161" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="W161" s="51" t="s">
+      <c r="X161" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="X161" s="2"/>
-    </row>
-    <row r="162" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y161" s="2"/>
+    </row>
+    <row r="162" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A162" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.04. - Cardiomyopathy, myocarditis, endocarditis</v>
@@ -15054,20 +15545,23 @@
       <c r="T162" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="U162" s="50" t="s">
+      <c r="U162" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="V162" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="V162" s="5" t="s">
+      <c r="W162" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="W162" s="51" t="s">
+      <c r="X162" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="X162" s="76" t="s">
+      <c r="Y162" s="76" t="s">
         <v>1344</v>
       </c>
     </row>
-    <row r="163" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A163" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.05. -  Congestive heart failure</v>
@@ -15115,12 +15609,15 @@
       <c r="T163" s="5" t="s">
         <v>1325</v>
       </c>
-      <c r="U163" s="50"/>
-      <c r="V163" s="5"/>
-      <c r="W163" s="51"/>
-      <c r="X163" s="2"/>
-    </row>
-    <row r="164" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="U163" s="5" t="s">
+        <v>1325</v>
+      </c>
+      <c r="V163" s="50"/>
+      <c r="W163" s="5"/>
+      <c r="X163" s="51"/>
+      <c r="Y163" s="2"/>
+    </row>
+    <row r="164" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A164" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...C.99. - Other or unspecified cardiovascular diseases</v>
@@ -15180,20 +15677,23 @@
       <c r="T164" s="74" t="s">
         <v>1319</v>
       </c>
-      <c r="U164" s="52" t="s">
+      <c r="U164" s="74" t="s">
+        <v>1420</v>
+      </c>
+      <c r="V164" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="V164" s="5" t="s">
+      <c r="W164" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="W164" s="53" t="s">
+      <c r="X164" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="X164" s="76" t="s">
+      <c r="Y164" s="76" t="s">
         <v>1341</v>
       </c>
     </row>
-    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15239,18 +15739,21 @@
       <c r="T165" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="U165" s="20" t="s">
+      <c r="U165" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="V165" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="V165" s="2" t="s">
+      <c r="W165" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="W165" s="45" t="s">
+      <c r="X165" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="X165" s="2"/>
-    </row>
-    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y165" s="2"/>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.66. - Chronic obstructive pulmonary disease</v>
@@ -15302,18 +15805,21 @@
       <c r="T166" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="U166" s="20" t="s">
+      <c r="U166" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="V166" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="V166" s="5" t="s">
+      <c r="W166" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="W166" s="45" t="s">
+      <c r="X166" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="X166" s="2"/>
-    </row>
-    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y166" s="2"/>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.67. - Asthma</v>
@@ -15365,18 +15871,21 @@
       <c r="T167" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="U167" s="20" t="s">
+      <c r="U167" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="V167" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="V167" s="5" t="s">
+      <c r="W167" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="W167" s="45" t="s">
+      <c r="X167" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="X167" s="2"/>
-    </row>
-    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y167" s="2"/>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.68. - Other respiratory diseases</v>
@@ -15428,18 +15937,21 @@
       <c r="T168" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="U168" s="20" t="s">
+      <c r="U168" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="V168" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="V168" s="5" t="s">
+      <c r="W168" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="W168" s="45" t="s">
+      <c r="X168" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="X168" s="2"/>
-    </row>
-    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y168" s="2"/>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.09. - Digestive diseases (excluding cirrhosis)</v>
@@ -15490,18 +16002,21 @@
       <c r="T169" s="76" t="s">
         <v>1328</v>
       </c>
-      <c r="U169" s="20" t="s">
+      <c r="U169" s="76" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V169" s="20" t="s">
         <v>1329</v>
       </c>
-      <c r="V169" s="2" t="s">
+      <c r="W169" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="W169" s="45" t="s">
+      <c r="X169" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="X169" s="2"/>
-    </row>
-    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y169" s="2"/>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15550,18 +16065,21 @@
       <c r="T170" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="U170" s="20" t="s">
+      <c r="U170" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="V170" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="V170" s="5" t="s">
+      <c r="W170" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="W170" s="45" t="s">
+      <c r="X170" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="X170" s="2"/>
-    </row>
-    <row r="171" spans="1:24" s="48" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y170" s="2"/>
+    </row>
+    <row r="171" spans="1:25" s="48" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A171" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.11. - Cirrhosis of the liver</v>
@@ -15617,18 +16135,21 @@
       <c r="T171" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="U171" s="50" t="s">
+      <c r="U171" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="V171" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="V171" s="5" t="s">
+      <c r="W171" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="W171" s="50" t="s">
+      <c r="X171" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="X171" s="2"/>
-    </row>
-    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y171" s="2"/>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15677,18 +16198,21 @@
       <c r="T172" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="U172" s="50" t="s">
+      <c r="U172" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="V172" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="V172" s="5" t="s">
+      <c r="W172" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="W172" s="51" t="s">
+      <c r="X172" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="X172" s="2"/>
-    </row>
-    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y172" s="2"/>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15738,17 +16262,20 @@
         <v>919</v>
       </c>
       <c r="U173" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="V173" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="V173" s="5" t="s">
+      <c r="W173" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="W173" s="5" t="s">
+      <c r="X173" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="X173" s="2"/>
-    </row>
-    <row r="174" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y173" s="2"/>
+    </row>
+    <row r="174" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A174" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15798,17 +16325,20 @@
         <v>920</v>
       </c>
       <c r="U174" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="V174" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="V174" s="5" t="s">
+      <c r="W174" s="5" t="s">
         <v>920</v>
       </c>
-      <c r="W174" s="5" t="s">
+      <c r="X174" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="X174" s="2"/>
-    </row>
-    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y174" s="2"/>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15858,17 +16388,20 @@
         <v>921</v>
       </c>
       <c r="U175" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="V175" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="V175" s="5" t="s">
+      <c r="W175" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="W175" s="5" t="s">
+      <c r="X175" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="X175" s="2"/>
-    </row>
-    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y175" s="2"/>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15918,17 +16451,20 @@
         <v>922</v>
       </c>
       <c r="U176" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="V176" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="V176" s="5" t="s">
+      <c r="W176" s="5" t="s">
         <v>922</v>
       </c>
-      <c r="W176" s="5" t="s">
+      <c r="X176" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="X176" s="2"/>
-    </row>
-    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y176" s="2"/>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -15978,17 +16514,20 @@
         <v>923</v>
       </c>
       <c r="U177" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="V177" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="V177" s="5" t="s">
+      <c r="W177" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="W177" s="5" t="s">
+      <c r="X177" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="X177" s="2"/>
-    </row>
-    <row r="178" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y177" s="2"/>
+    </row>
+    <row r="178" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A178" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16041,18 +16580,21 @@
       <c r="T178" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="U178" s="50" t="s">
+      <c r="U178" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="V178" s="50" t="s">
         <v>738</v>
       </c>
-      <c r="V178" s="5" t="s">
+      <c r="W178" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="W178" s="51" t="s">
+      <c r="X178" s="51" t="s">
         <v>738</v>
       </c>
-      <c r="X178" s="2"/>
-    </row>
-    <row r="179" spans="1:24" ht="33" x14ac:dyDescent="0.25">
+      <c r="Y178" s="2"/>
+    </row>
+    <row r="179" spans="1:25" ht="33" x14ac:dyDescent="0.25">
       <c r="A179" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16096,18 +16638,21 @@
       <c r="T179" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="U179" s="20" t="s">
+      <c r="U179" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="V179" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="V179" s="2" t="s">
+      <c r="W179" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="W179" s="45" t="s">
+      <c r="X179" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="X179" s="2"/>
-    </row>
-    <row r="180" spans="1:24" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="Y179" s="2"/>
+    </row>
+    <row r="180" spans="1:25" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A180" s="44" t="str">
         <f t="shared" si="12"/>
         <v>...D.10. - Kidney diseases</v>
@@ -16160,18 +16705,21 @@
       <c r="T180" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="U180" s="50" t="s">
+      <c r="U180" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="V180" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="V180" s="5" t="s">
+      <c r="W180" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="W180" s="51" t="s">
+      <c r="X180" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="X180" s="2"/>
-    </row>
-    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y180" s="2"/>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="44" t="str">
         <f t="shared" si="12"/>
         <v>....D.10.a. - Acute glomerulonephritis</v>
@@ -16228,17 +16776,20 @@
         <v>925</v>
       </c>
       <c r="U181" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="V181" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="V181" s="5" t="s">
+      <c r="W181" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="W181" s="5" t="s">
+      <c r="X181" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="X181" s="2"/>
-    </row>
-    <row r="182" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y181" s="2"/>
+    </row>
+    <row r="182" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A182" s="44" t="str">
         <f t="shared" si="12"/>
         <v>....D.10.b. - Chronic kidney disease due to diabetes</v>
@@ -16295,17 +16846,20 @@
         <v>1410</v>
       </c>
       <c r="U182" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="V182" s="5" t="s">
         <v>928</v>
       </c>
-      <c r="V182" s="5" t="s">
+      <c r="W182" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="W182" s="5" t="s">
+      <c r="X182" s="5" t="s">
         <v>928</v>
       </c>
-      <c r="X182" s="2"/>
-    </row>
-    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y182" s="2"/>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="44" t="str">
         <f t="shared" si="12"/>
         <v>....D.10.c. - Other chronic kidney disease</v>
@@ -16362,17 +16916,20 @@
         <v>927</v>
       </c>
       <c r="U183" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="V183" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="V183" s="5" t="s">
+      <c r="W183" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="W183" s="5" t="s">
+      <c r="X183" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="X183" s="2"/>
-    </row>
-    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y183" s="2"/>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16417,18 +16974,21 @@
       <c r="T184" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="U184" s="50" t="s">
+      <c r="U184" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="V184" s="50" t="s">
         <v>742</v>
       </c>
-      <c r="V184" s="5" t="s">
+      <c r="W184" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="W184" s="51" t="s">
+      <c r="X184" s="51" t="s">
         <v>742</v>
       </c>
-      <c r="X184" s="2"/>
-    </row>
-    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y184" s="2"/>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16477,18 +17037,21 @@
       <c r="T185" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="U185" s="50" t="s">
+      <c r="U185" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="V185" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="V185" s="5" t="s">
+      <c r="W185" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="W185" s="51" t="s">
+      <c r="X185" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="X185" s="2"/>
-    </row>
-    <row r="186" spans="1:24" ht="24" x14ac:dyDescent="0.25">
+      <c r="Y185" s="2"/>
+    </row>
+    <row r="186" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A186" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16537,18 +17100,21 @@
       <c r="T186" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="U186" s="50" t="s">
+      <c r="U186" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="V186" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="V186" s="5" t="s">
+      <c r="W186" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="W186" s="51" t="s">
+      <c r="X186" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="X186" s="2"/>
-    </row>
-    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y186" s="2"/>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16597,18 +17163,21 @@
       <c r="T187" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="U187" s="50" t="s">
+      <c r="U187" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="V187" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="V187" s="5" t="s">
+      <c r="W187" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="W187" s="51" t="s">
+      <c r="X187" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="X187" s="2"/>
-    </row>
-    <row r="188" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="Y187" s="2"/>
+    </row>
+    <row r="188" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A188" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16657,18 +17226,21 @@
       <c r="T188" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="U188" s="50" t="s">
+      <c r="U188" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="V188" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="V188" s="5" t="s">
+      <c r="W188" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="W188" s="51" t="s">
+      <c r="X188" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="X188" s="2"/>
-    </row>
-    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y188" s="2"/>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16715,18 +17287,21 @@
       <c r="T189" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="U189" s="20" t="s">
+      <c r="U189" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="V189" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="V189" s="5" t="s">
+      <c r="W189" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="W189" s="45" t="s">
+      <c r="X189" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="X189" s="2"/>
-    </row>
-    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y189" s="2"/>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16774,18 +17349,21 @@
       <c r="T190" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="U190" s="20" t="s">
+      <c r="U190" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="V190" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="V190" s="2" t="s">
+      <c r="W190" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="W190" s="45" t="s">
+      <c r="X190" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="X190" s="2"/>
-    </row>
-    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y190" s="2"/>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16834,18 +17412,21 @@
       <c r="T191" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="U191" s="50" t="s">
+      <c r="U191" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="V191" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="V191" s="5" t="s">
+      <c r="W191" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="W191" s="51" t="s">
+      <c r="X191" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="X191" s="2"/>
-    </row>
-    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y191" s="2"/>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16890,18 +17471,21 @@
       <c r="T192" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="U192" s="50" t="s">
+      <c r="U192" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="V192" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="V192" s="5" t="s">
+      <c r="W192" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="W192" s="51" t="s">
+      <c r="X192" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="X192" s="2"/>
-    </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y192" s="2"/>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -16946,18 +17530,21 @@
       <c r="T193" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="U193" s="50" t="s">
+      <c r="U193" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="V193" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="V193" s="5" t="s">
+      <c r="W193" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="W193" s="51" t="s">
+      <c r="X193" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="X193" s="2"/>
-    </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y193" s="2"/>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -17002,18 +17589,21 @@
       <c r="T194" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="U194" s="50" t="s">
+      <c r="U194" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="V194" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="V194" s="5" t="s">
+      <c r="W194" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="W194" s="51" t="s">
+      <c r="X194" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="X194" s="2"/>
-    </row>
-    <row r="195" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y194" s="2"/>
+    </row>
+    <row r="195" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A195" s="44" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -17066,18 +17656,21 @@
       <c r="T195" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="U195" s="50" t="s">
+      <c r="U195" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="V195" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="V195" s="5" t="s">
+      <c r="W195" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="W195" s="51" t="s">
+      <c r="X195" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="X195" s="2"/>
-    </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y195" s="2"/>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="44" t="str">
         <f t="shared" ref="A196:A232" si="19">IF(H196&lt;&gt;"",IF(F196&lt;&gt;"",CONCATENATE("....",D196,".",E196,".",F196,". - ",T196),IF(E196&lt;&gt;"",CONCATENATE("...",D196,".",E196,". - ",T196),CONCATENATE("..",D196,". - ",T196))),"")</f>
         <v>...D.12. - Congenital anomalies</v>
@@ -17128,18 +17721,21 @@
       <c r="T196" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="U196" s="20" t="s">
+      <c r="U196" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="V196" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="V196" s="2" t="s">
+      <c r="W196" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="W196" s="45" t="s">
+      <c r="X196" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="X196" s="2"/>
-    </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y196" s="2"/>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17188,18 +17784,21 @@
       <c r="T197" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="U197" s="50" t="s">
+      <c r="U197" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="V197" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="V197" s="5" t="s">
+      <c r="W197" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="W197" s="51" t="s">
+      <c r="X197" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="X197" s="2"/>
-    </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y197" s="2"/>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17248,18 +17847,21 @@
       <c r="T198" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="U198" s="50" t="s">
+      <c r="U198" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="V198" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="V198" s="5" t="s">
+      <c r="W198" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="W198" s="51" t="s">
+      <c r="X198" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="X198" s="2"/>
-    </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y198" s="2"/>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17308,18 +17910,21 @@
       <c r="T199" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="U199" s="50" t="s">
+      <c r="U199" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="V199" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="V199" s="5" t="s">
+      <c r="W199" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="W199" s="51" t="s">
+      <c r="X199" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="X199" s="2"/>
-    </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y199" s="2"/>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17368,18 +17973,21 @@
       <c r="T200" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="U200" s="50" t="s">
+      <c r="U200" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="V200" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="V200" s="5" t="s">
+      <c r="W200" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="W200" s="51" t="s">
+      <c r="X200" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="X200" s="2"/>
-    </row>
-    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y200" s="2"/>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17428,18 +18036,21 @@
       <c r="T201" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="U201" s="50" t="s">
+      <c r="U201" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="V201" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="V201" s="5" t="s">
+      <c r="W201" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="W201" s="51" t="s">
+      <c r="X201" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="X201" s="2"/>
-    </row>
-    <row r="202" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y201" s="2"/>
+    </row>
+    <row r="202" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A202" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17488,18 +18099,21 @@
       <c r="T202" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="U202" s="50" t="s">
+      <c r="U202" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="V202" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="V202" s="5" t="s">
+      <c r="W202" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="W202" s="51" t="s">
+      <c r="X202" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="X202" s="2"/>
-    </row>
-    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y202" s="2"/>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17541,18 +18155,21 @@
       <c r="T203" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="U203" s="20" t="s">
+      <c r="U203" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="V203" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="V203" s="2" t="s">
+      <c r="W203" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="W203" s="45" t="s">
+      <c r="X203" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="X203" s="2"/>
-    </row>
-    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y203" s="2"/>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17597,18 +18214,21 @@
       <c r="T204" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="U204" s="50" t="s">
+      <c r="U204" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="V204" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="V204" s="5" t="s">
+      <c r="W204" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="W204" s="51" t="s">
+      <c r="X204" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="X204" s="2"/>
-    </row>
-    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y204" s="2"/>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17653,18 +18273,21 @@
       <c r="T205" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="U205" s="50" t="s">
+      <c r="U205" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="V205" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="V205" s="5" t="s">
+      <c r="W205" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="W205" s="51" t="s">
+      <c r="X205" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="X205" s="2"/>
-    </row>
-    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y205" s="2"/>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17709,18 +18332,21 @@
       <c r="T206" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="U206" s="50" t="s">
+      <c r="U206" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="V206" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="V206" s="5" t="s">
+      <c r="W206" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="W206" s="51" t="s">
+      <c r="X206" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="X206" s="2"/>
-    </row>
-    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y206" s="2"/>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17765,18 +18391,21 @@
       <c r="T207" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="U207" s="50" t="s">
+      <c r="U207" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="V207" s="50" t="s">
         <v>744</v>
       </c>
-      <c r="V207" s="5" t="s">
+      <c r="W207" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="W207" s="51" t="s">
+      <c r="X207" s="51" t="s">
         <v>744</v>
       </c>
-      <c r="X207" s="2"/>
-    </row>
-    <row r="208" spans="1:24" ht="24" x14ac:dyDescent="0.25">
+      <c r="Y207" s="2"/>
+    </row>
+    <row r="208" spans="1:25" ht="24" x14ac:dyDescent="0.25">
       <c r="A208" s="44" t="str">
         <f t="shared" si="19"/>
         <v>..E. - Injuries</v>
@@ -17823,18 +18452,21 @@
       <c r="T208" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="U208" s="20" t="s">
+      <c r="U208" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="V208" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="V208" s="2" t="s">
+      <c r="W208" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="W208" s="45" t="s">
+      <c r="X208" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="X208" s="2"/>
-    </row>
-    <row r="209" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="Y208" s="2"/>
+    </row>
+    <row r="209" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -17880,18 +18512,21 @@
       <c r="T209" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="U209" s="20" t="s">
+      <c r="U209" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="V209" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="V209" s="2" t="s">
+      <c r="W209" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="W209" s="45" t="s">
+      <c r="X209" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="X209" s="2"/>
-    </row>
-    <row r="210" spans="1:24" ht="36" x14ac:dyDescent="0.25">
+      <c r="Y209" s="2"/>
+    </row>
+    <row r="210" spans="1:25" ht="36" x14ac:dyDescent="0.25">
       <c r="A210" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.01. - Road injury</v>
@@ -17947,18 +18582,21 @@
       <c r="T210" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="U210" s="20" t="s">
+      <c r="U210" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="V210" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="V210" s="5" t="s">
+      <c r="W210" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="W210" s="45" t="s">
+      <c r="X210" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="X210" s="2"/>
-    </row>
-    <row r="211" spans="1:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="Y210" s="2"/>
+    </row>
+    <row r="211" spans="1:25" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.02. - Drug poisonings</v>
@@ -18002,12 +18640,15 @@
       <c r="T211" s="5" t="s">
         <v>1395</v>
       </c>
-      <c r="U211" s="20"/>
-      <c r="V211" s="5"/>
-      <c r="W211" s="45"/>
-      <c r="X211" s="2"/>
-    </row>
-    <row r="212" spans="1:24" ht="51" x14ac:dyDescent="0.25">
+      <c r="U211" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="V211" s="20"/>
+      <c r="W211" s="5"/>
+      <c r="X211" s="45"/>
+      <c r="Y211" s="2"/>
+    </row>
+    <row r="212" spans="1:25" ht="51" x14ac:dyDescent="0.25">
       <c r="A212" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.03. - Poisonings (non-drug)</v>
@@ -18061,18 +18702,21 @@
       <c r="T212" s="5" t="s">
         <v>1396</v>
       </c>
-      <c r="U212" s="20" t="s">
+      <c r="U212" s="5" t="s">
+        <v>1396</v>
+      </c>
+      <c r="V212" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="V212" s="5" t="s">
+      <c r="W212" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="W212" s="45" t="s">
+      <c r="X212" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="X212" s="2"/>
-    </row>
-    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y212" s="2"/>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.04. - Falls</v>
@@ -18126,18 +18770,21 @@
       <c r="T213" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="U213" s="20" t="s">
+      <c r="U213" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="V213" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="V213" s="5" t="s">
+      <c r="W213" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="W213" s="45" t="s">
+      <c r="X213" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="X213" s="2"/>
-    </row>
-    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y213" s="2"/>
+    </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18184,18 +18831,21 @@
       <c r="T214" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="U214" s="20" t="s">
+      <c r="U214" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="V214" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="V214" s="5" t="s">
+      <c r="W214" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="W214" s="45" t="s">
+      <c r="X214" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="X214" s="2"/>
-    </row>
-    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y214" s="2"/>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18244,18 +18894,21 @@
       <c r="T215" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="U215" s="20" t="s">
+      <c r="U215" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="V215" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="V215" s="5" t="s">
+      <c r="W215" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="W215" s="45" t="s">
+      <c r="X215" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="X215" s="2"/>
-    </row>
-    <row r="216" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="Y215" s="2"/>
+    </row>
+    <row r="216" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A216" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18304,18 +18957,21 @@
       <c r="T216" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="U216" s="20" t="s">
+      <c r="U216" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="V216" s="20" t="s">
         <v>746</v>
       </c>
-      <c r="V216" s="5" t="s">
+      <c r="W216" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="W216" s="45" t="s">
+      <c r="X216" s="45" t="s">
         <v>746</v>
       </c>
-      <c r="X216" s="2"/>
-    </row>
-    <row r="217" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y216" s="2"/>
+    </row>
+    <row r="217" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A217" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18358,12 +19014,15 @@
       <c r="T217" s="5" t="s">
         <v>1374</v>
       </c>
-      <c r="U217" s="20"/>
-      <c r="V217" s="5"/>
-      <c r="W217" s="45"/>
-      <c r="X217" s="2"/>
-    </row>
-    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U217" s="5" t="s">
+        <v>1374</v>
+      </c>
+      <c r="V217" s="20"/>
+      <c r="W217" s="5"/>
+      <c r="X217" s="45"/>
+      <c r="Y217" s="2"/>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18412,18 +19071,21 @@
       <c r="T218" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="U218" s="20" t="s">
+      <c r="U218" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="V218" s="20" t="s">
         <v>747</v>
       </c>
-      <c r="V218" s="5" t="s">
+      <c r="W218" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="W218" s="45" t="s">
+      <c r="X218" s="45" t="s">
         <v>747</v>
       </c>
-      <c r="X218" s="2"/>
-    </row>
-    <row r="219" spans="1:24" ht="33" x14ac:dyDescent="0.25">
+      <c r="Y218" s="2"/>
+    </row>
+    <row r="219" spans="1:25" ht="33" x14ac:dyDescent="0.25">
       <c r="A219" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.05. - Other unintentional injuries</v>
@@ -18479,20 +19141,23 @@
       <c r="T219" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="U219" s="20" t="s">
+      <c r="U219" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="V219" s="20" t="s">
         <v>887</v>
       </c>
-      <c r="V219" s="5" t="s">
+      <c r="W219" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="W219" s="45" t="s">
+      <c r="X219" s="45" t="s">
         <v>887</v>
       </c>
-      <c r="X219" s="22" t="s">
+      <c r="Y219" s="22" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="220" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A220" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18534,18 +19199,21 @@
       <c r="T220" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="U220" s="20" t="s">
+      <c r="U220" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="V220" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="V220" s="2" t="s">
+      <c r="W220" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="W220" s="45" t="s">
+      <c r="X220" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="X220" s="2"/>
-    </row>
-    <row r="221" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y220" s="2"/>
+    </row>
+    <row r="221" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A221" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.07. - Suicide/Self-harm</v>
@@ -18601,18 +19269,21 @@
       <c r="T221" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="U221" s="20" t="s">
+      <c r="U221" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V221" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="V221" s="5" t="s">
+      <c r="W221" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="W221" s="45" t="s">
+      <c r="X221" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="X221" s="2"/>
-    </row>
-    <row r="222" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="Y221" s="2"/>
+    </row>
+    <row r="222" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A222" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.08. - Homicide/Interpersonal violence</v>
@@ -18659,18 +19330,21 @@
       <c r="T222" s="5" t="s">
         <v>1272</v>
       </c>
-      <c r="U222" s="20" t="s">
+      <c r="U222" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="V222" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="V222" s="5" t="s">
+      <c r="W222" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="W222" s="45" t="s">
+      <c r="X222" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="X222" s="2"/>
-    </row>
-    <row r="223" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y222" s="2"/>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="44" t="str">
         <f t="shared" si="19"/>
         <v>....E.08.a. - Homicide excluding legal intervention</v>
@@ -18714,12 +19388,15 @@
       <c r="T223" s="20" t="s">
         <v>1365</v>
       </c>
-      <c r="U223" s="46"/>
-      <c r="V223" s="5"/>
-      <c r="W223" s="45"/>
-      <c r="X223" s="2"/>
-    </row>
-    <row r="224" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U223" s="20" t="s">
+        <v>1365</v>
+      </c>
+      <c r="V223" s="46"/>
+      <c r="W223" s="5"/>
+      <c r="X223" s="45"/>
+      <c r="Y223" s="2"/>
+    </row>
+    <row r="224" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="44" t="str">
         <f t="shared" si="19"/>
         <v>....E.08.b. - Legal intervention</v>
@@ -18765,12 +19442,15 @@
       <c r="T224" s="20" t="s">
         <v>1364</v>
       </c>
-      <c r="U224" s="46"/>
-      <c r="V224" s="5"/>
-      <c r="W224" s="45"/>
-      <c r="X224" s="2"/>
-    </row>
-    <row r="225" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="U224" s="20" t="s">
+        <v>1364</v>
+      </c>
+      <c r="V224" s="46"/>
+      <c r="W224" s="5"/>
+      <c r="X224" s="45"/>
+      <c r="Y224" s="2"/>
+    </row>
+    <row r="225" spans="1:25" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A225" s="44" t="str">
         <f t="shared" si="19"/>
         <v>....E.08.c. - Execution, War, Terrorism</v>
@@ -18824,20 +19504,23 @@
       <c r="T225" s="5" t="s">
         <v>1411</v>
       </c>
-      <c r="U225" s="20" t="s">
+      <c r="U225" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="V225" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="V225" s="5" t="s">
+      <c r="W225" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="W225" s="45" t="s">
+      <c r="X225" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="X225" s="22" t="s">
+      <c r="Y225" s="22" t="s">
         <v>1237</v>
       </c>
     </row>
-    <row r="226" spans="1:24" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A226" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...E.99. - Injuries of unknown intent (e.g., unintentional or self-harm), including overdoses and deaths by firearm</v>
@@ -18877,8 +19560,11 @@
       <c r="T226" s="48" t="s">
         <v>1218</v>
       </c>
-    </row>
-    <row r="227" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U226" s="48" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A227" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...Z.01. - Symptoms, signs and ill-defined conditions, not elsewhere classified</v>
@@ -18912,8 +19598,11 @@
       <c r="T227" s="48" t="s">
         <v>1223</v>
       </c>
-    </row>
-    <row r="228" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="U227" s="48" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A228" s="44" t="str">
         <f t="shared" si="19"/>
         <v/>
@@ -18944,8 +19633,11 @@
       <c r="T228" s="48" t="s">
         <v>1214</v>
       </c>
-    </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U228" s="48" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...Z.02. - Unknown/Missing Value</v>
@@ -18964,8 +19656,11 @@
       <c r="T229" s="48" t="s">
         <v>1310</v>
       </c>
-    </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U229" s="48" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...Z.03. - Code does not map</v>
@@ -18987,8 +19682,11 @@
       <c r="T230" s="48" t="s">
         <v>1241</v>
       </c>
-    </row>
-    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U230" s="48" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" s="44" t="str">
         <f t="shared" si="19"/>
         <v>..Z. - Unknown/Missing Value</v>
@@ -19004,8 +19702,11 @@
       <c r="T231" s="48" t="s">
         <v>1310</v>
       </c>
-    </row>
-    <row r="232" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U231" s="48" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" s="44" t="str">
         <f t="shared" si="19"/>
         <v>...D.99. - Other Chronic Conditions</v>
@@ -19024,9 +19725,12 @@
       <c r="T232" s="48" t="s">
         <v>1271</v>
       </c>
+      <c r="U232" s="48" t="s">
+        <v>1271</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X225"/>
+  <autoFilter ref="A1:Y225"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
